--- a/Gaboch_portfolio.xlsx
+++ b/Gaboch_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gaboch_Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA3D9CF1-FCF2-4164-A426-4726CF90F385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269E82A3-F4A6-40C1-91ED-C94BD3D9A394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" xr2:uid="{D37FE5D9-1440-4A1A-AC91-48FA1ED826EA}"/>
   </bookViews>
@@ -1452,9 +1452,6 @@
     <t>Canadian #. Bought on May 28, 2024</t>
   </si>
   <si>
-    <t>Manulife</t>
-  </si>
-  <si>
     <t>Bought on May 30, 2024 and sold on July 30, 2024</t>
   </si>
   <si>
@@ -2290,6 +2287,9 @@
   <si>
     <t>TD.TO</t>
   </si>
+  <si>
+    <t>MFC.TO</t>
+  </si>
 </sst>
 </file>
 
@@ -2306,7 +2306,7 @@
     <numFmt numFmtId="170" formatCode="0.00000"/>
     <numFmt numFmtId="171" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2419,6 +2419,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF232A31"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2595,7 +2602,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="207">
+  <cellXfs count="208">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2999,16 +3006,16 @@
     <xf numFmtId="1" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3017,19 +3024,55 @@
     <xf numFmtId="2" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3038,53 +3081,17 @@
     <xf numFmtId="2" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3092,31 +3099,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3124,33 +3116,6 @@
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3164,56 +3129,101 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -9762,7 +9772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ECB3444-92D9-4200-8B78-7CB7FAE28719}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1" filterMode="1"/>
   <dimension ref="A1:AE611"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
@@ -9789,7 +9799,7 @@
   <sheetData>
     <row r="1" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -9798,16 +9808,16 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>2</v>
@@ -9816,19 +9826,19 @@
         <v>3</v>
       </c>
       <c r="J1" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="122" t="s">
         <v>404</v>
       </c>
-      <c r="L1" s="122" t="s">
+      <c r="M1" s="122" t="s">
         <v>405</v>
       </c>
-      <c r="M1" s="122" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -9864,7 +9874,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>1</v>
       </c>
@@ -9904,7 +9914,7 @@
       <c r="L3" s="11"/>
       <c r="M3" s="11"/>
     </row>
-    <row r="4" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -9940,7 +9950,7 @@
       <c r="L4" s="11"/>
       <c r="M4" s="11"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -9980,7 +9990,7 @@
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>1</v>
       </c>
@@ -10014,7 +10024,7 @@
       <c r="M6" s="11"/>
       <c r="N6" s="11"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>1</v>
       </c>
@@ -10056,12 +10066,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="198" t="s">
-        <v>306</v>
+      <c r="B8" s="138" t="s">
+        <v>305</v>
       </c>
       <c r="C8" s="13" t="e" vm="3">
         <v>#VALUE!</v>
@@ -10097,11 +10107,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>1</v>
       </c>
-      <c r="B9" s="198"/>
+      <c r="B9" s="138"/>
       <c r="C9" s="15" t="s">
         <v>10</v>
       </c>
@@ -10142,7 +10152,7 @@
         <v>-166.39000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>1</v>
       </c>
@@ -10180,7 +10190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>1</v>
       </c>
@@ -10224,8 +10234,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="156" t="s">
+    <row r="12" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B12" s="168" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="52" t="e" vm="5">
@@ -10257,8 +10267,8 @@
       <c r="L12" s="11"/>
       <c r="M12" s="11"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B13" s="156"/>
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B13" s="168"/>
       <c r="C13" s="52" t="s">
         <v>13</v>
       </c>
@@ -10296,7 +10306,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>1</v>
       </c>
@@ -10332,7 +10342,7 @@
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>1</v>
       </c>
@@ -10374,7 +10384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>1</v>
       </c>
@@ -10413,7 +10423,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>1</v>
       </c>
@@ -10456,7 +10466,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B18" s="51" t="s">
         <v>17</v>
       </c>
@@ -10492,7 +10502,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" s="51"/>
       <c r="C19" s="52" t="s">
         <v>20</v>
@@ -10528,7 +10538,7 @@
       <c r="L19" s="123"/>
       <c r="M19" s="123"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" s="51" t="s">
         <v>17</v>
       </c>
@@ -10564,7 +10574,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" s="51"/>
       <c r="C21" s="52" t="s">
         <v>20</v>
@@ -10600,7 +10610,7 @@
       <c r="L21" s="123"/>
       <c r="M21" s="123"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" s="51" t="s">
         <v>17</v>
       </c>
@@ -10636,7 +10646,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" s="51"/>
       <c r="C23" s="52" t="s">
         <v>20</v>
@@ -10672,7 +10682,7 @@
       <c r="L23" s="123"/>
       <c r="M23" s="123"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>1</v>
       </c>
@@ -10705,7 +10715,7 @@
       <c r="L24" s="11"/>
       <c r="M24" s="11"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>1</v>
       </c>
@@ -10744,7 +10754,7 @@
       <c r="L25" s="11"/>
       <c r="M25" s="11"/>
     </row>
-    <row r="26" spans="1:16" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="51" t="s">
         <v>21</v>
       </c>
@@ -10780,7 +10790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -10828,7 +10838,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>1</v>
       </c>
@@ -10863,7 +10873,7 @@
       <c r="L28" s="11"/>
       <c r="M28" s="11"/>
     </row>
-    <row r="29" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>1</v>
       </c>
@@ -10907,8 +10917,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B30" s="156" t="s">
+    <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="168" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="47" t="e" vm="8">
@@ -10939,8 +10949,8 @@
       <c r="L30" s="11"/>
       <c r="M30" s="11"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B31" s="156"/>
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="168"/>
       <c r="C31" s="47" t="s">
         <v>27</v>
       </c>
@@ -10977,8 +10987,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B32" s="156" t="s">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="168" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="47" t="e" vm="8">
@@ -11009,8 +11019,8 @@
       <c r="L32" s="11"/>
       <c r="M32" s="11"/>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B33" s="156"/>
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="168"/>
       <c r="C33" s="47" t="s">
         <v>27</v>
       </c>
@@ -11047,8 +11057,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B34" s="156" t="s">
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="168" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="47" t="e" vm="8">
@@ -11079,8 +11089,8 @@
       <c r="L34" s="11"/>
       <c r="M34" s="11"/>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B35" s="156"/>
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="168"/>
       <c r="C35" s="47" t="s">
         <v>27</v>
       </c>
@@ -11117,7 +11127,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" s="51" t="s">
         <v>29</v>
       </c>
@@ -11153,7 +11163,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="C37" s="52" t="s">
         <v>31</v>
       </c>
@@ -11189,8 +11199,8 @@
       <c r="L37" s="11"/>
       <c r="M37" s="11"/>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B38" s="156" t="s">
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="168" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="47" t="e" vm="8">
@@ -11221,8 +11231,8 @@
       <c r="L38" s="11"/>
       <c r="M38" s="11"/>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B39" s="156"/>
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="168"/>
       <c r="C39" s="47" t="s">
         <v>27</v>
       </c>
@@ -11259,8 +11269,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="157" t="s">
+    <row r="40" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="182" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="47" t="e" vm="8">
@@ -11291,8 +11301,8 @@
       <c r="L40" s="11"/>
       <c r="M40" s="11"/>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B41" s="157"/>
+    <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="182"/>
       <c r="C41" s="47" t="s">
         <v>27</v>
       </c>
@@ -11329,7 +11339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>1</v>
       </c>
@@ -11368,7 +11378,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>1</v>
       </c>
@@ -11411,8 +11421,8 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="44" spans="1:15" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="157" t="s">
+    <row r="44" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B44" s="182" t="s">
         <v>33</v>
       </c>
       <c r="C44" s="47" t="e" vm="8">
@@ -11443,8 +11453,8 @@
       <c r="L44" s="11"/>
       <c r="M44" s="11"/>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B45" s="157"/>
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B45" s="182"/>
       <c r="C45" s="47" t="s">
         <v>27</v>
       </c>
@@ -11481,11 +11491,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>1</v>
       </c>
-      <c r="B46" s="135" t="s">
+      <c r="B46" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C46" s="13" t="s">
@@ -11518,11 +11528,11 @@
       <c r="L46" s="83"/>
       <c r="M46" s="11"/>
     </row>
-    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>1</v>
       </c>
-      <c r="B47" s="136"/>
+      <c r="B47" s="137"/>
       <c r="C47" s="13" t="s">
         <v>37</v>
       </c>
@@ -11561,8 +11571,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B48" s="143" t="s">
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C48" s="63" t="s">
@@ -11593,8 +11603,8 @@
       <c r="L48" s="83"/>
       <c r="M48" s="11"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B49" s="143"/>
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B49" s="151"/>
       <c r="C49" s="63" t="s">
         <v>37</v>
       </c>
@@ -11632,8 +11642,8 @@
         <v>39</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="168" t="s">
+    <row r="50" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B50" s="200" t="s">
         <v>40</v>
       </c>
       <c r="C50" s="63" t="e" vm="11">
@@ -11664,8 +11674,8 @@
       <c r="L50" s="83"/>
       <c r="M50" s="11"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B51" s="169"/>
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B51" s="201"/>
       <c r="C51" s="63" t="s">
         <v>37</v>
       </c>
@@ -11700,8 +11710,8 @@
       <c r="L51" s="83"/>
       <c r="M51" s="11"/>
     </row>
-    <row r="52" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="168" t="s">
+    <row r="52" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="200" t="s">
         <v>35</v>
       </c>
       <c r="C52" s="63" t="e" vm="11">
@@ -11734,8 +11744,8 @@
       <c r="L52" s="83"/>
       <c r="M52" s="123"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B53" s="169"/>
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="201"/>
       <c r="C53" s="63" t="s">
         <v>37</v>
       </c>
@@ -11773,8 +11783,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B54" s="168" t="s">
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="200" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="63" t="e" vm="11">
@@ -11805,8 +11815,8 @@
       <c r="L54" s="83"/>
       <c r="M54" s="11"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B55" s="169"/>
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="201"/>
       <c r="C55" s="63" t="s">
         <v>37</v>
       </c>
@@ -11844,11 +11854,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>1</v>
       </c>
-      <c r="B56" s="135" t="s">
+      <c r="B56" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C56" s="20" t="e" vm="11">
@@ -11879,11 +11889,11 @@
       <c r="L56" s="83"/>
       <c r="M56" s="11"/>
     </row>
-    <row r="57" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
-      <c r="B57" s="136"/>
+      <c r="B57" s="137"/>
       <c r="C57" s="20" t="s">
         <v>37</v>
       </c>
@@ -11922,11 +11932,11 @@
         <v>38</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>1</v>
       </c>
-      <c r="B58" s="160" t="s">
+      <c r="B58" s="199" t="s">
         <v>44</v>
       </c>
       <c r="C58" s="16" t="e" vm="12">
@@ -11961,11 +11971,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>1</v>
       </c>
-      <c r="B59" s="160"/>
+      <c r="B59" s="199"/>
       <c r="C59" s="16" t="s">
         <v>45</v>
       </c>
@@ -12005,8 +12015,8 @@
         <v>-5589.75</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B60" s="170" t="s">
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B60" s="192" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="63" t="e" vm="11">
@@ -12037,8 +12047,8 @@
       <c r="L60" s="83"/>
       <c r="M60" s="11"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B61" s="170"/>
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B61" s="192"/>
       <c r="C61" s="63" t="s">
         <v>37</v>
       </c>
@@ -12076,8 +12086,8 @@
         <v>46</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B62" s="161" t="s">
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B62" s="188" t="s">
         <v>32</v>
       </c>
       <c r="C62" s="63" t="e" vm="12">
@@ -12112,8 +12122,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B63" s="162"/>
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B63" s="189"/>
       <c r="C63" s="79" t="s">
         <v>45</v>
       </c>
@@ -12155,8 +12165,8 @@
         <v>-738.09999999999991</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B64" s="161" t="s">
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B64" s="188" t="s">
         <v>32</v>
       </c>
       <c r="C64" s="63" t="e" vm="12">
@@ -12191,8 +12201,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B65" s="162"/>
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B65" s="189"/>
       <c r="C65" s="79" t="s">
         <v>45</v>
       </c>
@@ -12234,8 +12244,8 @@
         <v>-837</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B66" s="163" t="s">
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="193" t="s">
         <v>26</v>
       </c>
       <c r="C66" s="63" t="e" vm="12">
@@ -12266,8 +12276,8 @@
       <c r="L66" s="83"/>
       <c r="M66" s="11"/>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B67" s="163"/>
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B67" s="193"/>
       <c r="C67" s="79" t="s">
         <v>45</v>
       </c>
@@ -12305,8 +12315,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B68" s="163" t="s">
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B68" s="193" t="s">
         <v>26</v>
       </c>
       <c r="C68" s="63" t="e" vm="12">
@@ -12337,8 +12347,8 @@
       <c r="L68" s="83"/>
       <c r="M68" s="11"/>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B69" s="163"/>
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B69" s="193"/>
       <c r="C69" s="79" t="s">
         <v>45</v>
       </c>
@@ -12376,8 +12386,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B70" s="161" t="s">
+    <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="188" t="s">
         <v>32</v>
       </c>
       <c r="C70" s="63" t="e" vm="12">
@@ -12408,8 +12418,8 @@
       <c r="L70" s="83"/>
       <c r="M70" s="11"/>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B71" s="162"/>
+    <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B71" s="189"/>
       <c r="C71" s="79" t="s">
         <v>45</v>
       </c>
@@ -12447,8 +12457,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B72" s="161" t="s">
+    <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B72" s="188" t="s">
         <v>32</v>
       </c>
       <c r="C72" s="63" t="e" vm="12">
@@ -12479,8 +12489,8 @@
       <c r="L72" s="83"/>
       <c r="M72" s="11"/>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B73" s="162"/>
+    <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B73" s="189"/>
       <c r="C73" s="79" t="s">
         <v>45</v>
       </c>
@@ -12518,7 +12528,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" s="164" t="s">
         <v>47</v>
       </c>
@@ -12550,7 +12560,7 @@
       <c r="L74" s="83"/>
       <c r="M74" s="11"/>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" s="165"/>
       <c r="C75" s="79" t="s">
         <v>45</v>
@@ -12589,7 +12599,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>1</v>
       </c>
@@ -12627,7 +12637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>1</v>
       </c>
@@ -12671,7 +12681,7 @@
         <v>-2177.86</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>1</v>
       </c>
@@ -12705,7 +12715,7 @@
       <c r="L78" s="83"/>
       <c r="M78" s="11"/>
     </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>1</v>
       </c>
@@ -12745,7 +12755,7 @@
       <c r="L79" s="83"/>
       <c r="M79" s="11"/>
     </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>1</v>
       </c>
@@ -12779,7 +12789,7 @@
       <c r="L80" s="83"/>
       <c r="M80" s="11"/>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>1</v>
       </c>
@@ -12819,7 +12829,7 @@
       <c r="L81" s="83"/>
       <c r="M81" s="11"/>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>1</v>
       </c>
@@ -12853,7 +12863,7 @@
       <c r="L82" s="83"/>
       <c r="M82" s="11"/>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>1</v>
       </c>
@@ -12893,7 +12903,7 @@
       <c r="L83" s="83"/>
       <c r="M83" s="11"/>
     </row>
-    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>1</v>
       </c>
@@ -12927,7 +12937,7 @@
       <c r="L84" s="83"/>
       <c r="M84" s="11"/>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>1</v>
       </c>
@@ -12967,7 +12977,7 @@
       <c r="L85" s="83"/>
       <c r="M85" s="11"/>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>1</v>
       </c>
@@ -13001,7 +13011,7 @@
       <c r="L86" s="83"/>
       <c r="M86" s="11"/>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>1</v>
       </c>
@@ -13041,7 +13051,7 @@
       <c r="L87" s="83"/>
       <c r="M87" s="11"/>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>1</v>
       </c>
@@ -13075,7 +13085,7 @@
       <c r="L88" s="83"/>
       <c r="M88" s="11"/>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>1</v>
       </c>
@@ -13115,8 +13125,8 @@
       <c r="L89" s="83"/>
       <c r="M89" s="11"/>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B90" s="166" t="s">
+    <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B90" s="178" t="s">
         <v>47</v>
       </c>
       <c r="C90" s="63" t="e" vm="13">
@@ -13151,8 +13161,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B91" s="167"/>
+    <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B91" s="179"/>
       <c r="C91" s="79" t="s">
         <v>50</v>
       </c>
@@ -13187,8 +13197,8 @@
       <c r="L91" s="83"/>
       <c r="M91" s="11"/>
     </row>
-    <row r="92" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="166" t="s">
+    <row r="92" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="178" t="s">
         <v>47</v>
       </c>
       <c r="C92" s="52" t="e" vm="14">
@@ -13223,8 +13233,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B93" s="167"/>
+    <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B93" s="179"/>
       <c r="C93" s="78" t="s">
         <v>51</v>
       </c>
@@ -13259,8 +13269,8 @@
       <c r="L93" s="83"/>
       <c r="M93" s="11"/>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B94" s="166" t="s">
+    <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B94" s="178" t="s">
         <v>47</v>
       </c>
       <c r="C94" s="52" t="e" vm="14">
@@ -13295,8 +13305,8 @@
         <v>49</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B95" s="167"/>
+    <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B95" s="179"/>
       <c r="C95" s="78" t="s">
         <v>51</v>
       </c>
@@ -13331,7 +13341,7 @@
       <c r="L95" s="83"/>
       <c r="M95" s="11"/>
     </row>
-    <row r="96" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B96" s="61" t="s">
         <v>4</v>
       </c>
@@ -13368,7 +13378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B97" s="97"/>
       <c r="C97" s="79" t="s">
         <v>51</v>
@@ -13411,7 +13421,7 @@
         <v>-5200</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B98" s="61" t="s">
         <v>4</v>
       </c>
@@ -13444,7 +13454,7 @@
       <c r="L98" s="83"/>
       <c r="M98" s="11"/>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B99" s="97"/>
       <c r="C99" s="79" t="s">
         <v>51</v>
@@ -13483,7 +13493,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="C100" s="63" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -13513,7 +13523,7 @@
       <c r="L100" s="83"/>
       <c r="M100" s="11"/>
     </row>
-    <row r="101" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B101" s="61" t="s">
         <v>52</v>
       </c>
@@ -13554,8 +13564,8 @@
         <v>48</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B102" s="143" t="s">
+    <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B102" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C102" s="63" t="e" vm="15">
@@ -13591,8 +13601,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B103" s="143"/>
+    <row r="103" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B103" s="151"/>
       <c r="C103" s="79" t="s">
         <v>53</v>
       </c>
@@ -13633,11 +13643,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>1</v>
       </c>
-      <c r="B104" s="143" t="s">
+      <c r="B104" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C104" s="13" t="e" vm="16">
@@ -13673,11 +13683,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>1</v>
       </c>
-      <c r="B105" s="143"/>
+      <c r="B105" s="151"/>
       <c r="C105" s="15" t="s">
         <v>56</v>
       </c>
@@ -13717,7 +13727,7 @@
         <v>-2220.84</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>1</v>
       </c>
@@ -13757,7 +13767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>1</v>
       </c>
@@ -13801,7 +13811,7 @@
         <v>-3369.94</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>1</v>
       </c>
@@ -13837,7 +13847,7 @@
       <c r="L108" s="83"/>
       <c r="M108" s="11"/>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>1</v>
       </c>
@@ -13877,7 +13887,7 @@
       <c r="L109" s="83"/>
       <c r="M109" s="11"/>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>1</v>
       </c>
@@ -13913,7 +13923,7 @@
       <c r="L110" s="83"/>
       <c r="M110" s="11"/>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>1</v>
       </c>
@@ -13953,7 +13963,7 @@
       <c r="L111" s="83"/>
       <c r="M111" s="11"/>
     </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>1</v>
       </c>
@@ -13991,7 +14001,7 @@
       <c r="L112" s="83"/>
       <c r="M112" s="11"/>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>1</v>
       </c>
@@ -14031,7 +14041,7 @@
       <c r="L113" s="83"/>
       <c r="M113" s="11"/>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>1</v>
       </c>
@@ -14067,7 +14077,7 @@
       <c r="L114" s="83"/>
       <c r="M114" s="11"/>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>1</v>
       </c>
@@ -14107,8 +14117,8 @@
       <c r="L115" s="83"/>
       <c r="M115" s="11"/>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B116" s="175" t="s">
+    <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B116" s="170" t="s">
         <v>32</v>
       </c>
       <c r="C116" s="52" t="e" vm="18">
@@ -14140,8 +14150,8 @@
       <c r="L116" s="83"/>
       <c r="M116" s="11"/>
     </row>
-    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B117" s="176"/>
+    <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B117" s="171"/>
       <c r="C117" s="78" t="s">
         <v>59</v>
       </c>
@@ -14179,7 +14189,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:15" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B118" s="164" t="s">
         <v>60</v>
       </c>
@@ -14216,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B119" s="165"/>
       <c r="C119" s="78" t="s">
         <v>59</v>
@@ -14259,8 +14269,8 @@
         <v>-1592.5</v>
       </c>
     </row>
-    <row r="120" spans="1:15" ht="29.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="177" t="s">
+    <row r="120" spans="1:15" ht="29.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B120" s="196" t="s">
         <v>52</v>
       </c>
       <c r="C120" s="52" t="e" vm="18">
@@ -14292,8 +14302,8 @@
       <c r="L120" s="83"/>
       <c r="M120" s="11"/>
     </row>
-    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B121" s="178"/>
+    <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B121" s="197"/>
       <c r="C121" s="78" t="s">
         <v>59</v>
       </c>
@@ -14331,7 +14341,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>1</v>
       </c>
@@ -14365,7 +14375,7 @@
       <c r="L122" s="83"/>
       <c r="M122" s="124"/>
     </row>
-    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>1</v>
       </c>
@@ -14405,7 +14415,7 @@
       <c r="L123" s="83"/>
       <c r="M123" s="124"/>
     </row>
-    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>1</v>
       </c>
@@ -14439,7 +14449,7 @@
       <c r="L124" s="83"/>
       <c r="M124" s="124"/>
     </row>
-    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>1</v>
       </c>
@@ -14479,7 +14489,7 @@
       <c r="L125" s="83"/>
       <c r="M125" s="124"/>
     </row>
-    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>1</v>
       </c>
@@ -14516,7 +14526,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>1</v>
       </c>
@@ -14559,7 +14569,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>1</v>
       </c>
@@ -14596,7 +14606,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>1</v>
       </c>
@@ -14639,8 +14649,8 @@
         <v>62</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="29.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="177" t="s">
+    <row r="130" spans="1:16" ht="29.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B130" s="196" t="s">
         <v>52</v>
       </c>
       <c r="C130" s="52" t="e" vm="19">
@@ -14673,8 +14683,8 @@
       <c r="M130" s="11"/>
       <c r="N130" s="24"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B131" s="178"/>
+    <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B131" s="197"/>
       <c r="C131" s="78" t="s">
         <v>61</v>
       </c>
@@ -14715,7 +14725,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>1</v>
       </c>
@@ -14749,7 +14759,7 @@
       <c r="L132" s="83"/>
       <c r="M132" s="11"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>1</v>
       </c>
@@ -14788,7 +14798,7 @@
       <c r="L133" s="83"/>
       <c r="M133" s="11"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>1</v>
       </c>
@@ -14822,7 +14832,7 @@
       <c r="L134" s="83"/>
       <c r="M134" s="11"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>1</v>
       </c>
@@ -14861,8 +14871,8 @@
       <c r="L135" s="83"/>
       <c r="M135" s="11"/>
     </row>
-    <row r="136" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="170" t="s">
+    <row r="136" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B136" s="192" t="s">
         <v>66</v>
       </c>
       <c r="C136" s="43" t="e" vm="11">
@@ -14896,8 +14906,8 @@
       <c r="L136" s="83"/>
       <c r="M136" s="12"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B137" s="170"/>
+    <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B137" s="192"/>
       <c r="C137" s="80" t="s">
         <v>37</v>
       </c>
@@ -14941,8 +14951,8 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B138" s="177" t="s">
+    <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B138" s="196" t="s">
         <v>52</v>
       </c>
       <c r="C138" s="43" t="e" vm="22">
@@ -14974,8 +14984,8 @@
       <c r="L138" s="83"/>
       <c r="M138" s="12"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B139" s="178"/>
+    <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B139" s="197"/>
       <c r="C139" s="43" t="s">
         <v>69</v>
       </c>
@@ -15019,8 +15029,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B140" s="177" t="s">
+    <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B140" s="196" t="s">
         <v>52</v>
       </c>
       <c r="C140" s="43" t="e" vm="22">
@@ -15052,8 +15062,8 @@
       <c r="L140" s="83"/>
       <c r="M140" s="12"/>
     </row>
-    <row r="141" spans="1:16" ht="43.2" x14ac:dyDescent="0.35">
-      <c r="B141" s="178"/>
+    <row r="141" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B141" s="197"/>
       <c r="C141" s="43" t="s">
         <v>69</v>
       </c>
@@ -15097,7 +15107,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="B142" s="76" t="s">
         <v>74</v>
       </c>
@@ -15130,7 +15140,7 @@
       <c r="L142" s="83"/>
       <c r="M142" s="12"/>
     </row>
-    <row r="143" spans="1:16" ht="43.2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="B143" s="97"/>
       <c r="C143" s="43" t="s">
         <v>69</v>
@@ -15172,8 +15182,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B144" s="143" t="s">
+    <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B144" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C144" s="63" t="e" vm="22">
@@ -15205,8 +15215,8 @@
       <c r="L144" s="83"/>
       <c r="M144" s="11"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B145" s="143"/>
+    <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B145" s="151"/>
       <c r="C145" s="63" t="s">
         <v>69</v>
       </c>
@@ -15248,8 +15258,8 @@
         <v>77</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B146" s="143" t="s">
+    <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B146" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C146" s="63" t="e" vm="22">
@@ -15281,8 +15291,8 @@
       <c r="L146" s="83"/>
       <c r="M146" s="11"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B147" s="143"/>
+    <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B147" s="151"/>
       <c r="C147" s="63" t="s">
         <v>69</v>
       </c>
@@ -15323,7 +15333,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>1</v>
       </c>
@@ -15359,7 +15369,7 @@
       <c r="L148" s="83"/>
       <c r="M148" s="11"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>1</v>
       </c>
@@ -15401,7 +15411,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B150" s="97" t="s">
         <v>79</v>
       </c>
@@ -15437,7 +15447,7 @@
         <v>867.4</v>
       </c>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B151" s="97"/>
       <c r="C151" s="63" t="s">
         <v>81</v>
@@ -15479,7 +15489,7 @@
         <v>867.4</v>
       </c>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>1</v>
       </c>
@@ -15515,7 +15525,7 @@
         <v>868.92</v>
       </c>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>1</v>
       </c>
@@ -15557,11 +15567,11 @@
         <v>2603.7199999999998</v>
       </c>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>1</v>
       </c>
-      <c r="B154" s="174" t="s">
+      <c r="B154" s="155" t="s">
         <v>86</v>
       </c>
       <c r="C154" s="13" t="e" vm="23">
@@ -15593,11 +15603,11 @@
       <c r="L154" s="83"/>
       <c r="M154" s="11"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>1</v>
       </c>
-      <c r="B155" s="174"/>
+      <c r="B155" s="155"/>
       <c r="C155" s="15" t="s">
         <v>87</v>
       </c>
@@ -15633,7 +15643,7 @@
       <c r="L155" s="83"/>
       <c r="M155" s="11"/>
     </row>
-    <row r="156" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>1</v>
       </c>
@@ -15673,7 +15683,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>1</v>
       </c>
@@ -15713,11 +15723,11 @@
       <c r="L157" s="83"/>
       <c r="M157" s="11"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>1</v>
       </c>
-      <c r="B158" s="172" t="s">
+      <c r="B158" s="194" t="s">
         <v>89</v>
       </c>
       <c r="C158" s="16" t="e" vm="22">
@@ -15749,11 +15759,11 @@
       <c r="L158" s="83"/>
       <c r="M158" s="11"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>1</v>
       </c>
-      <c r="B159" s="173"/>
+      <c r="B159" s="195"/>
       <c r="C159" s="23" t="s">
         <v>69</v>
       </c>
@@ -15789,12 +15799,12 @@
       <c r="L159" s="83"/>
       <c r="M159" s="11"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>1</v>
       </c>
-      <c r="B160" s="146" t="s">
-        <v>381</v>
+      <c r="B160" s="158" t="s">
+        <v>380</v>
       </c>
       <c r="C160" s="13" t="e" vm="22">
         <v>#VALUE!</v>
@@ -15828,11 +15838,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>1</v>
       </c>
-      <c r="B161" s="147"/>
+      <c r="B161" s="159"/>
       <c r="C161" s="15" t="s">
         <v>69</v>
       </c>
@@ -15868,8 +15878,8 @@
       <c r="L161" s="83"/>
       <c r="M161" s="11"/>
     </row>
-    <row r="162" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B162" s="171" t="s">
+    <row r="162" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B162" s="180" t="s">
         <v>92</v>
       </c>
       <c r="C162" s="63" t="e" vm="22">
@@ -15904,8 +15914,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="32.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="171"/>
+    <row r="163" spans="1:15" ht="32.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B163" s="180"/>
       <c r="C163" s="63" t="s">
         <v>69</v>
       </c>
@@ -15943,12 +15953,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>1</v>
       </c>
-      <c r="B164" s="141" t="s">
-        <v>382</v>
+      <c r="B164" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C164" s="16" t="e" vm="22">
         <v>#VALUE!</v>
@@ -15982,11 +15992,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>1</v>
       </c>
-      <c r="B165" s="142"/>
+      <c r="B165" s="148"/>
       <c r="C165" s="23" t="s">
         <v>69</v>
       </c>
@@ -16022,8 +16032,8 @@
       <c r="L165" s="83"/>
       <c r="M165" s="11"/>
     </row>
-    <row r="166" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B166" s="171" t="s">
+    <row r="166" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B166" s="180" t="s">
         <v>92</v>
       </c>
       <c r="C166" s="63" t="e" vm="22">
@@ -16058,8 +16068,8 @@
         <v>95</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B167" s="171"/>
+    <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B167" s="180"/>
       <c r="C167" s="63" t="s">
         <v>69</v>
       </c>
@@ -16100,8 +16110,8 @@
         <v>72</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B168" s="143" t="s">
+    <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B168" s="151" t="s">
         <v>44</v>
       </c>
       <c r="C168" s="63" t="e" vm="22">
@@ -16139,8 +16149,8 @@
         <v>97</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B169" s="143"/>
+    <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B169" s="151"/>
       <c r="C169" s="63" t="s">
         <v>69</v>
       </c>
@@ -16175,7 +16185,7 @@
       <c r="L169" s="83"/>
       <c r="M169" s="123"/>
     </row>
-    <row r="170" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>1</v>
       </c>
@@ -16211,7 +16221,7 @@
       <c r="L170" s="83"/>
       <c r="M170" s="11"/>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>1</v>
       </c>
@@ -16251,7 +16261,7 @@
       <c r="L171" s="83"/>
       <c r="M171" s="11"/>
     </row>
-    <row r="172" spans="1:15" s="60" customFormat="1" ht="43.2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:15" s="60" customFormat="1" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5"/>
       <c r="B172" s="55" t="s">
         <v>17</v>
@@ -16291,7 +16301,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="173" spans="1:15" s="60" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:15" s="60" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5"/>
       <c r="B173" s="61"/>
       <c r="C173" s="62" t="s">
@@ -16328,8 +16338,8 @@
       <c r="L173" s="83"/>
       <c r="M173" s="125"/>
     </row>
-    <row r="174" spans="1:15" ht="32.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="183" t="s">
+    <row r="174" spans="1:15" ht="32.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B174" s="153" t="s">
         <v>102</v>
       </c>
       <c r="C174" s="63" t="e" vm="11">
@@ -16363,8 +16373,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B175" s="184"/>
+    <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B175" s="154"/>
       <c r="C175" s="63" t="s">
         <v>37</v>
       </c>
@@ -16400,8 +16410,8 @@
       <c r="L175" s="83"/>
       <c r="M175" s="11"/>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B176" s="182" t="s">
+    <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B176" s="190" t="s">
         <v>104</v>
       </c>
       <c r="C176" s="43" t="e" vm="26">
@@ -16439,8 +16449,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B177" s="182"/>
+    <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B177" s="190"/>
       <c r="C177" s="43" t="s">
         <v>107</v>
       </c>
@@ -16475,8 +16485,8 @@
       <c r="L177" s="83"/>
       <c r="M177" s="123"/>
     </row>
-    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B178" s="185" t="s">
+    <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B178" s="191" t="s">
         <v>108</v>
       </c>
       <c r="C178" s="39" t="e" vm="26">
@@ -16514,8 +16524,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B179" s="185"/>
+    <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B179" s="191"/>
       <c r="C179" s="39" t="s">
         <v>107</v>
       </c>
@@ -16550,8 +16560,8 @@
       <c r="L179" s="83"/>
       <c r="M179" s="125"/>
     </row>
-    <row r="180" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B180" s="179" t="s">
+    <row r="180" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B180" s="187" t="s">
         <v>104</v>
       </c>
       <c r="C180" s="47" t="s">
@@ -16585,8 +16595,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B181" s="179"/>
+    <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B181" s="187"/>
       <c r="C181" s="47" t="s">
         <v>111</v>
       </c>
@@ -16621,8 +16631,8 @@
       <c r="L181" s="83"/>
       <c r="M181" s="123"/>
     </row>
-    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B182" s="190" t="s">
+    <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B182" s="184" t="s">
         <v>112</v>
       </c>
       <c r="C182" s="49" t="e" vm="27">
@@ -16660,8 +16670,8 @@
         <v>106</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B183" s="190"/>
+    <row r="183" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B183" s="184"/>
       <c r="C183" s="49" t="s">
         <v>114</v>
       </c>
@@ -16696,8 +16706,8 @@
       <c r="L183" s="83"/>
       <c r="M183" s="125"/>
     </row>
-    <row r="184" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B184" s="138" t="s">
+    <row r="184" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B184" s="185" t="s">
         <v>40</v>
       </c>
       <c r="C184" s="63" t="e" vm="11">
@@ -16731,8 +16741,8 @@
         <v>103</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B185" s="191"/>
+    <row r="185" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B185" s="186"/>
       <c r="C185" s="63" t="s">
         <v>37</v>
       </c>
@@ -16770,8 +16780,8 @@
         <v>115</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="138" t="s">
+    <row r="186" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B186" s="185" t="s">
         <v>40</v>
       </c>
       <c r="C186" s="63" t="e" vm="11">
@@ -16805,8 +16815,8 @@
         <v>116</v>
       </c>
     </row>
-    <row r="187" spans="1:15" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="191"/>
+    <row r="187" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B187" s="186"/>
       <c r="C187" s="63" t="s">
         <v>37</v>
       </c>
@@ -16844,12 +16854,12 @@
         <v>115</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="11.3" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" ht="11.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>1</v>
       </c>
-      <c r="B188" s="135" t="s">
-        <v>386</v>
+      <c r="B188" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C188" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -16882,11 +16892,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" ht="40.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>1</v>
       </c>
-      <c r="B189" s="136"/>
+      <c r="B189" s="137"/>
       <c r="C189" s="16" t="s">
         <v>37</v>
       </c>
@@ -16922,12 +16932,12 @@
       <c r="L189" s="83"/>
       <c r="M189" s="11"/>
     </row>
-    <row r="190" spans="1:15" ht="13.55" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" ht="13.55" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>1</v>
       </c>
-      <c r="B190" s="141" t="s">
-        <v>382</v>
+      <c r="B190" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C190" s="20" t="e" vm="11">
         <v>#VALUE!</v>
@@ -16960,11 +16970,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" ht="36.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>1</v>
       </c>
-      <c r="B191" s="142"/>
+      <c r="B191" s="148"/>
       <c r="C191" s="20" t="s">
         <v>37</v>
       </c>
@@ -17000,8 +17010,8 @@
       <c r="L191" s="83"/>
       <c r="M191" s="11"/>
     </row>
-    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B192" s="143" t="s">
+    <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B192" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C192" s="63" t="e" vm="11">
@@ -17032,8 +17042,8 @@
       <c r="L192" s="83"/>
       <c r="M192" s="11"/>
     </row>
-    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B193" s="143"/>
+    <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B193" s="151"/>
       <c r="C193" s="63" t="s">
         <v>37</v>
       </c>
@@ -17071,8 +17081,8 @@
         <v>43</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B194" s="154" t="s">
+    <row r="194" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B194" s="160" t="s">
         <v>108</v>
       </c>
       <c r="C194" s="47" t="e" vm="28">
@@ -17103,8 +17113,8 @@
       <c r="L194" s="83"/>
       <c r="M194" s="11"/>
     </row>
-    <row r="195" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B195" s="154"/>
+    <row r="195" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B195" s="160"/>
       <c r="C195" s="47" t="s">
         <v>118</v>
       </c>
@@ -17139,14 +17149,14 @@
       <c r="L195" s="83"/>
       <c r="M195" s="11"/>
       <c r="N195" s="5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O195" s="6" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="196" spans="1:15" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="159" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="196" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B196" s="181" t="s">
         <v>29</v>
       </c>
       <c r="C196" s="63" t="e" vm="11">
@@ -17180,8 +17190,8 @@
         <v>119</v>
       </c>
     </row>
-    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B197" s="159"/>
+    <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B197" s="181"/>
       <c r="C197" s="63" t="s">
         <v>37</v>
       </c>
@@ -17216,8 +17226,8 @@
       <c r="L197" s="83"/>
       <c r="M197" s="123"/>
     </row>
-    <row r="198" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B198" s="159" t="s">
+    <row r="198" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B198" s="181" t="s">
         <v>104</v>
       </c>
       <c r="C198" s="63" t="e" vm="29">
@@ -17252,8 +17262,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B199" s="159"/>
+    <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B199" s="181"/>
       <c r="C199" s="63" t="s">
         <v>121</v>
       </c>
@@ -17289,8 +17299,8 @@
       <c r="M199" s="123"/>
       <c r="N199" s="53"/>
     </row>
-    <row r="200" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="159" t="s">
+    <row r="200" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B200" s="181" t="s">
         <v>108</v>
       </c>
       <c r="C200" s="63" t="e" vm="29">
@@ -17325,8 +17335,8 @@
         <v>120</v>
       </c>
     </row>
-    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B201" s="159"/>
+    <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B201" s="181"/>
       <c r="C201" s="63" t="s">
         <v>121</v>
       </c>
@@ -17361,8 +17371,8 @@
       <c r="L201" s="83"/>
       <c r="M201" s="123"/>
     </row>
-    <row r="202" spans="1:15" ht="11.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="158" t="s">
+    <row r="202" spans="1:15" ht="11.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B202" s="198" t="s">
         <v>29</v>
       </c>
       <c r="C202" s="47" t="e" vm="30">
@@ -17394,8 +17404,8 @@
       <c r="L202" s="83"/>
       <c r="M202" s="11"/>
     </row>
-    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B203" s="158"/>
+    <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B203" s="198"/>
       <c r="C203" s="47" t="s">
         <v>123</v>
       </c>
@@ -17433,12 +17443,12 @@
         <v>122</v>
       </c>
       <c r="O203" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="204" spans="1:15" s="53" customFormat="1" ht="43.2" x14ac:dyDescent="0.35">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="204" spans="1:15" s="53" customFormat="1" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5"/>
-      <c r="B204" s="159" t="s">
+      <c r="B204" s="181" t="s">
         <v>108</v>
       </c>
       <c r="C204" s="63" t="e" vm="22">
@@ -17470,9 +17480,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="205" spans="1:15" s="53" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:15" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5"/>
-      <c r="B205" s="159"/>
+      <c r="B205" s="181"/>
       <c r="C205" s="63" t="s">
         <v>125</v>
       </c>
@@ -17507,12 +17517,12 @@
       <c r="L205" s="83"/>
       <c r="M205" s="123"/>
     </row>
-    <row r="206" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>1</v>
       </c>
-      <c r="B206" s="141" t="s">
-        <v>382</v>
+      <c r="B206" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C206" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -17542,11 +17552,11 @@
       <c r="L206" s="83"/>
       <c r="M206" s="11"/>
     </row>
-    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>1</v>
       </c>
-      <c r="B207" s="142"/>
+      <c r="B207" s="148"/>
       <c r="C207" s="16" t="s">
         <v>37</v>
       </c>
@@ -17582,12 +17592,12 @@
       <c r="L207" s="83"/>
       <c r="M207" s="11"/>
     </row>
-    <row r="208" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>1</v>
       </c>
-      <c r="B208" s="135" t="s">
-        <v>386</v>
+      <c r="B208" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C208" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -17617,11 +17627,11 @@
       <c r="L208" s="83"/>
       <c r="M208" s="11"/>
     </row>
-    <row r="209" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>1</v>
       </c>
-      <c r="B209" s="136"/>
+      <c r="B209" s="137"/>
       <c r="C209" s="13" t="s">
         <v>37</v>
       </c>
@@ -17660,8 +17670,8 @@
         <v>38</v>
       </c>
     </row>
-    <row r="210" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B210" s="156" t="s">
+    <row r="210" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B210" s="168" t="s">
         <v>33</v>
       </c>
       <c r="C210" s="52" t="e" vm="11">
@@ -17692,8 +17702,8 @@
       <c r="L210" s="83"/>
       <c r="M210" s="11"/>
     </row>
-    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B211" s="180"/>
+    <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B211" s="169"/>
       <c r="C211" s="52" t="s">
         <v>37</v>
       </c>
@@ -17734,8 +17744,8 @@
         <v>127</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B212" s="181" t="s">
+    <row r="212" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B212" s="161" t="s">
         <v>17</v>
       </c>
       <c r="C212" s="52" t="e" vm="25">
@@ -17770,8 +17780,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B213" s="181"/>
+    <row r="213" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B213" s="161"/>
       <c r="C213" s="52" t="s">
         <v>101</v>
       </c>
@@ -17810,8 +17820,8 @@
         <v>128</v>
       </c>
     </row>
-    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B214" s="161" t="s">
+    <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B214" s="188" t="s">
         <v>32</v>
       </c>
       <c r="C214" s="52" t="e" vm="25">
@@ -17845,8 +17855,8 @@
       <c r="L214" s="83"/>
       <c r="M214" s="11"/>
     </row>
-    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B215" s="162"/>
+    <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B215" s="189"/>
       <c r="C215" s="52" t="s">
         <v>101</v>
       </c>
@@ -17884,8 +17894,8 @@
         <v>129</v>
       </c>
     </row>
-    <row r="216" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B216" s="181" t="s">
+    <row r="216" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B216" s="161" t="s">
         <v>29</v>
       </c>
       <c r="C216" s="52" t="e" vm="25">
@@ -17923,8 +17933,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B217" s="181"/>
+    <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B217" s="161"/>
       <c r="C217" s="52" t="s">
         <v>101</v>
       </c>
@@ -17959,8 +17969,8 @@
       <c r="L217" s="83"/>
       <c r="M217" s="126"/>
     </row>
-    <row r="218" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B218" s="181" t="s">
+    <row r="218" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B218" s="161" t="s">
         <v>29</v>
       </c>
       <c r="C218" s="52" t="e" vm="25">
@@ -17998,8 +18008,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B219" s="181"/>
+    <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B219" s="161"/>
       <c r="C219" s="52" t="s">
         <v>101</v>
       </c>
@@ -18034,8 +18044,8 @@
       <c r="L219" s="83"/>
       <c r="M219" s="126"/>
     </row>
-    <row r="220" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B220" s="181" t="s">
+    <row r="220" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B220" s="161" t="s">
         <v>29</v>
       </c>
       <c r="C220" s="52" t="e" vm="25">
@@ -18073,8 +18083,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B221" s="181"/>
+    <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B221" s="161"/>
       <c r="C221" s="52" t="s">
         <v>101</v>
       </c>
@@ -18109,9 +18119,9 @@
       <c r="L221" s="83"/>
       <c r="M221" s="126"/>
     </row>
-    <row r="222" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B222" s="181" t="s">
-        <v>396</v>
+    <row r="222" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B222" s="161" t="s">
+        <v>395</v>
       </c>
       <c r="C222" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -18148,8 +18158,8 @@
         <v>131</v>
       </c>
     </row>
-    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B223" s="181"/>
+    <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B223" s="161"/>
       <c r="C223" s="52" t="s">
         <v>101</v>
       </c>
@@ -18184,8 +18194,8 @@
       <c r="L223" s="83"/>
       <c r="M223" s="126"/>
     </row>
-    <row r="224" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B224" s="181" t="s">
+    <row r="224" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B224" s="161" t="s">
         <v>33</v>
       </c>
       <c r="C224" s="52" t="e" vm="25">
@@ -18223,8 +18233,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B225" s="181"/>
+    <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B225" s="161"/>
       <c r="C225" s="52" t="s">
         <v>101</v>
       </c>
@@ -18262,8 +18272,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="226" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B226" s="181" t="s">
+    <row r="226" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B226" s="161" t="s">
         <v>33</v>
       </c>
       <c r="C226" s="52" t="e" vm="25">
@@ -18301,8 +18311,8 @@
         <v>136</v>
       </c>
     </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B227" s="181"/>
+    <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B227" s="161"/>
       <c r="C227" s="52" t="s">
         <v>101</v>
       </c>
@@ -18340,8 +18350,8 @@
         <v>93</v>
       </c>
     </row>
-    <row r="228" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B228" s="186" t="s">
+    <row r="228" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B228" s="172" t="s">
         <v>33</v>
       </c>
       <c r="C228" s="52" t="e" vm="25">
@@ -18376,8 +18386,8 @@
         <v>138</v>
       </c>
     </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B229" s="187"/>
+    <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B229" s="173"/>
       <c r="C229" s="52" t="s">
         <v>101</v>
       </c>
@@ -18415,8 +18425,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B230" s="186" t="s">
+    <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B230" s="172" t="s">
         <v>33</v>
       </c>
       <c r="C230" s="52" t="e" vm="25">
@@ -18448,8 +18458,8 @@
       <c r="L230" s="83"/>
       <c r="M230" s="11"/>
     </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B231" s="187"/>
+    <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B231" s="173"/>
       <c r="C231" s="52" t="s">
         <v>101</v>
       </c>
@@ -18487,12 +18497,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="232" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>1</v>
       </c>
-      <c r="B232" s="141" t="s">
-        <v>382</v>
+      <c r="B232" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C232" s="81" t="e" vm="25">
         <v>#VALUE!</v>
@@ -18523,11 +18533,11 @@
       <c r="L232" s="83"/>
       <c r="M232" s="11"/>
     </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>1</v>
       </c>
-      <c r="B233" s="142"/>
+      <c r="B233" s="148"/>
       <c r="C233" s="81" t="s">
         <v>101</v>
       </c>
@@ -18566,10 +18576,10 @@
         <v>141</v>
       </c>
       <c r="P233" s="5" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B234" s="164" t="s">
         <v>142</v>
       </c>
@@ -18602,7 +18612,7 @@
       <c r="L234" s="83"/>
       <c r="M234" s="11"/>
     </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B235" s="165"/>
       <c r="C235" s="52" t="s">
         <v>101</v>
@@ -18644,9 +18654,9 @@
         <v>144</v>
       </c>
     </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B236" s="188" t="s">
-        <v>396</v>
+    <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B236" s="174" t="s">
+        <v>395</v>
       </c>
       <c r="C236" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -18677,8 +18687,8 @@
       <c r="L236" s="83"/>
       <c r="M236" s="11"/>
     </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B237" s="189"/>
+    <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B237" s="175"/>
       <c r="C237" s="52" t="s">
         <v>101</v>
       </c>
@@ -18719,7 +18729,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B238" s="139" t="s">
         <v>32</v>
       </c>
@@ -18752,7 +18762,7 @@
       <c r="L238" s="83"/>
       <c r="M238" s="11"/>
     </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B239" s="140"/>
       <c r="C239" s="63" t="s">
         <v>101</v>
@@ -18791,14 +18801,14 @@
         <v>146</v>
       </c>
       <c r="O239" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>1</v>
       </c>
-      <c r="B240" s="143" t="s">
+      <c r="B240" s="151" t="s">
         <v>147</v>
       </c>
       <c r="C240" s="20" t="e" vm="11">
@@ -18829,11 +18839,11 @@
       <c r="L240" s="83"/>
       <c r="M240" s="11"/>
     </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>1</v>
       </c>
-      <c r="B241" s="143"/>
+      <c r="B241" s="151"/>
       <c r="C241" s="20" t="s">
         <v>37</v>
       </c>
@@ -18869,8 +18879,8 @@
       <c r="L241" s="83"/>
       <c r="M241" s="11"/>
     </row>
-    <row r="242" spans="1:16" ht="29.3" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B242" s="157" t="s">
+    <row r="242" spans="1:16" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B242" s="182" t="s">
         <v>33</v>
       </c>
       <c r="C242" s="47" t="e" vm="8">
@@ -18901,8 +18911,8 @@
       <c r="L242" s="83"/>
       <c r="M242" s="11"/>
     </row>
-    <row r="243" spans="1:16" ht="51.05" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B243" s="157"/>
+    <row r="243" spans="1:16" ht="51.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B243" s="182"/>
       <c r="C243" s="47" t="s">
         <v>27</v>
       </c>
@@ -18939,12 +18949,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="244" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:16" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>1</v>
       </c>
-      <c r="B244" s="146" t="s">
-        <v>381</v>
+      <c r="B244" s="158" t="s">
+        <v>380</v>
       </c>
       <c r="C244" s="5" t="e" vm="31">
         <v>#VALUE!</v>
@@ -18975,11 +18985,11 @@
       <c r="L244" s="83"/>
       <c r="M244" s="11"/>
     </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>1</v>
       </c>
-      <c r="B245" s="147"/>
+      <c r="B245" s="159"/>
       <c r="C245" s="22" t="s">
         <v>148</v>
       </c>
@@ -19019,7 +19029,7 @@
       <c r="A246" s="5">
         <v>1</v>
       </c>
-      <c r="B246" s="192" t="s">
+      <c r="B246" s="183" t="s">
         <v>108</v>
       </c>
       <c r="C246" s="20" t="e" vm="32">
@@ -19051,17 +19061,17 @@
       <c r="L246" s="83"/>
       <c r="M246" s="11"/>
     </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" ht="15.4" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>1</v>
       </c>
-      <c r="B247" s="192"/>
-      <c r="C247" s="20" t="s">
-        <v>150</v>
+      <c r="B247" s="183"/>
+      <c r="C247" s="207" t="s">
+        <v>407</v>
       </c>
       <c r="D247" s="20" t="str">
         <f>C247</f>
-        <v>Manulife</v>
+        <v>MFC.TO</v>
       </c>
       <c r="E247" s="20">
         <f ca="1">E246</f>
@@ -19094,8 +19104,8 @@
         <v>149</v>
       </c>
     </row>
-    <row r="248" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B248" s="181" t="s">
+    <row r="248" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B248" s="161" t="s">
         <v>29</v>
       </c>
       <c r="C248" s="52" t="e" vm="22">
@@ -19127,11 +19137,11 @@
       <c r="L248" s="83"/>
       <c r="M248" s="11"/>
       <c r="N248" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B249" s="181"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B249" s="161"/>
       <c r="C249" s="52" t="s">
         <v>69</v>
       </c>
@@ -19166,9 +19176,9 @@
       <c r="L249" s="83"/>
       <c r="M249" s="11"/>
     </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B250" s="171" t="s">
-        <v>394</v>
+    <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B250" s="180" t="s">
+        <v>393</v>
       </c>
       <c r="C250" s="47" t="e" vm="33">
         <v>#VALUE!</v>
@@ -19199,19 +19209,19 @@
       <c r="L250" s="83"/>
       <c r="M250" s="11"/>
       <c r="N250" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="O250" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="P250" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B251" s="180"/>
+      <c r="C251" s="78" t="s">
         <v>152</v>
-      </c>
-      <c r="O250" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="P250" s="5" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B251" s="171"/>
-      <c r="C251" s="78" t="s">
-        <v>153</v>
       </c>
       <c r="D251" s="53" t="str">
         <f t="shared" ref="D251" si="126">C251</f>
@@ -19245,9 +19255,9 @@
       <c r="L251" s="83"/>
       <c r="M251" s="11"/>
     </row>
-    <row r="252" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B252" s="171" t="s">
-        <v>394</v>
+    <row r="252" spans="1:16" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B252" s="180" t="s">
+        <v>393</v>
       </c>
       <c r="C252" s="47" t="e" vm="33">
         <v>#VALUE!</v>
@@ -19278,10 +19288,10 @@
       <c r="L252" s="83"/>
       <c r="M252" s="11"/>
     </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B253" s="171"/>
+    <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B253" s="180"/>
       <c r="C253" s="78" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D253" s="53" t="str">
         <f t="shared" ref="D253" si="128">C253</f>
@@ -19315,14 +19325,14 @@
       <c r="L253" s="83"/>
       <c r="M253" s="11"/>
       <c r="N253" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O253" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B254" s="156" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B254" s="168" t="s">
         <v>66</v>
       </c>
       <c r="C254" s="98" t="e" vm="11">
@@ -19353,8 +19363,8 @@
       <c r="L254" s="83"/>
       <c r="M254" s="126"/>
     </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B255" s="180"/>
+    <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B255" s="169"/>
       <c r="C255" s="52" t="s">
         <v>37</v>
       </c>
@@ -19389,9 +19399,9 @@
       <c r="L255" s="83"/>
       <c r="M255" s="11"/>
     </row>
-    <row r="256" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B256" s="156" t="s">
-        <v>155</v>
+    <row r="256" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B256" s="168" t="s">
+        <v>154</v>
       </c>
       <c r="C256" s="52" t="e" vm="34">
         <v>#VALUE!</v>
@@ -19422,10 +19432,10 @@
       <c r="L256" s="83"/>
       <c r="M256" s="126"/>
     </row>
-    <row r="257" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B257" s="180"/>
+    <row r="257" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B257" s="169"/>
       <c r="C257" s="52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D257" s="52" t="str">
         <f t="shared" si="129"/>
@@ -19458,14 +19468,14 @@
       <c r="L257" s="83"/>
       <c r="M257" s="11"/>
       <c r="N257" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="O257" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="O257" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="258" spans="2:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B258" s="186" t="s">
+    </row>
+    <row r="258" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B258" s="172" t="s">
         <v>35</v>
       </c>
       <c r="C258" s="52" t="e" vm="30">
@@ -19497,8 +19507,8 @@
       <c r="L258" s="83"/>
       <c r="M258" s="11"/>
     </row>
-    <row r="259" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B259" s="187"/>
+    <row r="259" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B259" s="173"/>
       <c r="C259" s="52" t="s">
         <v>123</v>
       </c>
@@ -19533,18 +19543,18 @@
       <c r="L259" s="83"/>
       <c r="M259" s="11"/>
       <c r="N259" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="O259" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="P259" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="P259" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="260" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B260" s="188" t="s">
-        <v>395</v>
+    </row>
+    <row r="260" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B260" s="174" t="s">
+        <v>394</v>
       </c>
       <c r="C260" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -19575,8 +19585,8 @@
       <c r="L260" s="83"/>
       <c r="M260" s="11"/>
     </row>
-    <row r="261" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B261" s="189"/>
+    <row r="261" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B261" s="175"/>
       <c r="C261" s="52" t="s">
         <v>101</v>
       </c>
@@ -19611,15 +19621,15 @@
       <c r="L261" s="83"/>
       <c r="M261" s="11"/>
       <c r="N261" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O261" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="262" spans="2:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B262" s="156" t="s">
-        <v>162</v>
+    <row r="262" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B262" s="168" t="s">
+        <v>161</v>
       </c>
       <c r="C262" s="52" t="e" vm="35">
         <v>#VALUE!</v>
@@ -19650,16 +19660,16 @@
       <c r="L262" s="83"/>
       <c r="M262" s="126"/>
       <c r="N262" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="O262" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="O262" s="5" t="s">
+    </row>
+    <row r="263" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B263" s="169"/>
+      <c r="C263" s="52" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="263" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B263" s="180"/>
-      <c r="C263" s="52" t="s">
-        <v>165</v>
       </c>
       <c r="D263" s="52" t="str">
         <f t="shared" si="131"/>
@@ -19692,9 +19702,9 @@
       <c r="L263" s="83"/>
       <c r="M263" s="11"/>
     </row>
-    <row r="264" spans="2:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B264" s="175" t="s">
-        <v>162</v>
+    <row r="264" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B264" s="170" t="s">
+        <v>161</v>
       </c>
       <c r="C264" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -19725,14 +19735,14 @@
       <c r="L264" s="83"/>
       <c r="M264" s="126"/>
       <c r="N264" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O264" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="265" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B265" s="176"/>
+    <row r="265" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B265" s="171"/>
       <c r="C265" s="52" t="s">
         <v>101</v>
       </c>
@@ -19767,8 +19777,8 @@
       <c r="L265" s="83"/>
       <c r="M265" s="11"/>
     </row>
-    <row r="266" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B266" s="193" t="s">
+    <row r="266" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B266" s="176" t="s">
         <v>142</v>
       </c>
       <c r="C266" s="52" t="e" vm="25">
@@ -19800,8 +19810,8 @@
       <c r="L266" s="83"/>
       <c r="M266" s="11"/>
     </row>
-    <row r="267" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B267" s="194"/>
+    <row r="267" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B267" s="177"/>
       <c r="C267" s="52" t="s">
         <v>101</v>
       </c>
@@ -19836,14 +19846,14 @@
       <c r="L267" s="83"/>
       <c r="M267" s="11"/>
       <c r="N267" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="O267" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="268" spans="2:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B268" s="175" t="s">
+    <row r="268" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B268" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C268" s="52" t="e" vm="36">
@@ -19875,10 +19885,10 @@
       <c r="L268" s="83"/>
       <c r="M268" s="126"/>
     </row>
-    <row r="269" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B269" s="176"/>
+    <row r="269" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B269" s="171"/>
       <c r="C269" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D269" s="52" t="str">
         <f t="shared" ref="D269" si="136">C269</f>
@@ -19911,14 +19921,14 @@
       <c r="L269" s="83"/>
       <c r="M269" s="11"/>
       <c r="N269" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="O269" s="5" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="270" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B270" s="175" t="s">
+    <row r="270" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B270" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C270" s="52" t="e" vm="36">
@@ -19950,10 +19960,10 @@
       <c r="L270" s="83"/>
       <c r="M270" s="126"/>
     </row>
-    <row r="271" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B271" s="176"/>
+    <row r="271" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B271" s="171"/>
       <c r="C271" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D271" s="52" t="str">
         <f t="shared" ref="D271" si="138">C271</f>
@@ -19986,14 +19996,14 @@
       <c r="L271" s="83"/>
       <c r="M271" s="11"/>
       <c r="N271" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="O271" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="O271" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="272" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B272" s="175" t="s">
+    </row>
+    <row r="272" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B272" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C272" s="52" t="e" vm="37">
@@ -20025,10 +20035,10 @@
       <c r="L272" s="83"/>
       <c r="M272" s="126"/>
     </row>
-    <row r="273" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B273" s="176"/>
+    <row r="273" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B273" s="171"/>
       <c r="C273" s="52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D273" s="52" t="str">
         <f t="shared" ref="D273" si="140">C273</f>
@@ -20061,14 +20071,14 @@
       <c r="L273" s="83"/>
       <c r="M273" s="11"/>
       <c r="N273" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="O273" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="274" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B274" s="175" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="274" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B274" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C274" s="52" t="e" vm="37">
@@ -20100,10 +20110,10 @@
       <c r="L274" s="83"/>
       <c r="M274" s="126"/>
     </row>
-    <row r="275" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B275" s="176"/>
+    <row r="275" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B275" s="171"/>
       <c r="C275" s="52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D275" s="52" t="str">
         <f t="shared" ref="D275:D277" si="142">C275</f>
@@ -20136,14 +20146,14 @@
       <c r="L275" s="83"/>
       <c r="M275" s="11"/>
       <c r="N275" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="O275" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="O275" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="276" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B276" s="175" t="s">
+    </row>
+    <row r="276" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B276" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C276" s="52" t="e" vm="25">
@@ -20175,8 +20185,8 @@
       <c r="L276" s="83"/>
       <c r="M276" s="126"/>
     </row>
-    <row r="277" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B277" s="176"/>
+    <row r="277" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B277" s="171"/>
       <c r="C277" s="52" t="s">
         <v>101</v>
       </c>
@@ -20211,14 +20221,14 @@
       <c r="L277" s="83"/>
       <c r="M277" s="11"/>
       <c r="N277" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="O277" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="O277" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="278" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B278" s="175" t="s">
+    </row>
+    <row r="278" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B278" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C278" s="52" t="e" vm="36">
@@ -20250,10 +20260,10 @@
       <c r="L278" s="83"/>
       <c r="M278" s="126"/>
     </row>
-    <row r="279" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B279" s="176"/>
+    <row r="279" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B279" s="171"/>
       <c r="C279" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D279" s="52" t="str">
         <f t="shared" ref="D279" si="143">C279</f>
@@ -20286,14 +20296,14 @@
       <c r="L279" s="83"/>
       <c r="M279" s="11"/>
       <c r="N279" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="O279" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="280" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B280" s="175" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="280" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B280" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C280" s="52" t="e" vm="11">
@@ -20324,8 +20334,8 @@
       <c r="L280" s="83"/>
       <c r="M280" s="11"/>
     </row>
-    <row r="281" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B281" s="176"/>
+    <row r="281" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B281" s="171"/>
       <c r="C281" s="52" t="s">
         <v>37</v>
       </c>
@@ -20360,15 +20370,15 @@
       <c r="L281" s="83"/>
       <c r="M281" s="11"/>
       <c r="N281" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="O281" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="O281" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="282" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B282" s="166" t="s">
-        <v>155</v>
+    </row>
+    <row r="282" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B282" s="178" t="s">
+        <v>154</v>
       </c>
       <c r="C282" s="52" t="e" vm="37">
         <v>#VALUE!</v>
@@ -20399,10 +20409,10 @@
       <c r="L282" s="83"/>
       <c r="M282" s="126"/>
     </row>
-    <row r="283" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B283" s="176"/>
+    <row r="283" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B283" s="171"/>
       <c r="C283" s="52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D283" s="52" t="str">
         <f t="shared" ref="D283" si="146">C283</f>
@@ -20435,15 +20445,15 @@
       <c r="L283" s="83"/>
       <c r="M283" s="11"/>
       <c r="N283" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O283" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="284" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B284" s="166" t="s">
-        <v>155</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="284" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B284" s="178" t="s">
+        <v>154</v>
       </c>
       <c r="C284" s="52" t="e" vm="37">
         <v>#VALUE!</v>
@@ -20474,10 +20484,10 @@
       <c r="L284" s="83"/>
       <c r="M284" s="126"/>
     </row>
-    <row r="285" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B285" s="176"/>
+    <row r="285" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B285" s="171"/>
       <c r="C285" s="52" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D285" s="52" t="str">
         <f t="shared" ref="D285" si="148">C285</f>
@@ -20510,15 +20520,15 @@
       <c r="L285" s="83"/>
       <c r="M285" s="11"/>
       <c r="N285" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O285" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="286" spans="2:15" ht="35.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B286" s="166" t="s">
-        <v>155</v>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="286" spans="2:15" ht="35.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B286" s="178" t="s">
+        <v>154</v>
       </c>
       <c r="C286" s="52" t="e" vm="36">
         <v>#VALUE!</v>
@@ -20549,10 +20559,10 @@
       <c r="L286" s="83"/>
       <c r="M286" s="126"/>
     </row>
-    <row r="287" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B287" s="167"/>
+    <row r="287" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B287" s="179"/>
       <c r="C287" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D287" s="52" t="str">
         <f t="shared" ref="D287" si="149">C287</f>
@@ -20585,14 +20595,14 @@
       <c r="L287" s="83"/>
       <c r="M287" s="11"/>
       <c r="N287" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="O287" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="O287" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="288" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B288" s="175" t="s">
+    </row>
+    <row r="288" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B288" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C288" s="52" t="e" vm="36">
@@ -20624,10 +20634,10 @@
       <c r="L288" s="83"/>
       <c r="M288" s="126"/>
     </row>
-    <row r="289" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B289" s="176"/>
+    <row r="289" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B289" s="171"/>
       <c r="C289" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D289" s="52" t="str">
         <f t="shared" ref="D289" si="151">C289</f>
@@ -20660,14 +20670,14 @@
       <c r="L289" s="83"/>
       <c r="M289" s="11"/>
       <c r="N289" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="O289" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="290" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B290" s="175" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="290" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B290" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C290" s="52" t="e" vm="36">
@@ -20699,10 +20709,10 @@
       <c r="L290" s="83"/>
       <c r="M290" s="126"/>
     </row>
-    <row r="291" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B291" s="176"/>
+    <row r="291" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B291" s="171"/>
       <c r="C291" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D291" s="52" t="str">
         <f t="shared" ref="D291" si="153">C291</f>
@@ -20735,14 +20745,14 @@
       <c r="L291" s="83"/>
       <c r="M291" s="11"/>
       <c r="N291" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="O291" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="O291" s="5" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="292" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B292" s="175" t="s">
+    </row>
+    <row r="292" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B292" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C292" s="52" t="e" vm="36">
@@ -20774,10 +20784,10 @@
       <c r="L292" s="83"/>
       <c r="M292" s="126"/>
     </row>
-    <row r="293" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B293" s="176"/>
+    <row r="293" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B293" s="171"/>
       <c r="C293" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D293" s="52" t="str">
         <f t="shared" ref="D293" si="155">C293</f>
@@ -20810,14 +20820,14 @@
       <c r="L293" s="83"/>
       <c r="M293" s="11"/>
       <c r="N293" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O293" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="294" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B294" s="175" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="294" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B294" s="170" t="s">
         <v>44</v>
       </c>
       <c r="C294" s="52" t="e" vm="11">
@@ -20848,8 +20858,8 @@
       <c r="L294" s="83"/>
       <c r="M294" s="11"/>
     </row>
-    <row r="295" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B295" s="176"/>
+    <row r="295" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B295" s="171"/>
       <c r="C295" s="52" t="s">
         <v>37</v>
       </c>
@@ -20884,15 +20894,15 @@
       <c r="L295" s="83"/>
       <c r="M295" s="11"/>
       <c r="N295" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="O295" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="O295" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="296" spans="2:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B296" s="188" t="s">
-        <v>395</v>
+    </row>
+    <row r="296" spans="2:16" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B296" s="174" t="s">
+        <v>394</v>
       </c>
       <c r="C296" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -20923,8 +20933,8 @@
       <c r="L296" s="83"/>
       <c r="M296" s="11"/>
     </row>
-    <row r="297" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="B297" s="189"/>
+    <row r="297" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B297" s="175"/>
       <c r="C297" s="52" t="s">
         <v>101</v>
       </c>
@@ -20959,13 +20969,13 @@
       <c r="L297" s="83"/>
       <c r="M297" s="11"/>
       <c r="N297" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="O297" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="298" spans="2:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B298" s="164" t="s">
         <v>33</v>
       </c>
@@ -20998,7 +21008,7 @@
       <c r="L298" s="83"/>
       <c r="M298" s="11"/>
     </row>
-    <row r="299" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="299" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B299" s="165"/>
       <c r="C299" s="52" t="s">
         <v>101</v>
@@ -21034,13 +21044,13 @@
       <c r="L299" s="83"/>
       <c r="M299" s="11"/>
       <c r="N299" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O299" s="5" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="300" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="300" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B300" s="139" t="s">
         <v>32</v>
       </c>
@@ -21073,7 +21083,7 @@
       <c r="L300" s="83"/>
       <c r="M300" s="11"/>
     </row>
-    <row r="301" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="301" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B301" s="140"/>
       <c r="C301" s="63" t="s">
         <v>101</v>
@@ -21109,13 +21119,13 @@
       <c r="L301" s="83"/>
       <c r="M301" s="11"/>
       <c r="N301" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O301" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="302" spans="2:16" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="302" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B302" s="139" t="s">
         <v>32</v>
       </c>
@@ -21148,7 +21158,7 @@
       <c r="L302" s="83"/>
       <c r="M302" s="11"/>
     </row>
-    <row r="303" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="303" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B303" s="140"/>
       <c r="C303" s="63" t="s">
         <v>101</v>
@@ -21184,14 +21194,14 @@
       <c r="L303" s="83"/>
       <c r="M303" s="11"/>
       <c r="N303" s="18" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P303" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="304" spans="2:16" ht="30.8" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B304" s="135" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="304" spans="2:16" ht="30.8" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B304" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C304" s="63" t="e" vm="25">
@@ -21223,8 +21233,8 @@
       <c r="L304" s="83"/>
       <c r="M304" s="11"/>
     </row>
-    <row r="305" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B305" s="136"/>
+    <row r="305" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B305" s="137"/>
       <c r="C305" s="63" t="s">
         <v>101</v>
       </c>
@@ -21259,13 +21269,13 @@
       <c r="L305" s="83"/>
       <c r="M305" s="11"/>
       <c r="N305" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="O305" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="306" spans="2:15" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="306" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B306" s="139" t="s">
         <v>32</v>
       </c>
@@ -21298,7 +21308,7 @@
       <c r="L306" s="83"/>
       <c r="M306" s="11"/>
     </row>
-    <row r="307" spans="2:15" x14ac:dyDescent="0.35">
+    <row r="307" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B307" s="140"/>
       <c r="C307" s="63" t="s">
         <v>101</v>
@@ -21334,14 +21344,14 @@
       <c r="L307" s="83"/>
       <c r="M307" s="11"/>
       <c r="N307" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O307" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="308" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B308" s="166" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="308" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B308" s="178" t="s">
         <v>33</v>
       </c>
       <c r="C308" s="52" t="e" vm="25">
@@ -21373,8 +21383,8 @@
       <c r="L308" s="83"/>
       <c r="M308" s="11"/>
     </row>
-    <row r="309" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B309" s="167"/>
+    <row r="309" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B309" s="179"/>
       <c r="C309" s="52" t="s">
         <v>101</v>
       </c>
@@ -21409,15 +21419,15 @@
       <c r="L309" s="83"/>
       <c r="M309" s="11"/>
       <c r="N309" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="O309" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="O309" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="310" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B310" s="166" t="s">
-        <v>155</v>
+    </row>
+    <row r="310" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B310" s="178" t="s">
+        <v>154</v>
       </c>
       <c r="C310" s="52" t="e" vm="36">
         <v>#VALUE!</v>
@@ -21448,10 +21458,10 @@
       <c r="L310" s="83"/>
       <c r="M310" s="126"/>
     </row>
-    <row r="311" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B311" s="167"/>
+    <row r="311" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B311" s="179"/>
       <c r="C311" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D311" s="52" t="str">
         <f t="shared" ref="D311:D313" si="165">C311</f>
@@ -21484,14 +21494,14 @@
       <c r="L311" s="83"/>
       <c r="M311" s="11"/>
       <c r="N311" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="O311" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="O311" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="312" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B312" s="175" t="s">
+    </row>
+    <row r="312" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B312" s="170" t="s">
         <v>26</v>
       </c>
       <c r="C312" s="52" t="e" vm="25">
@@ -21523,8 +21533,8 @@
       <c r="L312" s="83"/>
       <c r="M312" s="11"/>
     </row>
-    <row r="313" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B313" s="176"/>
+    <row r="313" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B313" s="171"/>
       <c r="C313" s="52" t="s">
         <v>101</v>
       </c>
@@ -21559,14 +21569,14 @@
       <c r="L313" s="83"/>
       <c r="M313" s="11"/>
       <c r="N313" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="O313" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="O313" s="5" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="314" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B314" s="166" t="s">
+    </row>
+    <row r="314" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B314" s="178" t="s">
         <v>32</v>
       </c>
       <c r="C314" s="52" t="e" vm="36">
@@ -21598,10 +21608,10 @@
       <c r="L314" s="83"/>
       <c r="M314" s="126"/>
     </row>
-    <row r="315" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B315" s="167"/>
+    <row r="315" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B315" s="179"/>
       <c r="C315" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D315" s="52" t="str">
         <f t="shared" ref="D315" si="167">C315</f>
@@ -21634,14 +21644,14 @@
       <c r="L315" s="83"/>
       <c r="M315" s="11"/>
       <c r="N315" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="O315" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="O315" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="316" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B316" s="166" t="s">
+    </row>
+    <row r="316" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B316" s="178" t="s">
         <v>32</v>
       </c>
       <c r="C316" s="52" t="e" vm="36">
@@ -21673,10 +21683,10 @@
       <c r="L316" s="83"/>
       <c r="M316" s="126"/>
     </row>
-    <row r="317" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B317" s="167"/>
+    <row r="317" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B317" s="179"/>
       <c r="C317" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D317" s="52" t="str">
         <f t="shared" ref="D317" si="169">C317</f>
@@ -21709,14 +21719,14 @@
       <c r="L317" s="83"/>
       <c r="M317" s="11"/>
       <c r="N317" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="O317" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="O317" s="5" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="318" spans="2:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B318" s="166" t="s">
+    </row>
+    <row r="318" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B318" s="178" t="s">
         <v>32</v>
       </c>
       <c r="C318" s="52" t="e" vm="36">
@@ -21748,10 +21758,10 @@
       <c r="L318" s="83"/>
       <c r="M318" s="126"/>
     </row>
-    <row r="319" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B319" s="167"/>
+    <row r="319" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B319" s="179"/>
       <c r="C319" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D319" s="52" t="str">
         <f t="shared" ref="D319" si="171">C319</f>
@@ -21784,14 +21794,14 @@
       <c r="L319" s="83"/>
       <c r="M319" s="11"/>
       <c r="N319" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="O319" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="O319" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="320" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B320" s="166" t="s">
+    </row>
+    <row r="320" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B320" s="178" t="s">
         <v>32</v>
       </c>
       <c r="C320" s="52" t="e" vm="36">
@@ -21823,10 +21833,10 @@
       <c r="L320" s="83"/>
       <c r="M320" s="126"/>
     </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B321" s="167"/>
+    <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B321" s="179"/>
       <c r="C321" s="52" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D321" s="52" t="str">
         <f t="shared" ref="D321" si="173">C321</f>
@@ -21859,13 +21869,13 @@
       <c r="L321" s="83"/>
       <c r="M321" s="11"/>
       <c r="N321" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="O321" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="O321" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B322" s="139" t="s">
         <v>32</v>
       </c>
@@ -21897,7 +21907,7 @@
       <c r="L322" s="83"/>
       <c r="M322" s="11"/>
     </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B323" s="140"/>
       <c r="C323" s="52" t="s">
         <v>37</v>
@@ -21933,18 +21943,18 @@
       <c r="L323" s="83"/>
       <c r="M323" s="11"/>
       <c r="N323" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O323" s="5" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="324" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A324" s="5">
         <v>1</v>
       </c>
-      <c r="B324" s="141" t="s">
-        <v>382</v>
+      <c r="B324" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C324" s="16" t="e" vm="25">
         <v>#VALUE!</v>
@@ -21975,11 +21985,11 @@
       <c r="L324" s="83"/>
       <c r="M324" s="11"/>
     </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="5">
         <v>1</v>
       </c>
-      <c r="B325" s="142"/>
+      <c r="B325" s="148"/>
       <c r="C325" s="16" t="s">
         <v>101</v>
       </c>
@@ -22017,13 +22027,13 @@
       </c>
       <c r="M325" s="11"/>
       <c r="N325" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="O325" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="O325" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B326" s="164" t="s">
         <v>33</v>
       </c>
@@ -22056,10 +22066,10 @@
       <c r="L326" s="83"/>
       <c r="M326" s="11"/>
     </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B327" s="165"/>
       <c r="C327" s="52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D327" s="52" t="str">
         <f t="shared" si="175"/>
@@ -22092,13 +22102,13 @@
       <c r="L327" s="83"/>
       <c r="M327" s="11"/>
       <c r="N327" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O327" s="5" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B328" s="139" t="s">
         <v>32</v>
       </c>
@@ -22130,7 +22140,7 @@
       <c r="L328" s="83"/>
       <c r="M328" s="11"/>
     </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B329" s="140"/>
       <c r="C329" s="52" t="s">
         <v>37</v>
@@ -22166,13 +22176,13 @@
       <c r="L329" s="83"/>
       <c r="M329" s="11"/>
       <c r="N329" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="O329" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="O329" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B330" s="164" t="s">
         <v>33</v>
       </c>
@@ -22205,7 +22215,7 @@
       <c r="L330" s="83"/>
       <c r="M330" s="11"/>
     </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B331" s="165"/>
       <c r="C331" s="52" t="s">
         <v>101</v>
@@ -22241,15 +22251,15 @@
       <c r="L331" s="83"/>
       <c r="M331" s="11"/>
       <c r="N331" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="O331" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="O331" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B332" s="150" t="s">
-        <v>210</v>
+    </row>
+    <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B332" s="166" t="s">
+        <v>209</v>
       </c>
       <c r="C332" s="52" t="e" vm="25">
         <v>#VALUE!</v>
@@ -22280,8 +22290,8 @@
       <c r="L332" s="83"/>
       <c r="M332" s="11"/>
     </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B333" s="195"/>
+    <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B333" s="167"/>
       <c r="C333" s="52" t="s">
         <v>101</v>
       </c>
@@ -22316,13 +22326,13 @@
       <c r="L333" s="83"/>
       <c r="M333" s="11"/>
       <c r="N333" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O333" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B334" s="139" t="s">
         <v>32</v>
       </c>
@@ -22354,7 +22364,7 @@
       <c r="L334" s="83"/>
       <c r="M334" s="11"/>
     </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B335" s="140"/>
       <c r="C335" s="52" t="s">
         <v>37</v>
@@ -22390,16 +22400,16 @@
       <c r="L335" s="83"/>
       <c r="M335" s="11"/>
       <c r="N335" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="O335" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="O335" s="5" t="s">
+      <c r="P335" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="P335" s="5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B336" s="139" t="s">
         <v>32</v>
       </c>
@@ -22431,7 +22441,7 @@
       <c r="L336" s="83"/>
       <c r="M336" s="11"/>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="B337" s="140"/>
       <c r="C337" s="52" t="s">
         <v>37</v>
@@ -22466,13 +22476,13 @@
       <c r="L337" s="83"/>
       <c r="M337" s="11"/>
       <c r="N337" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="O337" s="5" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.35">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="B338" s="139" t="s">
         <v>32</v>
       </c>
@@ -22505,7 +22515,7 @@
       <c r="L338" s="83"/>
       <c r="M338" s="11"/>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="B339" s="140"/>
       <c r="C339" s="52" t="s">
         <v>101</v>
@@ -22541,18 +22551,18 @@
       <c r="L339" s="83"/>
       <c r="M339" s="11"/>
       <c r="N339" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="O339" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="O339" s="5" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.35">
+    </row>
+    <row r="340" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="5">
         <v>1</v>
       </c>
-      <c r="B340" s="135" t="s">
-        <v>386</v>
+      <c r="B340" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C340" s="81" t="e" vm="25">
         <v>#VALUE!</v>
@@ -22583,11 +22593,11 @@
       <c r="L340" s="83"/>
       <c r="M340" s="11"/>
     </row>
-    <row r="341" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="5">
         <v>1</v>
       </c>
-      <c r="B341" s="136"/>
+      <c r="B341" s="137"/>
       <c r="C341" s="81" t="s">
         <v>101</v>
       </c>
@@ -22625,11 +22635,11 @@
       </c>
       <c r="M341" s="11"/>
       <c r="N341" s="5" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="342" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B342" s="141" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B342" s="147" t="s">
         <v>42</v>
       </c>
       <c r="C342" s="52" t="e" vm="11">
@@ -22660,8 +22670,8 @@
       <c r="L342" s="83"/>
       <c r="M342" s="11"/>
     </row>
-    <row r="343" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B343" s="142"/>
+    <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B343" s="148"/>
       <c r="C343" s="99" t="s">
         <v>37</v>
       </c>
@@ -22696,17 +22706,17 @@
       <c r="L343" s="83"/>
       <c r="M343" s="11"/>
       <c r="N343" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="O343" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="P343" s="5">
         <v>150</v>
       </c>
     </row>
-    <row r="344" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B344" s="141" t="s">
+    <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B344" s="147" t="s">
         <v>42</v>
       </c>
       <c r="C344" s="52" t="e" vm="11">
@@ -22740,8 +22750,8 @@
         <v>100</v>
       </c>
     </row>
-    <row r="345" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B345" s="142"/>
+    <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B345" s="148"/>
       <c r="C345" s="52" t="s">
         <v>37</v>
       </c>
@@ -22779,11 +22789,11 @@
         <v>76</v>
       </c>
       <c r="O345" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="346" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B346" s="196" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B346" s="156" t="s">
         <v>35</v>
       </c>
       <c r="C346" s="52" t="e" vm="11">
@@ -22814,8 +22824,8 @@
       <c r="L346" s="83"/>
       <c r="M346" s="11"/>
     </row>
-    <row r="347" spans="1:17" ht="57.6" x14ac:dyDescent="0.35">
-      <c r="B347" s="197"/>
+    <row r="347" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B347" s="157"/>
       <c r="C347" s="52" t="s">
         <v>37</v>
       </c>
@@ -22850,20 +22860,20 @@
       <c r="L347" s="83"/>
       <c r="M347" s="11"/>
       <c r="N347" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="O347" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="P347" s="6" t="s">
         <v>219</v>
-      </c>
-      <c r="O347" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="P347" s="6" t="s">
-        <v>220</v>
       </c>
       <c r="Q347" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="348" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B348" s="198" t="s">
+    <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B348" s="138" t="s">
         <v>32</v>
       </c>
       <c r="C348" s="52" t="e" vm="11">
@@ -22894,8 +22904,8 @@
       <c r="L348" s="83"/>
       <c r="M348" s="11"/>
     </row>
-    <row r="349" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B349" s="198"/>
+    <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B349" s="138"/>
       <c r="C349" s="52" t="s">
         <v>37</v>
       </c>
@@ -22931,14 +22941,14 @@
       <c r="L349" s="83"/>
       <c r="M349" s="11"/>
       <c r="N349" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="O349" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="350" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="B350" s="135" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="350" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B350" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C350" s="13" t="e" vm="11">
@@ -22969,8 +22979,8 @@
       <c r="L350" s="83"/>
       <c r="M350" s="11"/>
     </row>
-    <row r="351" spans="1:17" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B351" s="136"/>
+    <row r="351" spans="1:17" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B351" s="137"/>
       <c r="C351" s="84" t="s">
         <v>37</v>
       </c>
@@ -23005,21 +23015,21 @@
       <c r="L351" s="83"/>
       <c r="M351" s="11"/>
       <c r="N351" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="O351" s="5" t="s">
         <v>222</v>
-      </c>
-      <c r="O351" s="5" t="s">
-        <v>223</v>
       </c>
       <c r="P351" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="352" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="5">
         <v>0</v>
       </c>
-      <c r="B352" s="143" t="s">
-        <v>224</v>
+      <c r="B352" s="151" t="s">
+        <v>223</v>
       </c>
       <c r="C352" s="5" t="e" vm="39">
         <v>#VALUE!</v>
@@ -23051,10 +23061,10 @@
       <c r="M352" s="7"/>
       <c r="N352" s="13"/>
     </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B353" s="203"/>
+    <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B353" s="152"/>
       <c r="C353" s="52" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D353" s="52" t="str">
         <f>C353</f>
@@ -23088,14 +23098,14 @@
       <c r="L353" s="83"/>
       <c r="M353" s="7"/>
       <c r="N353" s="13" t="s">
+        <v>225</v>
+      </c>
+      <c r="O353" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="O353" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B354" s="135" t="s">
+    </row>
+    <row r="354" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B354" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C354" s="16" t="e" vm="11">
@@ -23126,8 +23136,8 @@
       <c r="L354" s="83"/>
       <c r="M354" s="11"/>
     </row>
-    <row r="355" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B355" s="136"/>
+    <row r="355" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B355" s="137"/>
       <c r="C355" s="16" t="s">
         <v>37</v>
       </c>
@@ -23162,17 +23172,17 @@
       <c r="L355" s="83"/>
       <c r="M355" s="11"/>
       <c r="N355" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="O355" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P355" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B356" s="135" t="s">
+    <row r="356" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B356" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C356" s="52" t="e" vm="11">
@@ -23203,8 +23213,8 @@
       <c r="L356" s="83"/>
       <c r="M356" s="11"/>
     </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B357" s="136"/>
+    <row r="357" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B357" s="137"/>
       <c r="C357" s="99" t="s">
         <v>37</v>
       </c>
@@ -23239,14 +23249,14 @@
       <c r="L357" s="83"/>
       <c r="M357" s="11"/>
       <c r="N357" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O357" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B358" s="141" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B358" s="147" t="s">
         <v>42</v>
       </c>
       <c r="C358" s="52" t="e" vm="11">
@@ -23277,8 +23287,8 @@
       <c r="L358" s="83"/>
       <c r="M358" s="11"/>
     </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B359" s="142"/>
+    <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B359" s="148"/>
       <c r="C359" s="99" t="s">
         <v>37</v>
       </c>
@@ -23313,15 +23323,15 @@
       <c r="L359" s="83"/>
       <c r="M359" s="11"/>
       <c r="N359" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="O359" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
-      <c r="B360" s="143" t="s">
+      <c r="B360" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C360" s="52" t="e" vm="11">
@@ -23352,9 +23362,9 @@
       <c r="L360" s="83"/>
       <c r="M360" s="11"/>
     </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
-      <c r="B361" s="143"/>
+      <c r="B361" s="151"/>
       <c r="C361" s="52" t="s">
         <v>37</v>
       </c>
@@ -23389,14 +23399,14 @@
       <c r="L361" s="83"/>
       <c r="M361" s="11"/>
       <c r="N361" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="O361" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="O361" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B362" s="199" t="s">
+    </row>
+    <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B362" s="162" t="s">
         <v>44</v>
       </c>
       <c r="C362" s="52" t="e" vm="11">
@@ -23427,8 +23437,8 @@
       <c r="L362" s="83"/>
       <c r="M362" s="123"/>
     </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B363" s="200"/>
+    <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B363" s="163"/>
       <c r="C363" s="99" t="s">
         <v>37</v>
       </c>
@@ -23463,14 +23473,14 @@
       <c r="L363" s="83"/>
       <c r="M363" s="123"/>
       <c r="N363" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O363" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B364" s="141" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B364" s="147" t="s">
         <v>42</v>
       </c>
       <c r="C364" s="52" t="e" vm="11">
@@ -23501,8 +23511,8 @@
       <c r="L364" s="83"/>
       <c r="M364" s="11"/>
     </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B365" s="142"/>
+    <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B365" s="148"/>
       <c r="C365" s="99" t="s">
         <v>37</v>
       </c>
@@ -23537,15 +23547,15 @@
       <c r="L365" s="83"/>
       <c r="M365" s="11"/>
       <c r="N365" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="O365" s="5" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B366" s="151" t="s">
         <v>233</v>
-      </c>
-      <c r="O365" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B366" s="143" t="s">
-        <v>234</v>
       </c>
       <c r="C366" s="52" t="e" vm="29">
         <v>#VALUE!</v>
@@ -23576,8 +23586,8 @@
       <c r="L366" s="83"/>
       <c r="M366" s="123"/>
     </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B367" s="143"/>
+    <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B367" s="151"/>
       <c r="C367" s="52" t="s">
         <v>121</v>
       </c>
@@ -23612,15 +23622,15 @@
       <c r="L367" s="83"/>
       <c r="M367" s="11"/>
       <c r="N367" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="O367" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="O367" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B368" s="143" t="s">
-        <v>234</v>
+    </row>
+    <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B368" s="151" t="s">
+        <v>233</v>
       </c>
       <c r="C368" s="52" t="e" vm="40">
         <v>#VALUE!</v>
@@ -23651,10 +23661,10 @@
       <c r="L368" s="83"/>
       <c r="M368" s="123"/>
     </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B369" s="143"/>
+    <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B369" s="151"/>
       <c r="C369" s="52" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D369" s="52" t="str">
         <f t="shared" si="201"/>
@@ -23687,14 +23697,14 @@
       <c r="L369" s="83"/>
       <c r="M369" s="11"/>
       <c r="N369" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="O369" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="O369" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B370" s="201" t="s">
+    </row>
+    <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B370" s="149" t="s">
         <v>35</v>
       </c>
       <c r="C370" s="47" t="e" vm="11">
@@ -23725,8 +23735,8 @@
       <c r="L370" s="83"/>
       <c r="M370" s="11"/>
     </row>
-    <row r="371" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
-      <c r="B371" s="202"/>
+    <row r="371" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B371" s="150"/>
       <c r="C371" s="93" t="s">
         <v>37</v>
       </c>
@@ -23761,18 +23771,18 @@
       <c r="L371" s="83"/>
       <c r="M371" s="11"/>
       <c r="N371" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O371" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="P371" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="13"/>
-      <c r="B372" s="135" t="s">
+      <c r="B372" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C372" s="13" t="e" vm="11">
@@ -23803,9 +23813,9 @@
       <c r="L372" s="83"/>
       <c r="M372" s="11"/>
     </row>
-    <row r="373" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="13"/>
-      <c r="B373" s="136"/>
+      <c r="B373" s="137"/>
       <c r="C373" s="13" t="s">
         <v>37</v>
       </c>
@@ -23840,17 +23850,17 @@
       <c r="L373" s="83"/>
       <c r="M373" s="11"/>
       <c r="N373" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O373" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P373" s="6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B374" s="141" t="s">
+    <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B374" s="147" t="s">
         <v>42</v>
       </c>
       <c r="C374" s="52" t="e" vm="11">
@@ -23881,8 +23891,8 @@
       <c r="L374" s="83"/>
       <c r="M374" s="11"/>
     </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B375" s="142"/>
+    <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B375" s="148"/>
       <c r="C375" s="52" t="s">
         <v>37</v>
       </c>
@@ -23917,18 +23927,18 @@
       <c r="L375" s="83"/>
       <c r="M375" s="11"/>
       <c r="N375" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O375" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="5">
         <v>1</v>
       </c>
-      <c r="B376" s="141" t="s">
-        <v>382</v>
+      <c r="B376" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C376" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -23958,11 +23968,11 @@
       <c r="L376" s="83"/>
       <c r="M376" s="11"/>
     </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="5">
         <v>1</v>
       </c>
-      <c r="B377" s="142"/>
+      <c r="B377" s="148"/>
       <c r="C377" s="86" t="s">
         <v>37</v>
       </c>
@@ -24000,11 +24010,11 @@
       </c>
       <c r="M377" s="11"/>
       <c r="N377" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B378" s="135" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="378" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B378" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C378" s="13" t="e" vm="11">
@@ -24035,8 +24045,8 @@
       <c r="L378" s="83"/>
       <c r="M378" s="11"/>
     </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B379" s="136"/>
+    <row r="379" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B379" s="137"/>
       <c r="C379" s="13" t="s">
         <v>37</v>
       </c>
@@ -24071,14 +24081,14 @@
       <c r="L379" s="83"/>
       <c r="M379" s="11"/>
       <c r="N379" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O379" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B380" s="183" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B380" s="153" t="s">
         <v>102</v>
       </c>
       <c r="C380" s="63" t="e" vm="11">
@@ -24109,8 +24119,8 @@
       <c r="L380" s="83"/>
       <c r="M380" s="11"/>
     </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B381" s="184"/>
+    <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B381" s="154"/>
       <c r="C381" s="90" t="s">
         <v>37</v>
       </c>
@@ -24145,14 +24155,14 @@
       <c r="L381" s="83"/>
       <c r="M381" s="11"/>
       <c r="N381" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="O381" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B382" s="135" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="382" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B382" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C382" s="52" t="e" vm="11">
@@ -24183,8 +24193,8 @@
       <c r="L382" s="83"/>
       <c r="M382" s="11"/>
     </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B383" s="136"/>
+    <row r="383" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B383" s="137"/>
       <c r="C383" s="52" t="s">
         <v>37</v>
       </c>
@@ -24219,14 +24229,14 @@
       <c r="L383" s="83"/>
       <c r="M383" s="11"/>
       <c r="N383" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="O383" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="O383" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B384" s="201" t="s">
+    </row>
+    <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B384" s="149" t="s">
         <v>35</v>
       </c>
       <c r="C384" s="52" t="e" vm="41">
@@ -24258,10 +24268,10 @@
       <c r="L384" s="83"/>
       <c r="M384" s="11"/>
     </row>
-    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B385" s="202"/>
+    <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B385" s="150"/>
       <c r="C385" s="52" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D385" s="52" t="str">
         <f t="shared" ref="D385" si="212">C385</f>
@@ -24294,18 +24304,18 @@
       <c r="L385" s="83"/>
       <c r="M385" s="11"/>
       <c r="N385" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="O385" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="O385" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="5">
         <v>1</v>
       </c>
-      <c r="B386" s="141" t="s">
-        <v>382</v>
+      <c r="B386" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C386" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -24335,11 +24345,11 @@
       <c r="L386" s="83"/>
       <c r="M386" s="11"/>
     </row>
-    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="5">
         <v>1</v>
       </c>
-      <c r="B387" s="142"/>
+      <c r="B387" s="148"/>
       <c r="C387" s="13" t="s">
         <v>37</v>
       </c>
@@ -24377,11 +24387,11 @@
       </c>
       <c r="M387" s="11"/>
       <c r="N387" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B388" s="135" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="388" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B388" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C388" s="63" t="e" vm="25">
@@ -24413,8 +24423,8 @@
       <c r="L388" s="83"/>
       <c r="M388" s="11"/>
     </row>
-    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B389" s="136"/>
+    <row r="389" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B389" s="137"/>
       <c r="C389" s="63" t="s">
         <v>101</v>
       </c>
@@ -24449,15 +24459,15 @@
       <c r="L389" s="83"/>
       <c r="M389" s="11"/>
       <c r="N389" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="O389" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B390" s="151" t="s">
         <v>249</v>
-      </c>
-      <c r="O389" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B390" s="143" t="s">
-        <v>250</v>
       </c>
       <c r="C390" s="52" t="e" vm="42">
         <v>#VALUE!</v>
@@ -24488,10 +24498,10 @@
       <c r="L390" s="83"/>
       <c r="M390" s="123"/>
     </row>
-    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B391" s="203"/>
+    <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B391" s="152"/>
       <c r="C391" s="52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D391" s="52" t="str">
         <f t="shared" si="213"/>
@@ -24524,14 +24534,14 @@
       <c r="L391" s="83"/>
       <c r="M391" s="11"/>
       <c r="N391" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="O391" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B392" s="135" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="392" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B392" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C392" s="20" t="e" vm="11">
@@ -24562,8 +24572,8 @@
       <c r="L392" s="83"/>
       <c r="M392" s="11"/>
     </row>
-    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B393" s="136"/>
+    <row r="393" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B393" s="137"/>
       <c r="C393" s="88" t="s">
         <v>37</v>
       </c>
@@ -24598,14 +24608,14 @@
       <c r="L393" s="83"/>
       <c r="M393" s="11"/>
       <c r="N393" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="O393" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B394" s="148" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B394" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C394" s="52" t="e" vm="11">
@@ -24636,8 +24646,8 @@
       <c r="L394" s="83"/>
       <c r="M394" s="11"/>
     </row>
-    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B395" s="149"/>
+    <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B395" s="143"/>
       <c r="C395" s="52" t="s">
         <v>37</v>
       </c>
@@ -24672,15 +24682,15 @@
       <c r="L395" s="83"/>
       <c r="M395" s="11"/>
       <c r="N395" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="O395" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="O395" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B396" s="143" t="s">
-        <v>224</v>
+    </row>
+    <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B396" s="151" t="s">
+        <v>223</v>
       </c>
       <c r="C396" s="52" t="e" vm="42">
         <v>#VALUE!</v>
@@ -24711,10 +24721,10 @@
       <c r="L396" s="83"/>
       <c r="M396" s="123"/>
     </row>
-    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B397" s="203"/>
+    <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B397" s="152"/>
       <c r="C397" s="52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D397" s="52" t="str">
         <f t="shared" si="214"/>
@@ -24747,15 +24757,15 @@
       <c r="L397" s="83"/>
       <c r="M397" s="11"/>
       <c r="N397" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="O397" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B398" s="151" t="s">
         <v>249</v>
-      </c>
-      <c r="O397" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B398" s="143" t="s">
-        <v>250</v>
       </c>
       <c r="C398" s="52" t="e" vm="42">
         <v>#VALUE!</v>
@@ -24786,10 +24796,10 @@
       <c r="L398" s="83"/>
       <c r="M398" s="123"/>
     </row>
-    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B399" s="203"/>
+    <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B399" s="152"/>
       <c r="C399" s="52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D399" s="52" t="str">
         <f t="shared" si="214"/>
@@ -24822,15 +24832,15 @@
       <c r="L399" s="83"/>
       <c r="M399" s="11"/>
       <c r="N399" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="O399" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B400" s="151" t="s">
         <v>255</v>
-      </c>
-      <c r="O399" s="5" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B400" s="143" t="s">
-        <v>256</v>
       </c>
       <c r="C400" s="52" t="e" vm="29">
         <v>#VALUE!</v>
@@ -24861,8 +24871,8 @@
       <c r="L400" s="83"/>
       <c r="M400" s="123"/>
     </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B401" s="143"/>
+    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B401" s="151"/>
       <c r="C401" s="52" t="s">
         <v>121</v>
       </c>
@@ -24897,15 +24907,15 @@
       <c r="L401" s="83"/>
       <c r="M401" s="11"/>
       <c r="N401" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="O401" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="O401" s="5" t="s">
+    </row>
+    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B402" s="151" t="s">
         <v>258</v>
-      </c>
-    </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B402" s="143" t="s">
-        <v>259</v>
       </c>
       <c r="C402" s="52" t="e" vm="29">
         <v>#VALUE!</v>
@@ -24936,8 +24946,8 @@
       <c r="L402" s="83"/>
       <c r="M402" s="123"/>
     </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B403" s="143"/>
+    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B403" s="151"/>
       <c r="C403" s="52" t="s">
         <v>121</v>
       </c>
@@ -24972,14 +24982,14 @@
       <c r="L403" s="83"/>
       <c r="M403" s="11"/>
       <c r="N403" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="O403" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="O403" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B404" s="148" t="s">
+    </row>
+    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B404" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C404" s="52" t="e" vm="11">
@@ -25010,8 +25020,8 @@
       <c r="L404" s="83"/>
       <c r="M404" s="11"/>
     </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B405" s="149"/>
+    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B405" s="143"/>
       <c r="C405" s="52" t="s">
         <v>37</v>
       </c>
@@ -25046,15 +25056,15 @@
       <c r="L405" s="83"/>
       <c r="M405" s="11"/>
       <c r="N405" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="O405" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="O405" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B406" s="143" t="s">
-        <v>256</v>
+    </row>
+    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B406" s="151" t="s">
+        <v>255</v>
       </c>
       <c r="C406" s="52" t="e" vm="29">
         <v>#VALUE!</v>
@@ -25085,8 +25095,8 @@
       <c r="L406" s="83"/>
       <c r="M406" s="123"/>
     </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B407" s="143"/>
+    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B407" s="151"/>
       <c r="C407" s="52" t="s">
         <v>121</v>
       </c>
@@ -25121,14 +25131,14 @@
       <c r="L407" s="83"/>
       <c r="M407" s="11"/>
       <c r="N407" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="O407" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B408" s="181" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B408" s="161" t="s">
         <v>89</v>
       </c>
       <c r="C408" s="52" t="e" vm="22">
@@ -25160,8 +25170,8 @@
       <c r="L408" s="83"/>
       <c r="M408" s="11"/>
     </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B409" s="181"/>
+    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B409" s="161"/>
       <c r="C409" s="78" t="s">
         <v>69</v>
       </c>
@@ -25196,20 +25206,20 @@
       <c r="L409" s="83"/>
       <c r="M409" s="11"/>
       <c r="N409" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O409" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="P409" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="P409" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="5">
         <v>1</v>
       </c>
-      <c r="B410" s="174" t="s">
+      <c r="B410" s="155" t="s">
         <v>89</v>
       </c>
       <c r="C410" s="13" t="e" vm="22">
@@ -25242,11 +25252,11 @@
       <c r="M410" s="11"/>
       <c r="N410" s="18"/>
     </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="5">
         <v>1</v>
       </c>
-      <c r="B411" s="174"/>
+      <c r="B411" s="155"/>
       <c r="C411" s="15" t="s">
         <v>69</v>
       </c>
@@ -25284,21 +25294,21 @@
       </c>
       <c r="M411" s="11"/>
       <c r="N411" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="O411" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="O411" s="5" t="s">
-        <v>264</v>
-      </c>
       <c r="P411" s="5" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="5">
         <v>1</v>
       </c>
-      <c r="B412" s="148" t="s">
-        <v>383</v>
+      <c r="B412" s="142" t="s">
+        <v>382</v>
       </c>
       <c r="C412" s="16" t="e" vm="22">
         <v>#VALUE!</v>
@@ -25329,11 +25339,11 @@
       <c r="L412" s="83"/>
       <c r="M412" s="11"/>
     </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="5">
         <v>1</v>
       </c>
-      <c r="B413" s="149"/>
+      <c r="B413" s="143"/>
       <c r="C413" s="23" t="s">
         <v>69</v>
       </c>
@@ -25374,11 +25384,11 @@
         <v>8</v>
       </c>
       <c r="O413" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B414" s="148" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B414" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C414" s="63" t="e" vm="25">
@@ -25410,8 +25420,8 @@
       <c r="L414" s="83"/>
       <c r="M414" s="11"/>
     </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B415" s="149"/>
+    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B415" s="143"/>
       <c r="C415" s="63" t="s">
         <v>101</v>
       </c>
@@ -25446,18 +25456,18 @@
       <c r="L415" s="83"/>
       <c r="M415" s="11"/>
       <c r="N415" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="O415" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="5">
         <v>1</v>
       </c>
-      <c r="B416" s="146" t="s">
-        <v>381</v>
+      <c r="B416" s="158" t="s">
+        <v>380</v>
       </c>
       <c r="C416" s="13" t="e" vm="22">
         <v>#VALUE!</v>
@@ -25488,11 +25498,11 @@
       <c r="L416" s="83"/>
       <c r="M416" s="11"/>
     </row>
-    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="5">
         <v>1</v>
       </c>
-      <c r="B417" s="147"/>
+      <c r="B417" s="159"/>
       <c r="C417" s="15" t="s">
         <v>69</v>
       </c>
@@ -25530,12 +25540,12 @@
       </c>
       <c r="M417" s="11"/>
       <c r="N417" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B418" s="154" t="s">
-        <v>317</v>
+        <v>266</v>
+      </c>
+    </row>
+    <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B418" s="160" t="s">
+        <v>316</v>
       </c>
       <c r="C418" s="47" t="e" vm="33">
         <v>#VALUE!</v>
@@ -25566,10 +25576,10 @@
       <c r="L418" s="83"/>
       <c r="M418" s="11"/>
     </row>
-    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B419" s="154"/>
+    <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B419" s="160"/>
       <c r="C419" s="78" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D419" s="53" t="str">
         <f t="shared" ref="D419" si="228">C419</f>
@@ -25603,18 +25613,18 @@
       <c r="L419" s="83"/>
       <c r="M419" s="11"/>
       <c r="N419" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="O419" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="420" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="5">
         <v>1</v>
       </c>
-      <c r="B420" s="148" t="s">
-        <v>384</v>
+      <c r="B420" s="142" t="s">
+        <v>383</v>
       </c>
       <c r="C420" s="13" t="e" vm="43">
         <v>#VALUE!</v>
@@ -25645,13 +25655,13 @@
       <c r="L420" s="83"/>
       <c r="M420" s="11"/>
     </row>
-    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="5">
         <v>1</v>
       </c>
-      <c r="B421" s="149"/>
+      <c r="B421" s="143"/>
       <c r="C421" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D421" s="13" t="str">
         <f t="shared" ref="D421" si="229">C421</f>
@@ -25687,11 +25697,11 @@
       </c>
       <c r="M421" s="11"/>
       <c r="N421" s="5" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B422" s="135" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="422" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B422" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C422" s="63" t="e" vm="25">
@@ -25723,8 +25733,8 @@
       <c r="L422" s="83"/>
       <c r="M422" s="11"/>
     </row>
-    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B423" s="136"/>
+    <row r="423" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B423" s="137"/>
       <c r="C423" s="63" t="s">
         <v>101</v>
       </c>
@@ -25759,14 +25769,14 @@
       <c r="L423" s="83"/>
       <c r="M423" s="11"/>
       <c r="N423" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="O423" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B424" s="201" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B424" s="149" t="s">
         <v>35</v>
       </c>
       <c r="C424" s="95" t="e" vm="25">
@@ -25798,8 +25808,8 @@
       <c r="L424" s="83"/>
       <c r="M424" s="123"/>
     </row>
-    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B425" s="202"/>
+    <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B425" s="150"/>
       <c r="C425" s="95" t="s">
         <v>101</v>
       </c>
@@ -25834,14 +25844,14 @@
       <c r="L425" s="83"/>
       <c r="M425" s="123"/>
       <c r="N425" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="O425" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="O425" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B426" s="201" t="s">
+    </row>
+    <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B426" s="149" t="s">
         <v>35</v>
       </c>
       <c r="C426" s="95" t="e" vm="25">
@@ -25873,8 +25883,8 @@
       <c r="L426" s="83"/>
       <c r="M426" s="123"/>
     </row>
-    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B427" s="202"/>
+    <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B427" s="150"/>
       <c r="C427" s="95" t="s">
         <v>101</v>
       </c>
@@ -25909,18 +25919,18 @@
       <c r="L427" s="83"/>
       <c r="M427" s="123"/>
       <c r="N427" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O427" s="5" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="428" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="5">
         <v>1</v>
       </c>
-      <c r="B428" s="135" t="s">
-        <v>386</v>
+      <c r="B428" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C428" s="16" t="e" vm="22">
         <v>#VALUE!</v>
@@ -25951,11 +25961,11 @@
       <c r="L428" s="83"/>
       <c r="M428" s="11"/>
     </row>
-    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="5">
         <v>1</v>
       </c>
-      <c r="B429" s="136"/>
+      <c r="B429" s="137"/>
       <c r="C429" s="23" t="s">
         <v>69</v>
       </c>
@@ -25993,11 +26003,11 @@
       </c>
       <c r="M429" s="11"/>
       <c r="N429" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B430" s="135" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="430" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B430" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C430" s="63" t="e" vm="25">
@@ -26029,8 +26039,8 @@
       <c r="L430" s="83"/>
       <c r="M430" s="11"/>
     </row>
-    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B431" s="136"/>
+    <row r="431" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B431" s="137"/>
       <c r="C431" s="63" t="s">
         <v>101</v>
       </c>
@@ -26065,14 +26075,14 @@
       <c r="L431" s="83"/>
       <c r="M431" s="11"/>
       <c r="N431" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="O431" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B432" s="201" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B432" s="149" t="s">
         <v>35</v>
       </c>
       <c r="C432" s="63" t="e" vm="25">
@@ -26104,8 +26114,8 @@
       <c r="L432" s="83"/>
       <c r="M432" s="123"/>
     </row>
-    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B433" s="202"/>
+    <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B433" s="150"/>
       <c r="C433" s="63" t="s">
         <v>101</v>
       </c>
@@ -26140,14 +26150,14 @@
       <c r="L433" s="83"/>
       <c r="M433" s="123"/>
       <c r="N433" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="O433" s="5" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B434" s="135" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="434" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B434" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C434" s="63" t="e" vm="25">
@@ -26179,8 +26189,8 @@
       <c r="L434" s="83"/>
       <c r="M434" s="11"/>
     </row>
-    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B435" s="136"/>
+    <row r="435" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B435" s="137"/>
       <c r="C435" s="63" t="s">
         <v>101</v>
       </c>
@@ -26215,14 +26225,14 @@
       <c r="L435" s="83"/>
       <c r="M435" s="11"/>
       <c r="N435" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="O435" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B436" s="148" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B436" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C436" s="52" t="e" vm="11">
@@ -26253,8 +26263,8 @@
       <c r="L436" s="83"/>
       <c r="M436" s="11"/>
     </row>
-    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B437" s="149"/>
+    <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B437" s="143"/>
       <c r="C437" s="52" t="s">
         <v>37</v>
       </c>
@@ -26289,13 +26299,13 @@
       <c r="L437" s="83"/>
       <c r="M437" s="11"/>
       <c r="N437" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O437" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B438" s="139" t="s">
         <v>32</v>
       </c>
@@ -26328,7 +26338,7 @@
       <c r="L438" s="83"/>
       <c r="M438" s="11"/>
     </row>
-    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B439" s="140"/>
       <c r="C439" s="63" t="s">
         <v>101</v>
@@ -26364,18 +26374,18 @@
       <c r="L439" s="83"/>
       <c r="M439" s="11"/>
       <c r="N439" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O439" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="440" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="5">
         <v>1</v>
       </c>
-      <c r="B440" s="205" t="s">
-        <v>383</v>
+      <c r="B440" s="145" t="s">
+        <v>382</v>
       </c>
       <c r="C440" s="101" t="e" vm="43">
         <v>#VALUE!</v>
@@ -26406,13 +26416,13 @@
       <c r="L440" s="83"/>
       <c r="M440" s="11"/>
     </row>
-    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="5">
         <v>1</v>
       </c>
-      <c r="B441" s="206"/>
+      <c r="B441" s="146"/>
       <c r="C441" s="101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D441" s="101" t="str">
         <f t="shared" ref="D441" si="243">C441</f>
@@ -26448,15 +26458,15 @@
       </c>
       <c r="M441" s="11"/>
       <c r="N441" s="5" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="442" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="5">
         <v>1</v>
       </c>
       <c r="B442" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C442" s="13" t="e" vm="43">
         <v>#VALUE!</v>
@@ -26487,13 +26497,13 @@
       <c r="L442" s="83"/>
       <c r="M442" s="11"/>
     </row>
-    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="5">
         <v>1</v>
       </c>
       <c r="B443" s="140"/>
       <c r="C443" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D443" s="13" t="str">
         <f t="shared" ref="D443" si="244">C443</f>
@@ -26529,11 +26539,11 @@
       </c>
       <c r="M443" s="11"/>
       <c r="N443" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B444" s="135" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="444" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B444" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C444" s="52" t="e" vm="11">
@@ -26564,8 +26574,8 @@
       <c r="L444" s="83"/>
       <c r="M444" s="11"/>
     </row>
-    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B445" s="136"/>
+    <row r="445" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B445" s="137"/>
       <c r="C445" s="99" t="s">
         <v>37</v>
       </c>
@@ -26600,14 +26610,14 @@
       <c r="L445" s="83"/>
       <c r="M445" s="11"/>
       <c r="N445" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="O445" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="O445" s="5" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B446" s="148" t="s">
+    </row>
+    <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B446" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C446" s="63" t="e" vm="25">
@@ -26639,8 +26649,8 @@
       <c r="L446" s="83"/>
       <c r="M446" s="11"/>
     </row>
-    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B447" s="149"/>
+    <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B447" s="143"/>
       <c r="C447" s="63" t="s">
         <v>101</v>
       </c>
@@ -26675,14 +26685,14 @@
       <c r="L447" s="83"/>
       <c r="M447" s="11"/>
       <c r="N447" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="O447" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B448" s="141" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B448" s="147" t="s">
         <v>33</v>
       </c>
       <c r="C448" s="63" t="e" vm="25">
@@ -26714,8 +26724,8 @@
       <c r="L448" s="83"/>
       <c r="M448" s="11"/>
     </row>
-    <row r="449" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B449" s="142"/>
+    <row r="449" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B449" s="148"/>
       <c r="C449" s="63" t="s">
         <v>101</v>
       </c>
@@ -26750,14 +26760,14 @@
       <c r="L449" s="83"/>
       <c r="M449" s="11"/>
       <c r="N449" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O449" s="5" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="450" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B450" s="204" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="450" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B450" s="144" t="s">
         <v>35</v>
       </c>
       <c r="C450" s="95" t="e" vm="25">
@@ -26789,8 +26799,8 @@
       <c r="L450" s="83"/>
       <c r="M450" s="11"/>
     </row>
-    <row r="451" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B451" s="136"/>
+    <row r="451" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B451" s="137"/>
       <c r="C451" s="95" t="s">
         <v>101</v>
       </c>
@@ -26825,14 +26835,14 @@
       <c r="L451" s="83"/>
       <c r="M451" s="11"/>
       <c r="N451" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="O451" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="O451" s="5" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="452" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B452" s="148" t="s">
+    </row>
+    <row r="452" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B452" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C452" s="13" t="e" vm="11">
@@ -26863,8 +26873,8 @@
       <c r="L452" s="83"/>
       <c r="M452" s="11"/>
     </row>
-    <row r="453" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B453" s="149"/>
+    <row r="453" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B453" s="143"/>
       <c r="C453" s="13" t="s">
         <v>37</v>
       </c>
@@ -26899,14 +26909,14 @@
       <c r="L453" s="83"/>
       <c r="M453" s="11"/>
       <c r="N453" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="O453" s="5" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="454" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B454" s="204" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="454" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B454" s="144" t="s">
         <v>35</v>
       </c>
       <c r="C454" s="95" t="e" vm="25">
@@ -26938,8 +26948,8 @@
       <c r="L454" s="83"/>
       <c r="M454" s="11"/>
     </row>
-    <row r="455" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B455" s="136"/>
+    <row r="455" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B455" s="137"/>
       <c r="C455" s="95" t="s">
         <v>101</v>
       </c>
@@ -26974,14 +26984,14 @@
       <c r="L455" s="83"/>
       <c r="M455" s="11"/>
       <c r="N455" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O455" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="456" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B456" s="148" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="456" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B456" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C456" s="52" t="e" vm="34">
@@ -27013,10 +27023,10 @@
       <c r="L456" s="83"/>
       <c r="M456" s="11"/>
     </row>
-    <row r="457" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B457" s="149"/>
+    <row r="457" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B457" s="143"/>
       <c r="C457" s="52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D457" s="52" t="str">
         <f t="shared" ref="D457" si="251">C457</f>
@@ -27049,14 +27059,14 @@
       <c r="L457" s="83"/>
       <c r="M457" s="11"/>
       <c r="N457" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O457" s="5" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="458" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B458" s="153" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="458" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B458" s="141" t="s">
         <v>42</v>
       </c>
       <c r="C458" s="52" t="e" vm="11">
@@ -27087,8 +27097,8 @@
       <c r="L458" s="83"/>
       <c r="M458" s="11"/>
     </row>
-    <row r="459" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B459" s="153"/>
+    <row r="459" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B459" s="141"/>
       <c r="C459" s="52" t="s">
         <v>37</v>
       </c>
@@ -27123,14 +27133,14 @@
       <c r="L459" s="83"/>
       <c r="M459" s="11"/>
       <c r="N459" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O459" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="460" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B460" s="148" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="460" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B460" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C460" s="52" t="e" vm="11">
@@ -27161,8 +27171,8 @@
       <c r="L460" s="83"/>
       <c r="M460" s="11"/>
     </row>
-    <row r="461" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B461" s="149"/>
+    <row r="461" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B461" s="143"/>
       <c r="C461" s="52" t="s">
         <v>37</v>
       </c>
@@ -27197,14 +27207,14 @@
       <c r="L461" s="83"/>
       <c r="M461" s="11"/>
       <c r="N461" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O461" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="462" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B462" s="148" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="462" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B462" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C462" s="95" t="e" vm="25">
@@ -27236,8 +27246,8 @@
       <c r="L462" s="83"/>
       <c r="M462" s="11"/>
     </row>
-    <row r="463" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B463" s="149"/>
+    <row r="463" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B463" s="143"/>
       <c r="C463" s="95" t="s">
         <v>101</v>
       </c>
@@ -27272,14 +27282,14 @@
       <c r="L463" s="83"/>
       <c r="M463" s="11"/>
       <c r="N463" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="O463" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="464" spans="2:15" x14ac:dyDescent="0.35">
-      <c r="B464" s="148" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="464" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B464" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C464" s="63" t="e" vm="11">
@@ -27310,8 +27320,8 @@
       <c r="L464" s="83"/>
       <c r="M464" s="11"/>
     </row>
-    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B465" s="149"/>
+    <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B465" s="143"/>
       <c r="C465" s="90" t="s">
         <v>37</v>
       </c>
@@ -27346,14 +27356,14 @@
       <c r="L465" s="83"/>
       <c r="M465" s="11"/>
       <c r="N465" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O465" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B466" s="135" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="466" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B466" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C466" s="52" t="e" vm="11">
@@ -27384,8 +27394,8 @@
       <c r="L466" s="83"/>
       <c r="M466" s="11"/>
     </row>
-    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B467" s="136"/>
+    <row r="467" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B467" s="137"/>
       <c r="C467" s="52" t="s">
         <v>37</v>
       </c>
@@ -27420,14 +27430,14 @@
       <c r="L467" s="83"/>
       <c r="M467" s="11"/>
       <c r="N467" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="O467" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B468" s="204" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B468" s="144" t="s">
         <v>35</v>
       </c>
       <c r="C468" s="63" t="e" vm="25">
@@ -27459,8 +27469,8 @@
       <c r="L468" s="83"/>
       <c r="M468" s="11"/>
     </row>
-    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B469" s="136"/>
+    <row r="469" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B469" s="137"/>
       <c r="C469" s="63" t="s">
         <v>101</v>
       </c>
@@ -27495,14 +27505,14 @@
       <c r="L469" s="83"/>
       <c r="M469" s="11"/>
       <c r="N469" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O469" s="5" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B470" s="153" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B470" s="141" t="s">
         <v>42</v>
       </c>
       <c r="C470" s="52" t="e" vm="11">
@@ -27533,8 +27543,8 @@
       <c r="L470" s="83"/>
       <c r="M470" s="11"/>
     </row>
-    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B471" s="153"/>
+    <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B471" s="141"/>
       <c r="C471" s="52" t="s">
         <v>37</v>
       </c>
@@ -27569,14 +27579,14 @@
       <c r="L471" s="83"/>
       <c r="M471" s="11"/>
       <c r="N471" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="O471" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B472" s="135" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="472" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B472" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C472" s="52" t="e" vm="11">
@@ -27607,8 +27617,8 @@
       <c r="L472" s="83"/>
       <c r="M472" s="11"/>
     </row>
-    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B473" s="136"/>
+    <row r="473" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B473" s="137"/>
       <c r="C473" s="52" t="s">
         <v>37</v>
       </c>
@@ -27643,14 +27653,14 @@
       <c r="L473" s="83"/>
       <c r="M473" s="11"/>
       <c r="N473" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O473" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B474" s="148" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B474" s="142" t="s">
         <v>32</v>
       </c>
       <c r="C474" s="52" t="e" vm="34">
@@ -27682,10 +27692,10 @@
       <c r="L474" s="83"/>
       <c r="M474" s="11"/>
     </row>
-    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B475" s="149"/>
+    <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B475" s="143"/>
       <c r="C475" s="52" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D475" s="52" t="str">
         <f t="shared" ref="D475" si="261">C475</f>
@@ -27718,18 +27728,18 @@
       <c r="L475" s="83"/>
       <c r="M475" s="11"/>
       <c r="N475" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O475" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="5">
         <v>1</v>
       </c>
       <c r="B476" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C476" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -27759,7 +27769,7 @@
       <c r="L476" s="83"/>
       <c r="M476" s="11"/>
     </row>
-    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="5">
         <v>1</v>
       </c>
@@ -27801,10 +27811,10 @@
       </c>
       <c r="M477" s="11"/>
       <c r="N477" s="5" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B478" s="139" t="s">
         <v>32</v>
       </c>
@@ -27837,7 +27847,7 @@
       <c r="L478" s="83"/>
       <c r="M478" s="11"/>
     </row>
-    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B479" s="140"/>
       <c r="C479" s="63" t="s">
         <v>101</v>
@@ -27873,18 +27883,18 @@
       <c r="L479" s="83"/>
       <c r="M479" s="11"/>
       <c r="N479" s="5" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O479" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="480" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="5">
         <v>1</v>
       </c>
-      <c r="B480" s="150" t="s">
-        <v>308</v>
+      <c r="B480" s="166" t="s">
+        <v>307</v>
       </c>
       <c r="C480" s="13" t="e" vm="43">
         <v>#VALUE!</v>
@@ -27915,13 +27925,13 @@
       <c r="L480" s="83"/>
       <c r="M480" s="11"/>
     </row>
-    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="5">
         <v>1</v>
       </c>
-      <c r="B481" s="149"/>
+      <c r="B481" s="143"/>
       <c r="C481" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D481" s="13" t="str">
         <f t="shared" ref="D481" si="264">C481</f>
@@ -27957,15 +27967,15 @@
       </c>
       <c r="M481" s="11"/>
       <c r="N481" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="482" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="5">
         <v>1</v>
       </c>
-      <c r="B482" s="151" t="s">
-        <v>382</v>
+      <c r="B482" s="202" t="s">
+        <v>381</v>
       </c>
       <c r="C482" s="13" t="e" vm="43">
         <v>#VALUE!</v>
@@ -27996,13 +28006,13 @@
       <c r="L482" s="83"/>
       <c r="M482" s="11"/>
     </row>
-    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="5">
         <v>1</v>
       </c>
-      <c r="B483" s="152"/>
+      <c r="B483" s="203"/>
       <c r="C483" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D483" s="13" t="str">
         <f t="shared" ref="D483" si="265">C483</f>
@@ -28038,11 +28048,11 @@
       </c>
       <c r="M483" s="11"/>
       <c r="N483" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B484" s="155" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B484" s="204" t="s">
         <v>90</v>
       </c>
       <c r="C484" s="52" t="e" vm="44">
@@ -28074,10 +28084,10 @@
       <c r="L484" s="83"/>
       <c r="M484" s="11"/>
     </row>
-    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B485" s="155"/>
+    <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B485" s="204"/>
       <c r="C485" s="52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D485" s="52" t="str">
         <f t="shared" ref="D485:D491" si="267">C485</f>
@@ -28110,18 +28120,18 @@
       <c r="L485" s="83"/>
       <c r="M485" s="11"/>
       <c r="N485" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O485" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="486" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="5">
         <v>1</v>
       </c>
-      <c r="B486" s="148" t="s">
-        <v>383</v>
+      <c r="B486" s="142" t="s">
+        <v>382</v>
       </c>
       <c r="C486" s="16" t="e" vm="25">
         <v>#VALUE!</v>
@@ -28152,11 +28162,11 @@
       <c r="L486" s="83"/>
       <c r="M486" s="11"/>
     </row>
-    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="5">
         <v>1</v>
       </c>
-      <c r="B487" s="149"/>
+      <c r="B487" s="143"/>
       <c r="C487" s="16" t="s">
         <v>101</v>
       </c>
@@ -28194,18 +28204,18 @@
       </c>
       <c r="M487" s="11"/>
       <c r="N487" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O487" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="488" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="5">
         <v>1</v>
       </c>
       <c r="B488" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C488" s="81" t="e" vm="25">
         <v>#VALUE!</v>
@@ -28236,7 +28246,7 @@
       <c r="L488" s="83"/>
       <c r="M488" s="11"/>
     </row>
-    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="5">
         <v>1</v>
       </c>
@@ -28278,13 +28288,13 @@
       </c>
       <c r="M489" s="11"/>
       <c r="N489" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O489" s="5" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B490" s="139" t="s">
         <v>32</v>
       </c>
@@ -28317,10 +28327,10 @@
       <c r="L490" s="128"/>
       <c r="M490" s="11"/>
     </row>
-    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B491" s="140"/>
       <c r="C491" s="108" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D491" s="95" t="str">
         <f t="shared" si="267"/>
@@ -28353,18 +28363,18 @@
       <c r="L491" s="128"/>
       <c r="M491" s="11"/>
       <c r="N491" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O491" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="492" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="5">
         <v>1</v>
       </c>
-      <c r="B492" s="150" t="s">
-        <v>308</v>
+      <c r="B492" s="166" t="s">
+        <v>307</v>
       </c>
       <c r="C492" s="81" t="e" vm="46">
         <v>#VALUE!</v>
@@ -28395,13 +28405,13 @@
       <c r="L492" s="128"/>
       <c r="M492" s="11"/>
     </row>
-    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="5">
         <v>1</v>
       </c>
-      <c r="B493" s="149"/>
+      <c r="B493" s="143"/>
       <c r="C493" s="105" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D493" s="81" t="str">
         <f t="shared" si="270"/>
@@ -28435,15 +28445,15 @@
       <c r="L493" s="128"/>
       <c r="M493" s="11"/>
       <c r="N493" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="494" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="5">
         <v>1</v>
       </c>
-      <c r="B494" s="150" t="s">
-        <v>308</v>
+      <c r="B494" s="166" t="s">
+        <v>307</v>
       </c>
       <c r="C494" s="81" t="e" vm="46">
         <v>#VALUE!</v>
@@ -28474,13 +28484,13 @@
       <c r="L494" s="128"/>
       <c r="M494" s="11"/>
     </row>
-    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="5">
         <v>1</v>
       </c>
-      <c r="B495" s="149"/>
+      <c r="B495" s="143"/>
       <c r="C495" s="105" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D495" s="81" t="str">
         <f t="shared" si="272"/>
@@ -28514,11 +28524,11 @@
       <c r="L495" s="128"/>
       <c r="M495" s="11"/>
       <c r="N495" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B496" s="143" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B496" s="151" t="s">
         <v>32</v>
       </c>
       <c r="C496" s="52" t="e" vm="44">
@@ -28550,10 +28560,10 @@
       <c r="L496" s="128"/>
       <c r="M496" s="11"/>
     </row>
-    <row r="497" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B497" s="143"/>
+    <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B497" s="151"/>
       <c r="C497" s="52" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D497" s="52" t="str">
         <f t="shared" ref="D497" si="274">C497</f>
@@ -28586,13 +28596,13 @@
       <c r="L497" s="128"/>
       <c r="M497" s="11"/>
       <c r="N497" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="O497" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="O497" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="498" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B498" s="139" t="s">
         <v>32</v>
       </c>
@@ -28624,7 +28634,7 @@
       <c r="L498" s="128"/>
       <c r="M498" s="11"/>
     </row>
-    <row r="499" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B499" s="140"/>
       <c r="C499" s="52" t="s">
         <v>37</v>
@@ -28660,18 +28670,18 @@
       <c r="L499" s="128"/>
       <c r="M499" s="11"/>
       <c r="N499" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O499" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="5">
         <v>1</v>
       </c>
       <c r="B500" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C500" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -28701,7 +28711,7 @@
       <c r="L500" s="128"/>
       <c r="M500" s="11"/>
     </row>
-    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="5">
         <v>1</v>
       </c>
@@ -28743,10 +28753,10 @@
       </c>
       <c r="M501" s="11"/>
       <c r="N501" s="5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="502" spans="1:15" x14ac:dyDescent="0.35">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B502" s="139" t="s">
         <v>32</v>
       </c>
@@ -28778,7 +28788,7 @@
       <c r="L502" s="128"/>
       <c r="M502" s="11"/>
     </row>
-    <row r="503" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="B503" s="140"/>
       <c r="C503" s="52" t="s">
         <v>37</v>
@@ -28814,15 +28824,15 @@
       <c r="L503" s="128"/>
       <c r="M503" s="11"/>
       <c r="N503" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="O503" s="5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B504" s="160" t="s">
         <v>316</v>
-      </c>
-      <c r="O503" s="5" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="504" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B504" s="154" t="s">
-        <v>317</v>
       </c>
       <c r="C504" s="78" t="e" vm="47">
         <v>#VALUE!</v>
@@ -28853,10 +28863,10 @@
       <c r="L504" s="128"/>
       <c r="M504" s="11"/>
     </row>
-    <row r="505" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B505" s="154"/>
+    <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B505" s="160"/>
       <c r="C505" s="78" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D505" s="53" t="str">
         <f t="shared" ref="D505" si="280">C505</f>
@@ -28889,18 +28899,18 @@
       <c r="L505" s="128"/>
       <c r="M505" s="11"/>
       <c r="N505" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="O505" s="5" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="506" spans="1:15" x14ac:dyDescent="0.35">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="506" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="5">
         <v>1</v>
       </c>
-      <c r="B506" s="146" t="s">
-        <v>381</v>
+      <c r="B506" s="158" t="s">
+        <v>380</v>
       </c>
       <c r="C506" s="101" t="e" vm="43">
         <v>#VALUE!</v>
@@ -28931,13 +28941,13 @@
       <c r="L506" s="128"/>
       <c r="M506" s="11"/>
     </row>
-    <row r="507" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="5">
         <v>1</v>
       </c>
-      <c r="B507" s="147"/>
+      <c r="B507" s="159"/>
       <c r="C507" s="101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D507" s="101" t="str">
         <f t="shared" ref="D507" si="281">C507</f>
@@ -28973,11 +28983,11 @@
       </c>
       <c r="M507" s="11"/>
       <c r="N507" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="508" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B508" s="153" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B508" s="141" t="s">
         <v>42</v>
       </c>
       <c r="C508" s="52" t="e" vm="11">
@@ -29008,8 +29018,8 @@
       <c r="L508" s="128"/>
       <c r="M508" s="11"/>
     </row>
-    <row r="509" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B509" s="153"/>
+    <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B509" s="141"/>
       <c r="C509" s="52" t="s">
         <v>37</v>
       </c>
@@ -29044,18 +29054,18 @@
       <c r="L509" s="128"/>
       <c r="M509" s="11"/>
       <c r="N509" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O509" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="5">
         <v>1</v>
       </c>
-      <c r="B510" s="141" t="s">
-        <v>382</v>
+      <c r="B510" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C510" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -29085,11 +29095,11 @@
       <c r="L510" s="83"/>
       <c r="M510" s="11"/>
     </row>
-    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="5">
         <v>1</v>
       </c>
-      <c r="B511" s="142"/>
+      <c r="B511" s="148"/>
       <c r="C511" s="86" t="s">
         <v>37</v>
       </c>
@@ -29127,11 +29137,11 @@
       </c>
       <c r="M511" s="11"/>
       <c r="N511" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="512" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B512" s="153" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B512" s="141" t="s">
         <v>42</v>
       </c>
       <c r="C512" s="63" t="e" vm="11">
@@ -29162,8 +29172,8 @@
       <c r="L512" s="128"/>
       <c r="M512" s="11"/>
     </row>
-    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B513" s="153"/>
+    <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B513" s="141"/>
       <c r="C513" s="90" t="s">
         <v>37</v>
       </c>
@@ -29198,14 +29208,14 @@
       <c r="L513" s="128"/>
       <c r="M513" s="11"/>
       <c r="N513" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="O513" s="5" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B514" s="153" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B514" s="141" t="s">
         <v>42</v>
       </c>
       <c r="C514" s="63" t="e" vm="11">
@@ -29236,8 +29246,8 @@
       <c r="L514" s="128"/>
       <c r="M514" s="11"/>
     </row>
-    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B515" s="153"/>
+    <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B515" s="141"/>
       <c r="C515" s="90" t="s">
         <v>37</v>
       </c>
@@ -29272,14 +29282,14 @@
       <c r="L515" s="128"/>
       <c r="M515" s="11"/>
       <c r="N515" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O515" s="5" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B516" s="135" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="516" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B516" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C516" s="52" t="e" vm="11">
@@ -29310,8 +29320,8 @@
       <c r="L516" s="128"/>
       <c r="M516" s="11"/>
     </row>
-    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B517" s="136"/>
+    <row r="517" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B517" s="137"/>
       <c r="C517" s="52" t="s">
         <v>37</v>
       </c>
@@ -29346,18 +29356,18 @@
       <c r="L517" s="128"/>
       <c r="M517" s="11"/>
       <c r="N517" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="O517" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="O517" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="5">
         <v>1</v>
       </c>
       <c r="B518" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C518" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -29387,7 +29397,7 @@
       <c r="L518" s="83"/>
       <c r="M518" s="11"/>
     </row>
-    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="5">
         <v>1</v>
       </c>
@@ -29429,15 +29439,15 @@
       </c>
       <c r="M519" s="11"/>
       <c r="N519" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="520" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="5">
         <v>1</v>
       </c>
-      <c r="B520" s="148" t="s">
-        <v>383</v>
+      <c r="B520" s="142" t="s">
+        <v>382</v>
       </c>
       <c r="C520" s="101" t="e" vm="43">
         <v>#VALUE!</v>
@@ -29468,13 +29478,13 @@
       <c r="L520" s="128"/>
       <c r="M520" s="11"/>
     </row>
-    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="5">
         <v>1</v>
       </c>
-      <c r="B521" s="149"/>
+      <c r="B521" s="143"/>
       <c r="C521" s="101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D521" s="101" t="str">
         <f t="shared" ref="D521" si="291">C521</f>
@@ -29510,11 +29520,11 @@
       </c>
       <c r="M521" s="11"/>
       <c r="N521" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B522" s="135" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="522" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B522" s="136" t="s">
         <v>35</v>
       </c>
       <c r="C522" s="52" t="e" vm="11">
@@ -29545,8 +29555,8 @@
       <c r="L522" s="128"/>
       <c r="M522" s="11"/>
     </row>
-    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="B523" s="136"/>
+    <row r="523" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B523" s="137"/>
       <c r="C523" s="52" t="s">
         <v>37</v>
       </c>
@@ -29581,18 +29591,18 @@
       <c r="L523" s="128"/>
       <c r="M523" s="11"/>
       <c r="N523" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="O523" s="5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="524" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="5">
         <v>1</v>
       </c>
       <c r="B524" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C524" s="81" t="e" vm="45">
         <v>#VALUE!</v>
@@ -29625,13 +29635,13 @@
       <c r="L524" s="128"/>
       <c r="M524" s="11"/>
     </row>
-    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="5">
         <v>1</v>
       </c>
       <c r="B525" s="140"/>
       <c r="C525" s="105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D525" s="81" t="str">
         <f t="shared" si="293"/>
@@ -29667,18 +29677,18 @@
       </c>
       <c r="M525" s="11"/>
       <c r="N525" s="5" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O525" s="5" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="526" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="5">
         <v>1</v>
       </c>
-      <c r="B526" s="148" t="s">
-        <v>383</v>
+      <c r="B526" s="142" t="s">
+        <v>382</v>
       </c>
       <c r="C526" s="13" t="e" vm="22">
         <v>#VALUE!</v>
@@ -29709,11 +29719,11 @@
       <c r="L526" s="128"/>
       <c r="M526" s="11"/>
     </row>
-    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="5">
         <v>1</v>
       </c>
-      <c r="B527" s="149"/>
+      <c r="B527" s="143"/>
       <c r="C527" s="15" t="s">
         <v>69</v>
       </c>
@@ -29751,15 +29761,15 @@
       </c>
       <c r="M527" s="11"/>
       <c r="N527" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="5">
         <v>1</v>
       </c>
-      <c r="B528" s="135" t="s">
-        <v>386</v>
+      <c r="B528" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C528" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -29789,11 +29799,11 @@
       <c r="L528" s="83"/>
       <c r="M528" s="11"/>
     </row>
-    <row r="529" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="5">
         <v>1</v>
       </c>
-      <c r="B529" s="136"/>
+      <c r="B529" s="137"/>
       <c r="C529" s="86" t="s">
         <v>37</v>
       </c>
@@ -29831,7 +29841,7 @@
       </c>
       <c r="M529" s="11"/>
       <c r="N529" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AC529" s="5">
         <v>1.7500000000000002E-2</v>
@@ -29844,9 +29854,9 @@
         <v>0.52500000000000002</v>
       </c>
     </row>
-    <row r="530" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B530" s="135" t="s">
-        <v>386</v>
+    <row r="530" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B530" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C530" s="129" t="e" vm="25">
         <v>#VALUE!</v>
@@ -29877,8 +29887,8 @@
       <c r="L530" s="83"/>
       <c r="M530" s="11"/>
     </row>
-    <row r="531" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B531" s="136"/>
+    <row r="531" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B531" s="137"/>
       <c r="C531" s="131" t="s">
         <v>101</v>
       </c>
@@ -29917,15 +29927,15 @@
         <v>46058</v>
       </c>
       <c r="N531" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="532" spans="1:31" x14ac:dyDescent="0.35">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="532" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="13">
         <v>1</v>
       </c>
-      <c r="B532" s="138" t="s">
-        <v>377</v>
+      <c r="B532" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C532" s="117" t="e" vm="48">
         <v>#VALUE!</v>
@@ -29956,13 +29966,13 @@
       <c r="L532" s="128"/>
       <c r="M532" s="127"/>
     </row>
-    <row r="533" spans="1:31" ht="43.2" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:31" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="13">
         <v>1</v>
       </c>
-      <c r="B533" s="138"/>
+      <c r="B533" s="185"/>
       <c r="C533" s="117" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D533" s="118" t="str">
         <f t="shared" ref="D533" si="296">C533</f>
@@ -29998,18 +30008,18 @@
       </c>
       <c r="M533" s="127"/>
       <c r="N533" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P533" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="534" spans="1:31" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="534" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="5">
         <v>1</v>
       </c>
-      <c r="B534" s="141" t="s">
-        <v>382</v>
+      <c r="B534" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C534" s="114" t="e" vm="22">
         <v>#VALUE!</v>
@@ -30040,11 +30050,11 @@
       <c r="L534" s="128"/>
       <c r="M534" s="11"/>
     </row>
-    <row r="535" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="5">
         <v>1</v>
       </c>
-      <c r="B535" s="142"/>
+      <c r="B535" s="148"/>
       <c r="C535" s="23" t="s">
         <v>69</v>
       </c>
@@ -30082,15 +30092,15 @@
       </c>
       <c r="M535" s="11"/>
       <c r="N535" s="5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="536" spans="1:31" x14ac:dyDescent="0.35">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="536" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="5">
         <v>1</v>
       </c>
-      <c r="B536" s="135" t="s">
-        <v>386</v>
+      <c r="B536" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C536" s="81" t="e" vm="45">
         <v>#VALUE!</v>
@@ -30121,13 +30131,13 @@
       <c r="L536" s="128"/>
       <c r="M536" s="11"/>
     </row>
-    <row r="537" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="5">
         <v>1</v>
       </c>
-      <c r="B537" s="136"/>
+      <c r="B537" s="137"/>
       <c r="C537" s="105" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D537" s="81" t="str">
         <f t="shared" si="297"/>
@@ -30163,15 +30173,15 @@
       </c>
       <c r="M537" s="11"/>
       <c r="N537" s="5" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="538" spans="1:31" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="538" spans="1:31" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A538" s="5">
         <v>1</v>
       </c>
-      <c r="B538" s="141" t="s">
-        <v>382</v>
+      <c r="B538" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C538" s="16" t="e" vm="25">
         <v>#VALUE!</v>
@@ -30202,11 +30212,11 @@
       <c r="L538" s="83"/>
       <c r="M538" s="11"/>
     </row>
-    <row r="539" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="5">
         <v>1</v>
       </c>
-      <c r="B539" s="142"/>
+      <c r="B539" s="148"/>
       <c r="C539" s="16" t="s">
         <v>101</v>
       </c>
@@ -30244,15 +30254,15 @@
       </c>
       <c r="M539" s="11"/>
       <c r="N539" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="540" spans="1:31" x14ac:dyDescent="0.35">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="540" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="5">
         <v>1</v>
       </c>
       <c r="B540" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C540" s="16" t="e" vm="49">
         <v>#VALUE!</v>
@@ -30283,13 +30293,13 @@
       <c r="L540" s="128"/>
       <c r="M540" s="11"/>
     </row>
-    <row r="541" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="5">
         <v>1</v>
       </c>
       <c r="B541" s="140"/>
       <c r="C541" s="86" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D541" s="86" t="str">
         <f t="shared" ref="D541" si="299">C541</f>
@@ -30325,11 +30335,11 @@
       </c>
       <c r="M541" s="11"/>
       <c r="N541" s="5" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="542" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B542" s="148" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="542" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B542" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C542" s="52" t="e" vm="11">
@@ -30360,8 +30370,8 @@
       <c r="L542" s="128"/>
       <c r="M542" s="11"/>
     </row>
-    <row r="543" spans="1:31" x14ac:dyDescent="0.35">
-      <c r="B543" s="149"/>
+    <row r="543" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B543" s="143"/>
       <c r="C543" s="52" t="s">
         <v>37</v>
       </c>
@@ -30396,18 +30406,18 @@
       <c r="L543" s="128"/>
       <c r="M543" s="11"/>
       <c r="N543" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O543" s="5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="544" spans="1:31" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="544" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="5">
         <v>1</v>
       </c>
       <c r="B544" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C544" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -30437,7 +30447,7 @@
       <c r="L544" s="83"/>
       <c r="M544" s="11"/>
     </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="5">
         <v>1</v>
       </c>
@@ -30479,11 +30489,11 @@
       </c>
       <c r="M545" s="11"/>
       <c r="N545" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B546" s="148" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B546" s="142" t="s">
         <v>44</v>
       </c>
       <c r="C546" s="52" t="e" vm="11">
@@ -30514,8 +30524,8 @@
       <c r="L546" s="128"/>
       <c r="M546" s="11"/>
     </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B547" s="149"/>
+    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="B547" s="143"/>
       <c r="C547" s="99" t="s">
         <v>37</v>
       </c>
@@ -30550,18 +30560,18 @@
       <c r="L547" s="128"/>
       <c r="M547" s="11"/>
       <c r="N547" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="O547" s="5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="13">
         <v>1</v>
       </c>
-      <c r="B548" s="138" t="s">
-        <v>377</v>
+      <c r="B548" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C548" s="107" t="e" vm="48">
         <v>#VALUE!</v>
@@ -30592,13 +30602,13 @@
       <c r="L548" s="128"/>
       <c r="M548" s="127"/>
     </row>
-    <row r="549" spans="1:16" ht="43.2" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="13">
         <v>1</v>
       </c>
-      <c r="B549" s="138"/>
+      <c r="B549" s="185"/>
       <c r="C549" s="107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D549" s="106" t="str">
         <f t="shared" ref="D549" si="304">C549</f>
@@ -30634,18 +30644,18 @@
       </c>
       <c r="M549" s="127"/>
       <c r="N549" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="P549" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="5">
         <v>1</v>
       </c>
-      <c r="B550" s="135" t="s">
-        <v>386</v>
+      <c r="B550" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C550" s="114" t="e" vm="11">
         <v>#VALUE!</v>
@@ -30675,11 +30685,11 @@
       <c r="L550" s="83"/>
       <c r="M550" s="11"/>
     </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="5">
         <v>1</v>
       </c>
-      <c r="B551" s="136"/>
+      <c r="B551" s="137"/>
       <c r="C551" s="86" t="s">
         <v>37</v>
       </c>
@@ -30717,15 +30727,15 @@
       </c>
       <c r="M551" s="11"/>
       <c r="N551" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="5">
         <v>1</v>
       </c>
-      <c r="B552" s="135" t="s">
-        <v>386</v>
+      <c r="B552" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C552" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -30755,11 +30765,11 @@
       <c r="L552" s="83"/>
       <c r="M552" s="11"/>
     </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="5">
         <v>1</v>
       </c>
-      <c r="B553" s="136"/>
+      <c r="B553" s="137"/>
       <c r="C553" s="13" t="s">
         <v>37</v>
       </c>
@@ -30797,15 +30807,15 @@
       </c>
       <c r="M553" s="11"/>
       <c r="N553" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="5">
         <v>1</v>
       </c>
       <c r="B554" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C554" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -30835,7 +30845,7 @@
       <c r="L554" s="83"/>
       <c r="M554" s="11"/>
     </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="5">
         <v>1</v>
       </c>
@@ -30877,15 +30887,15 @@
       </c>
       <c r="M555" s="11"/>
       <c r="N555" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="13">
         <v>1</v>
       </c>
-      <c r="B556" s="143" t="s">
-        <v>360</v>
+      <c r="B556" s="151" t="s">
+        <v>359</v>
       </c>
       <c r="C556" s="117" t="e" vm="48">
         <v>#VALUE!</v>
@@ -30916,13 +30926,13 @@
       <c r="L556" s="128"/>
       <c r="M556" s="127"/>
     </row>
-    <row r="557" spans="1:16" ht="72" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="13">
         <v>1</v>
       </c>
-      <c r="B557" s="143"/>
+      <c r="B557" s="151"/>
       <c r="C557" s="117" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D557" s="118" t="str">
         <f t="shared" ref="D557:D559" si="309">C557</f>
@@ -30958,15 +30968,15 @@
       </c>
       <c r="M557" s="127"/>
       <c r="N557" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="P557" s="6" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B558" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C558" s="133" t="e" vm="25">
         <v>#VALUE!</v>
@@ -30997,7 +31007,7 @@
       <c r="L558" s="83"/>
       <c r="M558" s="11"/>
     </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B559" s="140"/>
       <c r="C559" s="63" t="s">
         <v>101</v>
@@ -31037,15 +31047,15 @@
         <v>46076</v>
       </c>
       <c r="N559" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="5">
         <v>1</v>
       </c>
       <c r="B560" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C560" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -31075,7 +31085,7 @@
       <c r="L560" s="83"/>
       <c r="M560" s="11"/>
     </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="5">
         <v>1</v>
       </c>
@@ -31117,18 +31127,18 @@
       </c>
       <c r="M561" s="11"/>
       <c r="N561" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="O561" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="13">
         <v>1</v>
       </c>
-      <c r="B562" s="138" t="s">
-        <v>377</v>
+      <c r="B562" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C562" s="107" t="e" vm="48">
         <v>#VALUE!</v>
@@ -31159,13 +31169,13 @@
       <c r="L562" s="83"/>
       <c r="M562" s="127"/>
     </row>
-    <row r="563" spans="1:16" ht="72" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:16" ht="72" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="13">
         <v>1</v>
       </c>
-      <c r="B563" s="138"/>
+      <c r="B563" s="185"/>
       <c r="C563" s="107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D563" s="106" t="str">
         <f t="shared" ref="D563" si="312">C563</f>
@@ -31201,18 +31211,18 @@
       </c>
       <c r="M563" s="127"/>
       <c r="N563" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P563" s="6" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="13">
         <v>1</v>
       </c>
-      <c r="B564" s="137" t="s">
-        <v>362</v>
+      <c r="B564" s="135" t="s">
+        <v>361</v>
       </c>
       <c r="C564" s="117" t="e" vm="48">
         <v>#VALUE!</v>
@@ -31243,13 +31253,13 @@
       <c r="L564" s="83"/>
       <c r="M564" s="127"/>
     </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="13">
         <v>1</v>
       </c>
-      <c r="B565" s="137"/>
+      <c r="B565" s="135"/>
       <c r="C565" s="117" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D565" s="118" t="str">
         <f t="shared" ref="D565" si="314">C565</f>
@@ -31285,10 +31295,10 @@
       </c>
       <c r="M565" s="127"/>
       <c r="N565" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B566" s="139" t="s">
         <v>32</v>
       </c>
@@ -31321,10 +31331,10 @@
       <c r="L566" s="83"/>
       <c r="M566" s="11"/>
     </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B567" s="140"/>
       <c r="C567" s="90" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D567" s="90" t="str">
         <f t="shared" ref="D567" si="315">C567</f>
@@ -31357,18 +31367,18 @@
       <c r="L567" s="83"/>
       <c r="M567" s="11"/>
       <c r="N567" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="O567" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="13">
         <v>1</v>
       </c>
-      <c r="B568" s="138" t="s">
-        <v>377</v>
+      <c r="B568" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C568" s="107" t="e" vm="48">
         <v>#VALUE!</v>
@@ -31399,13 +31409,13 @@
       <c r="L568" s="83"/>
       <c r="M568" s="127"/>
     </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="13">
         <v>1</v>
       </c>
-      <c r="B569" s="138"/>
+      <c r="B569" s="185"/>
       <c r="C569" s="107" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D569" s="106" t="str">
         <f t="shared" ref="D569" si="316">C569</f>
@@ -31441,16 +31451,16 @@
       </c>
       <c r="M569" s="127"/>
       <c r="N569" s="5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P569" s="6"/>
     </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="5">
         <v>1</v>
       </c>
-      <c r="B570" s="141" t="s">
-        <v>382</v>
+      <c r="B570" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C570" s="13" t="e" vm="44">
         <v>#VALUE!</v>
@@ -31481,13 +31491,13 @@
       <c r="L570" s="83"/>
       <c r="M570" s="11"/>
     </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="5">
         <v>1</v>
       </c>
-      <c r="B571" s="142"/>
+      <c r="B571" s="148"/>
       <c r="C571" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D571" s="13" t="str">
         <f t="shared" ref="D571" si="317">C571</f>
@@ -31523,10 +31533,10 @@
       </c>
       <c r="M571" s="11"/>
       <c r="N571" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B572" s="139" t="s">
         <v>32</v>
       </c>
@@ -31559,10 +31569,10 @@
       <c r="L572" s="83"/>
       <c r="M572" s="11"/>
     </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B573" s="140"/>
       <c r="C573" s="52" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D573" s="52" t="str">
         <f t="shared" ref="D573" si="319">C573</f>
@@ -31595,18 +31605,18 @@
       <c r="L573" s="83"/>
       <c r="M573" s="11"/>
       <c r="N573" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="O573" s="5" t="s">
         <v>373</v>
       </c>
-      <c r="O573" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="5">
         <v>1</v>
       </c>
-      <c r="B574" s="141" t="s">
-        <v>382</v>
+      <c r="B574" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C574" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -31636,11 +31646,11 @@
       <c r="L574" s="83"/>
       <c r="M574" s="11"/>
     </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="5">
         <v>1</v>
       </c>
-      <c r="B575" s="142"/>
+      <c r="B575" s="148"/>
       <c r="C575" s="86" t="s">
         <v>37</v>
       </c>
@@ -31678,15 +31688,15 @@
       </c>
       <c r="M575" s="11"/>
       <c r="N575" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="5">
         <v>1</v>
       </c>
-      <c r="B576" s="141" t="s">
-        <v>382</v>
+      <c r="B576" s="147" t="s">
+        <v>381</v>
       </c>
       <c r="C576" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -31716,11 +31726,11 @@
       <c r="L576" s="11"/>
       <c r="M576" s="11"/>
     </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="5">
         <v>1</v>
       </c>
-      <c r="B577" s="142"/>
+      <c r="B577" s="148"/>
       <c r="C577" s="13" t="s">
         <v>37</v>
       </c>
@@ -31758,15 +31768,15 @@
       </c>
       <c r="M577" s="11"/>
       <c r="N577" s="5" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="13">
         <v>1</v>
       </c>
-      <c r="B578" s="138" t="s">
-        <v>377</v>
+      <c r="B578" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C578" s="107" t="e" vm="50">
         <v>#VALUE!</v>
@@ -31797,13 +31807,13 @@
       <c r="L578" s="127"/>
       <c r="M578" s="127"/>
     </row>
-    <row r="579" spans="1:16" ht="43.2" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="13">
         <v>1</v>
       </c>
-      <c r="B579" s="138"/>
+      <c r="B579" s="185"/>
       <c r="C579" s="107" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D579" s="106" t="str">
         <f t="shared" ref="D579" si="323">C579</f>
@@ -31837,21 +31847,21 @@
       <c r="L579" s="127"/>
       <c r="M579" s="127"/>
       <c r="N579" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="O579" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="O579" s="5" t="s">
-        <v>379</v>
-      </c>
       <c r="P579" s="6" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="13">
         <v>1</v>
       </c>
-      <c r="B580" s="138" t="s">
-        <v>377</v>
+      <c r="B580" s="185" t="s">
+        <v>376</v>
       </c>
       <c r="C580" s="107" t="e" vm="51">
         <v>#VALUE!</v>
@@ -31882,13 +31892,13 @@
       <c r="L580" s="127"/>
       <c r="M580" s="127"/>
     </row>
-    <row r="581" spans="1:16" ht="28.8" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="13">
         <v>1</v>
       </c>
-      <c r="B581" s="138"/>
+      <c r="B581" s="185"/>
       <c r="C581" s="107" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D581" s="106" t="str">
         <f t="shared" ref="D581" si="325">C581</f>
@@ -31924,12 +31934,12 @@
       </c>
       <c r="M581" s="127"/>
       <c r="N581" s="6" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B582" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C582" s="63" t="e" vm="36">
         <v>#VALUE!</v>
@@ -31960,10 +31970,10 @@
       <c r="L582" s="11"/>
       <c r="M582" s="11"/>
     </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B583" s="140"/>
       <c r="C583" s="90" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D583" s="90" t="str">
         <f t="shared" ref="D583" si="326">C583</f>
@@ -31996,18 +32006,18 @@
       <c r="L583" s="11"/>
       <c r="M583" s="11"/>
       <c r="N583" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="O583" s="5" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="5">
         <v>1</v>
       </c>
-      <c r="B584" s="146" t="s">
-        <v>381</v>
+      <c r="B584" s="158" t="s">
+        <v>380</v>
       </c>
       <c r="C584" s="101" t="e" vm="43">
         <v>#VALUE!</v>
@@ -32038,13 +32048,13 @@
       <c r="L584" s="11"/>
       <c r="M584" s="11"/>
     </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="5">
         <v>1</v>
       </c>
-      <c r="B585" s="147"/>
+      <c r="B585" s="159"/>
       <c r="C585" s="101" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D585" s="101" t="str">
         <f t="shared" ref="D585" si="327">C585</f>
@@ -32080,14 +32090,14 @@
       </c>
       <c r="M585" s="11"/>
       <c r="N585" s="5" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="5">
         <v>1</v>
       </c>
-      <c r="B586" s="144" t="s">
+      <c r="B586" s="205" t="s">
         <v>29</v>
       </c>
       <c r="C586" s="16" t="e" vm="49">
@@ -32119,13 +32129,13 @@
       <c r="L586" s="11"/>
       <c r="M586" s="11"/>
     </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="5">
         <v>1</v>
       </c>
-      <c r="B587" s="145"/>
+      <c r="B587" s="206"/>
       <c r="C587" s="86" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D587" s="86" t="str">
         <f t="shared" ref="D587" si="328">C587</f>
@@ -32161,14 +32171,14 @@
       </c>
       <c r="M587" s="11"/>
       <c r="N587" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="5">
         <v>1</v>
       </c>
-      <c r="B588" s="137" t="s">
+      <c r="B588" s="135" t="s">
         <v>102</v>
       </c>
       <c r="C588" s="16" t="e" vm="11">
@@ -32197,11 +32207,11 @@
       <c r="J588" s="10"/>
       <c r="K588" s="7"/>
     </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="5">
         <v>1</v>
       </c>
-      <c r="B589" s="137"/>
+      <c r="B589" s="135"/>
       <c r="C589" s="86" t="s">
         <v>37</v>
       </c>
@@ -32238,12 +32248,12 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="5">
         <v>1</v>
       </c>
       <c r="B590" s="139" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C590" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -32271,7 +32281,7 @@
       <c r="J590" s="10"/>
       <c r="K590" s="7"/>
     </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="5">
         <v>1</v>
       </c>
@@ -32312,12 +32322,12 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="5">
         <v>1</v>
       </c>
-      <c r="B592" s="135" t="s">
-        <v>386</v>
+      <c r="B592" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C592" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -32347,11 +32357,11 @@
       <c r="L592" s="83"/>
       <c r="M592" s="11"/>
     </row>
-    <row r="593" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="5">
         <v>1</v>
       </c>
-      <c r="B593" s="136"/>
+      <c r="B593" s="137"/>
       <c r="C593" s="86" t="s">
         <v>37</v>
       </c>
@@ -32389,15 +32399,15 @@
       </c>
       <c r="M593" s="11"/>
       <c r="N593" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="594" spans="1:14" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="5">
         <v>1</v>
       </c>
-      <c r="B594" s="135" t="s">
-        <v>386</v>
+      <c r="B594" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C594" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -32426,11 +32436,11 @@
       <c r="K594" s="7"/>
       <c r="L594" s="83"/>
     </row>
-    <row r="595" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="5">
         <v>1</v>
       </c>
-      <c r="B595" s="136"/>
+      <c r="B595" s="137"/>
       <c r="C595" s="13" t="s">
         <v>37</v>
       </c>
@@ -32467,12 +32477,12 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="596" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="5">
         <v>1</v>
       </c>
-      <c r="B596" s="135" t="s">
-        <v>386</v>
+      <c r="B596" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C596" s="16" t="e" vm="11">
         <v>#VALUE!</v>
@@ -32501,11 +32511,11 @@
       <c r="K596" s="7"/>
       <c r="L596" s="83"/>
     </row>
-    <row r="597" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="5">
         <v>1</v>
       </c>
-      <c r="B597" s="136"/>
+      <c r="B597" s="137"/>
       <c r="C597" s="86" t="s">
         <v>37</v>
       </c>
@@ -32542,12 +32552,12 @@
         <v>46076</v>
       </c>
     </row>
-    <row r="598" spans="1:14" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:14" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A598" s="5">
         <v>1</v>
       </c>
-      <c r="B598" s="135" t="s">
-        <v>386</v>
+      <c r="B598" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C598" s="81" t="e" vm="25">
         <v>#VALUE!</v>
@@ -32578,11 +32588,11 @@
       <c r="L598" s="83"/>
       <c r="M598" s="11"/>
     </row>
-    <row r="599" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="5">
         <v>1</v>
       </c>
-      <c r="B599" s="136"/>
+      <c r="B599" s="137"/>
       <c r="C599" s="81" t="s">
         <v>101</v>
       </c>
@@ -32620,12 +32630,12 @@
       </c>
       <c r="M599" s="11"/>
     </row>
-    <row r="600" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="5">
         <v>1</v>
       </c>
-      <c r="B600" s="135" t="s">
-        <v>386</v>
+      <c r="B600" s="136" t="s">
+        <v>385</v>
       </c>
       <c r="C600" s="13" t="e" vm="11">
         <v>#VALUE!</v>
@@ -32654,11 +32664,11 @@
       <c r="K600" s="7"/>
       <c r="L600" s="83"/>
     </row>
-    <row r="601" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="5">
         <v>1</v>
       </c>
-      <c r="B601" s="136"/>
+      <c r="B601" s="137"/>
       <c r="C601" s="13" t="s">
         <v>37</v>
       </c>
@@ -32695,11 +32705,11 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="602" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:14" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="5">
         <v>1</v>
       </c>
-      <c r="B602" s="137" t="s">
+      <c r="B602" s="135" t="s">
         <v>102</v>
       </c>
       <c r="C602" s="16" t="e" vm="11">
@@ -32728,11 +32738,11 @@
       <c r="J602" s="10"/>
       <c r="K602" s="7"/>
     </row>
-    <row r="603" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="5">
         <v>1</v>
       </c>
-      <c r="B603" s="137"/>
+      <c r="B603" s="135"/>
       <c r="C603" s="86" t="s">
         <v>37</v>
       </c>
@@ -32773,8 +32783,250 @@
       <c r="C611" s="83"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q603" xr:uid="{7ECB3444-92D9-4200-8B78-7CB7FAE28719}"/>
+  <autoFilter ref="A1:Q603" xr:uid="{7ECB3444-92D9-4200-8B78-7CB7FAE28719}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="Manulife"/>
+        <filter val="MANULIFE FINANCIAL CORPORATION (XTSE:MFC)"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="259">
+    <mergeCell ref="B596:B597"/>
+    <mergeCell ref="B592:B593"/>
+    <mergeCell ref="B588:B589"/>
+    <mergeCell ref="B578:B579"/>
+    <mergeCell ref="B580:B581"/>
+    <mergeCell ref="B572:B573"/>
+    <mergeCell ref="B570:B571"/>
+    <mergeCell ref="B566:B567"/>
+    <mergeCell ref="B554:B555"/>
+    <mergeCell ref="B556:B557"/>
+    <mergeCell ref="B590:B591"/>
+    <mergeCell ref="B594:B595"/>
+    <mergeCell ref="B550:B551"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="B574:B575"/>
+    <mergeCell ref="B576:B577"/>
+    <mergeCell ref="B586:B587"/>
+    <mergeCell ref="B582:B583"/>
+    <mergeCell ref="B584:B585"/>
+    <mergeCell ref="B548:B549"/>
+    <mergeCell ref="B542:B543"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="B546:B547"/>
+    <mergeCell ref="B560:B561"/>
+    <mergeCell ref="B562:B563"/>
+    <mergeCell ref="B564:B565"/>
+    <mergeCell ref="B558:B559"/>
+    <mergeCell ref="B568:B569"/>
+    <mergeCell ref="B538:B539"/>
+    <mergeCell ref="B530:B531"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="B516:B517"/>
+    <mergeCell ref="B518:B519"/>
+    <mergeCell ref="B540:B541"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="B534:B535"/>
+    <mergeCell ref="B532:B533"/>
+    <mergeCell ref="B522:B523"/>
+    <mergeCell ref="B524:B525"/>
+    <mergeCell ref="B526:B527"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="B514:B515"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="B484:B485"/>
+    <mergeCell ref="B486:B487"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="B202:B203"/>
+    <mergeCell ref="B196:B197"/>
+    <mergeCell ref="B194:B195"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="B168:B169"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B118:B119"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="B266:B267"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="B442:B443"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="B352:B353"/>
+    <mergeCell ref="B354:B355"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="B396:B397"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="B392:B393"/>
     <mergeCell ref="B602:B603"/>
     <mergeCell ref="B600:B601"/>
     <mergeCell ref="B598:B599"/>
@@ -32799,241 +33051,6 @@
     <mergeCell ref="B470:B471"/>
     <mergeCell ref="B448:B449"/>
     <mergeCell ref="B446:B447"/>
-    <mergeCell ref="B442:B443"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="B352:B353"/>
-    <mergeCell ref="B354:B355"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="B396:B397"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="B266:B267"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="B202:B203"/>
-    <mergeCell ref="B196:B197"/>
-    <mergeCell ref="B194:B195"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="B168:B169"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="B514:B515"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="B484:B485"/>
-    <mergeCell ref="B486:B487"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="B488:B489"/>
-    <mergeCell ref="B538:B539"/>
-    <mergeCell ref="B530:B531"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="B516:B517"/>
-    <mergeCell ref="B518:B519"/>
-    <mergeCell ref="B540:B541"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="B534:B535"/>
-    <mergeCell ref="B532:B533"/>
-    <mergeCell ref="B522:B523"/>
-    <mergeCell ref="B524:B525"/>
-    <mergeCell ref="B526:B527"/>
-    <mergeCell ref="B550:B551"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="B574:B575"/>
-    <mergeCell ref="B576:B577"/>
-    <mergeCell ref="B586:B587"/>
-    <mergeCell ref="B582:B583"/>
-    <mergeCell ref="B584:B585"/>
-    <mergeCell ref="B548:B549"/>
-    <mergeCell ref="B542:B543"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="B546:B547"/>
-    <mergeCell ref="B560:B561"/>
-    <mergeCell ref="B562:B563"/>
-    <mergeCell ref="B564:B565"/>
-    <mergeCell ref="B558:B559"/>
-    <mergeCell ref="B568:B569"/>
-    <mergeCell ref="B596:B597"/>
-    <mergeCell ref="B592:B593"/>
-    <mergeCell ref="B588:B589"/>
-    <mergeCell ref="B578:B579"/>
-    <mergeCell ref="B580:B581"/>
-    <mergeCell ref="B572:B573"/>
-    <mergeCell ref="B570:B571"/>
-    <mergeCell ref="B566:B567"/>
-    <mergeCell ref="B554:B555"/>
-    <mergeCell ref="B556:B557"/>
-    <mergeCell ref="B590:B591"/>
-    <mergeCell ref="B594:B595"/>
   </mergeCells>
   <conditionalFormatting sqref="J2:J5 J174:J243">
     <cfRule type="cellIs" dxfId="132" priority="584" operator="greaterThan">

--- a/Gaboch_portfolio.xlsx
+++ b/Gaboch_portfolio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Gaboch_Portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{269E82A3-F4A6-40C1-91ED-C94BD3D9A394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272265CE-29F1-43B5-9FDF-84BD99EAAF07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" xr2:uid="{D37FE5D9-1440-4A1A-AC91-48FA1ED826EA}"/>
   </bookViews>
@@ -928,7 +928,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1360" uniqueCount="408">
   <si>
     <t>Account</t>
   </si>
@@ -3006,8 +3006,8 @@
     <xf numFmtId="1" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3015,7 +3015,10 @@
     <xf numFmtId="2" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3024,8 +3027,26 @@
     <xf numFmtId="2" fontId="2" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3033,31 +3054,103 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3066,56 +3159,8 @@
     <xf numFmtId="2" fontId="12" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3129,101 +3174,56 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="9" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3233,7 +3233,38 @@
     <cellStyle name="Normal 3" xfId="4" xr:uid="{53590949-50F7-46F0-AD03-5E851C6CFA14}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="133">
+  <dxfs count="136">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF66FF66"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00FF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -10070,7 +10101,7 @@
       <c r="A8" s="5">
         <v>1</v>
       </c>
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="199" t="s">
         <v>305</v>
       </c>
       <c r="C8" s="13" t="e" vm="3">
@@ -10111,7 +10142,7 @@
       <c r="A9" s="5">
         <v>1</v>
       </c>
-      <c r="B9" s="138"/>
+      <c r="B9" s="199"/>
       <c r="C9" s="15" t="s">
         <v>10</v>
       </c>
@@ -10235,7 +10266,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="168" t="s">
+      <c r="B12" s="157" t="s">
         <v>12</v>
       </c>
       <c r="C12" s="52" t="e" vm="5">
@@ -10268,7 +10299,7 @@
       <c r="M12" s="11"/>
     </row>
     <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="168"/>
+      <c r="B13" s="157"/>
       <c r="C13" s="52" t="s">
         <v>13</v>
       </c>
@@ -10918,7 +10949,7 @@
       </c>
     </row>
     <row r="30" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="168" t="s">
+      <c r="B30" s="157" t="s">
         <v>26</v>
       </c>
       <c r="C30" s="47" t="e" vm="8">
@@ -10950,7 +10981,7 @@
       <c r="M30" s="11"/>
     </row>
     <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="168"/>
+      <c r="B31" s="157"/>
       <c r="C31" s="47" t="s">
         <v>27</v>
       </c>
@@ -10988,7 +11019,7 @@
       </c>
     </row>
     <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="168" t="s">
+      <c r="B32" s="157" t="s">
         <v>26</v>
       </c>
       <c r="C32" s="47" t="e" vm="8">
@@ -11020,7 +11051,7 @@
       <c r="M32" s="11"/>
     </row>
     <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="168"/>
+      <c r="B33" s="157"/>
       <c r="C33" s="47" t="s">
         <v>27</v>
       </c>
@@ -11058,7 +11089,7 @@
       </c>
     </row>
     <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="168" t="s">
+      <c r="B34" s="157" t="s">
         <v>26</v>
       </c>
       <c r="C34" s="47" t="e" vm="8">
@@ -11090,7 +11121,7 @@
       <c r="M34" s="11"/>
     </row>
     <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="168"/>
+      <c r="B35" s="157"/>
       <c r="C35" s="47" t="s">
         <v>27</v>
       </c>
@@ -11200,7 +11231,7 @@
       <c r="M37" s="11"/>
     </row>
     <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="168" t="s">
+      <c r="B38" s="157" t="s">
         <v>32</v>
       </c>
       <c r="C38" s="47" t="e" vm="8">
@@ -11232,7 +11263,7 @@
       <c r="M38" s="11"/>
     </row>
     <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="168"/>
+      <c r="B39" s="157"/>
       <c r="C39" s="47" t="s">
         <v>27</v>
       </c>
@@ -11270,7 +11301,7 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="182" t="s">
+      <c r="B40" s="158" t="s">
         <v>33</v>
       </c>
       <c r="C40" s="47" t="e" vm="8">
@@ -11302,7 +11333,7 @@
       <c r="M40" s="11"/>
     </row>
     <row r="41" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="182"/>
+      <c r="B41" s="158"/>
       <c r="C41" s="47" t="s">
         <v>27</v>
       </c>
@@ -11422,7 +11453,7 @@
       </c>
     </row>
     <row r="44" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B44" s="182" t="s">
+      <c r="B44" s="158" t="s">
         <v>33</v>
       </c>
       <c r="C44" s="47" t="e" vm="8">
@@ -11454,7 +11485,7 @@
       <c r="M44" s="11"/>
     </row>
     <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B45" s="182"/>
+      <c r="B45" s="158"/>
       <c r="C45" s="47" t="s">
         <v>27</v>
       </c>
@@ -11491,7 +11522,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>1</v>
       </c>
@@ -11528,7 +11559,7 @@
       <c r="L46" s="83"/>
       <c r="M46" s="11"/>
     </row>
-    <row r="47" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>1</v>
       </c>
@@ -11572,7 +11603,7 @@
       </c>
     </row>
     <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B48" s="151" t="s">
+      <c r="B48" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C48" s="63" t="s">
@@ -11604,7 +11635,7 @@
       <c r="M48" s="11"/>
     </row>
     <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B49" s="151"/>
+      <c r="B49" s="144"/>
       <c r="C49" s="63" t="s">
         <v>37</v>
       </c>
@@ -11643,7 +11674,7 @@
       </c>
     </row>
     <row r="50" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="200" t="s">
+      <c r="B50" s="169" t="s">
         <v>40</v>
       </c>
       <c r="C50" s="63" t="e" vm="11">
@@ -11675,7 +11706,7 @@
       <c r="M50" s="11"/>
     </row>
     <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B51" s="201"/>
+      <c r="B51" s="170"/>
       <c r="C51" s="63" t="s">
         <v>37</v>
       </c>
@@ -11711,7 +11742,7 @@
       <c r="M51" s="11"/>
     </row>
     <row r="52" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="200" t="s">
+      <c r="B52" s="169" t="s">
         <v>35</v>
       </c>
       <c r="C52" s="63" t="e" vm="11">
@@ -11745,7 +11776,7 @@
       <c r="M52" s="123"/>
     </row>
     <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="201"/>
+      <c r="B53" s="170"/>
       <c r="C53" s="63" t="s">
         <v>37</v>
       </c>
@@ -11784,7 +11815,7 @@
       </c>
     </row>
     <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B54" s="200" t="s">
+      <c r="B54" s="169" t="s">
         <v>42</v>
       </c>
       <c r="C54" s="63" t="e" vm="11">
@@ -11816,7 +11847,7 @@
       <c r="M54" s="11"/>
     </row>
     <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B55" s="201"/>
+      <c r="B55" s="170"/>
       <c r="C55" s="63" t="s">
         <v>37</v>
       </c>
@@ -11854,7 +11885,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>1</v>
       </c>
@@ -11889,7 +11920,7 @@
       <c r="L56" s="83"/>
       <c r="M56" s="11"/>
     </row>
-    <row r="57" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>1</v>
       </c>
@@ -11936,7 +11967,7 @@
       <c r="A58" s="5">
         <v>1</v>
       </c>
-      <c r="B58" s="199" t="s">
+      <c r="B58" s="161" t="s">
         <v>44</v>
       </c>
       <c r="C58" s="16" t="e" vm="12">
@@ -11975,7 +12006,7 @@
       <c r="A59" s="5">
         <v>1</v>
       </c>
-      <c r="B59" s="199"/>
+      <c r="B59" s="161"/>
       <c r="C59" s="16" t="s">
         <v>45</v>
       </c>
@@ -12016,7 +12047,7 @@
       </c>
     </row>
     <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B60" s="192" t="s">
+      <c r="B60" s="171" t="s">
         <v>42</v>
       </c>
       <c r="C60" s="63" t="e" vm="11">
@@ -12048,7 +12079,7 @@
       <c r="M60" s="11"/>
     </row>
     <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B61" s="192"/>
+      <c r="B61" s="171"/>
       <c r="C61" s="63" t="s">
         <v>37</v>
       </c>
@@ -12087,7 +12118,7 @@
       </c>
     </row>
     <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B62" s="188" t="s">
+      <c r="B62" s="162" t="s">
         <v>32</v>
       </c>
       <c r="C62" s="63" t="e" vm="12">
@@ -12123,7 +12154,7 @@
       </c>
     </row>
     <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B63" s="189"/>
+      <c r="B63" s="163"/>
       <c r="C63" s="79" t="s">
         <v>45</v>
       </c>
@@ -12166,7 +12197,7 @@
       </c>
     </row>
     <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B64" s="188" t="s">
+      <c r="B64" s="162" t="s">
         <v>32</v>
       </c>
       <c r="C64" s="63" t="e" vm="12">
@@ -12202,7 +12233,7 @@
       </c>
     </row>
     <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="189"/>
+      <c r="B65" s="163"/>
       <c r="C65" s="79" t="s">
         <v>45</v>
       </c>
@@ -12245,7 +12276,7 @@
       </c>
     </row>
     <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B66" s="193" t="s">
+      <c r="B66" s="164" t="s">
         <v>26</v>
       </c>
       <c r="C66" s="63" t="e" vm="12">
@@ -12277,7 +12308,7 @@
       <c r="M66" s="11"/>
     </row>
     <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B67" s="193"/>
+      <c r="B67" s="164"/>
       <c r="C67" s="79" t="s">
         <v>45</v>
       </c>
@@ -12316,7 +12347,7 @@
       </c>
     </row>
     <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B68" s="193" t="s">
+      <c r="B68" s="164" t="s">
         <v>26</v>
       </c>
       <c r="C68" s="63" t="e" vm="12">
@@ -12348,7 +12379,7 @@
       <c r="M68" s="11"/>
     </row>
     <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B69" s="193"/>
+      <c r="B69" s="164"/>
       <c r="C69" s="79" t="s">
         <v>45</v>
       </c>
@@ -12387,7 +12418,7 @@
       </c>
     </row>
     <row r="70" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="188" t="s">
+      <c r="B70" s="162" t="s">
         <v>32</v>
       </c>
       <c r="C70" s="63" t="e" vm="12">
@@ -12419,7 +12450,7 @@
       <c r="M70" s="11"/>
     </row>
     <row r="71" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B71" s="189"/>
+      <c r="B71" s="163"/>
       <c r="C71" s="79" t="s">
         <v>45</v>
       </c>
@@ -12458,7 +12489,7 @@
       </c>
     </row>
     <row r="72" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B72" s="188" t="s">
+      <c r="B72" s="162" t="s">
         <v>32</v>
       </c>
       <c r="C72" s="63" t="e" vm="12">
@@ -12490,7 +12521,7 @@
       <c r="M72" s="11"/>
     </row>
     <row r="73" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B73" s="189"/>
+      <c r="B73" s="163"/>
       <c r="C73" s="79" t="s">
         <v>45</v>
       </c>
@@ -12529,7 +12560,7 @@
       </c>
     </row>
     <row r="74" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B74" s="164" t="s">
+      <c r="B74" s="165" t="s">
         <v>47</v>
       </c>
       <c r="C74" s="63" t="e" vm="12">
@@ -12561,7 +12592,7 @@
       <c r="M74" s="11"/>
     </row>
     <row r="75" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B75" s="165"/>
+      <c r="B75" s="166"/>
       <c r="C75" s="79" t="s">
         <v>45</v>
       </c>
@@ -13126,7 +13157,7 @@
       <c r="M89" s="11"/>
     </row>
     <row r="90" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B90" s="178" t="s">
+      <c r="B90" s="167" t="s">
         <v>47</v>
       </c>
       <c r="C90" s="63" t="e" vm="13">
@@ -13162,7 +13193,7 @@
       </c>
     </row>
     <row r="91" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B91" s="179"/>
+      <c r="B91" s="168"/>
       <c r="C91" s="79" t="s">
         <v>50</v>
       </c>
@@ -13198,7 +13229,7 @@
       <c r="M91" s="11"/>
     </row>
     <row r="92" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B92" s="178" t="s">
+      <c r="B92" s="167" t="s">
         <v>47</v>
       </c>
       <c r="C92" s="52" t="e" vm="14">
@@ -13234,7 +13265,7 @@
       </c>
     </row>
     <row r="93" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B93" s="179"/>
+      <c r="B93" s="168"/>
       <c r="C93" s="78" t="s">
         <v>51</v>
       </c>
@@ -13270,7 +13301,7 @@
       <c r="M93" s="11"/>
     </row>
     <row r="94" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B94" s="178" t="s">
+      <c r="B94" s="167" t="s">
         <v>47</v>
       </c>
       <c r="C94" s="52" t="e" vm="14">
@@ -13306,7 +13337,7 @@
       </c>
     </row>
     <row r="95" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B95" s="179"/>
+      <c r="B95" s="168"/>
       <c r="C95" s="78" t="s">
         <v>51</v>
       </c>
@@ -13565,7 +13596,7 @@
       </c>
     </row>
     <row r="102" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B102" s="151" t="s">
+      <c r="B102" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C102" s="63" t="e" vm="15">
@@ -13602,7 +13633,7 @@
       </c>
     </row>
     <row r="103" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="151"/>
+      <c r="B103" s="144"/>
       <c r="C103" s="79" t="s">
         <v>53</v>
       </c>
@@ -13647,7 +13678,7 @@
       <c r="A104" s="5">
         <v>1</v>
       </c>
-      <c r="B104" s="151" t="s">
+      <c r="B104" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C104" s="13" t="e" vm="16">
@@ -13687,7 +13718,7 @@
       <c r="A105" s="5">
         <v>1</v>
       </c>
-      <c r="B105" s="151"/>
+      <c r="B105" s="144"/>
       <c r="C105" s="15" t="s">
         <v>56</v>
       </c>
@@ -14118,7 +14149,7 @@
       <c r="M115" s="11"/>
     </row>
     <row r="116" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B116" s="170" t="s">
+      <c r="B116" s="176" t="s">
         <v>32</v>
       </c>
       <c r="C116" s="52" t="e" vm="18">
@@ -14151,7 +14182,7 @@
       <c r="M116" s="11"/>
     </row>
     <row r="117" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B117" s="171"/>
+      <c r="B117" s="177"/>
       <c r="C117" s="78" t="s">
         <v>59</v>
       </c>
@@ -14190,7 +14221,7 @@
       </c>
     </row>
     <row r="118" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B118" s="164" t="s">
+      <c r="B118" s="165" t="s">
         <v>60</v>
       </c>
       <c r="C118" s="52" t="e" vm="18">
@@ -14227,7 +14258,7 @@
       </c>
     </row>
     <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B119" s="165"/>
+      <c r="B119" s="166"/>
       <c r="C119" s="78" t="s">
         <v>59</v>
       </c>
@@ -14270,7 +14301,7 @@
       </c>
     </row>
     <row r="120" spans="1:15" ht="29.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B120" s="196" t="s">
+      <c r="B120" s="178" t="s">
         <v>52</v>
       </c>
       <c r="C120" s="52" t="e" vm="18">
@@ -14303,7 +14334,7 @@
       <c r="M120" s="11"/>
     </row>
     <row r="121" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B121" s="197"/>
+      <c r="B121" s="179"/>
       <c r="C121" s="78" t="s">
         <v>59</v>
       </c>
@@ -14650,7 +14681,7 @@
       </c>
     </row>
     <row r="130" spans="1:16" ht="29.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B130" s="196" t="s">
+      <c r="B130" s="178" t="s">
         <v>52</v>
       </c>
       <c r="C130" s="52" t="e" vm="19">
@@ -14684,7 +14715,7 @@
       <c r="N130" s="24"/>
     </row>
     <row r="131" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B131" s="197"/>
+      <c r="B131" s="179"/>
       <c r="C131" s="78" t="s">
         <v>61</v>
       </c>
@@ -14872,7 +14903,7 @@
       <c r="M135" s="11"/>
     </row>
     <row r="136" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B136" s="192" t="s">
+      <c r="B136" s="171" t="s">
         <v>66</v>
       </c>
       <c r="C136" s="43" t="e" vm="11">
@@ -14907,7 +14938,7 @@
       <c r="M136" s="12"/>
     </row>
     <row r="137" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B137" s="192"/>
+      <c r="B137" s="171"/>
       <c r="C137" s="80" t="s">
         <v>37</v>
       </c>
@@ -14952,7 +14983,7 @@
       </c>
     </row>
     <row r="138" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B138" s="196" t="s">
+      <c r="B138" s="178" t="s">
         <v>52</v>
       </c>
       <c r="C138" s="43" t="e" vm="22">
@@ -14985,7 +15016,7 @@
       <c r="M138" s="12"/>
     </row>
     <row r="139" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B139" s="197"/>
+      <c r="B139" s="179"/>
       <c r="C139" s="43" t="s">
         <v>69</v>
       </c>
@@ -15030,7 +15061,7 @@
       </c>
     </row>
     <row r="140" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B140" s="196" t="s">
+      <c r="B140" s="178" t="s">
         <v>52</v>
       </c>
       <c r="C140" s="43" t="e" vm="22">
@@ -15063,7 +15094,7 @@
       <c r="M140" s="12"/>
     </row>
     <row r="141" spans="1:16" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B141" s="197"/>
+      <c r="B141" s="179"/>
       <c r="C141" s="43" t="s">
         <v>69</v>
       </c>
@@ -15183,7 +15214,7 @@
       </c>
     </row>
     <row r="144" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B144" s="151" t="s">
+      <c r="B144" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C144" s="63" t="e" vm="22">
@@ -15216,7 +15247,7 @@
       <c r="M144" s="11"/>
     </row>
     <row r="145" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B145" s="151"/>
+      <c r="B145" s="144"/>
       <c r="C145" s="63" t="s">
         <v>69</v>
       </c>
@@ -15259,7 +15290,7 @@
       </c>
     </row>
     <row r="146" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B146" s="151" t="s">
+      <c r="B146" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C146" s="63" t="e" vm="22">
@@ -15292,7 +15323,7 @@
       <c r="M146" s="11"/>
     </row>
     <row r="147" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B147" s="151"/>
+      <c r="B147" s="144"/>
       <c r="C147" s="63" t="s">
         <v>69</v>
       </c>
@@ -15571,7 +15602,7 @@
       <c r="A154" s="5">
         <v>1</v>
       </c>
-      <c r="B154" s="155" t="s">
+      <c r="B154" s="175" t="s">
         <v>86</v>
       </c>
       <c r="C154" s="13" t="e" vm="23">
@@ -15607,7 +15638,7 @@
       <c r="A155" s="5">
         <v>1</v>
       </c>
-      <c r="B155" s="155"/>
+      <c r="B155" s="175"/>
       <c r="C155" s="15" t="s">
         <v>87</v>
       </c>
@@ -15727,7 +15758,7 @@
       <c r="A158" s="5">
         <v>1</v>
       </c>
-      <c r="B158" s="194" t="s">
+      <c r="B158" s="173" t="s">
         <v>89</v>
       </c>
       <c r="C158" s="16" t="e" vm="22">
@@ -15763,7 +15794,7 @@
       <c r="A159" s="5">
         <v>1</v>
       </c>
-      <c r="B159" s="195"/>
+      <c r="B159" s="174"/>
       <c r="C159" s="23" t="s">
         <v>69</v>
       </c>
@@ -15803,7 +15834,7 @@
       <c r="A160" s="5">
         <v>1</v>
       </c>
-      <c r="B160" s="158" t="s">
+      <c r="B160" s="147" t="s">
         <v>380</v>
       </c>
       <c r="C160" s="13" t="e" vm="22">
@@ -15842,7 +15873,7 @@
       <c r="A161" s="5">
         <v>1</v>
       </c>
-      <c r="B161" s="159"/>
+      <c r="B161" s="148"/>
       <c r="C161" s="15" t="s">
         <v>69</v>
       </c>
@@ -15879,7 +15910,7 @@
       <c r="M161" s="11"/>
     </row>
     <row r="162" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B162" s="180" t="s">
+      <c r="B162" s="172" t="s">
         <v>92</v>
       </c>
       <c r="C162" s="63" t="e" vm="22">
@@ -15915,7 +15946,7 @@
       </c>
     </row>
     <row r="163" spans="1:15" ht="32.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B163" s="180"/>
+      <c r="B163" s="172"/>
       <c r="C163" s="63" t="s">
         <v>69</v>
       </c>
@@ -15957,7 +15988,7 @@
       <c r="A164" s="5">
         <v>1</v>
       </c>
-      <c r="B164" s="147" t="s">
+      <c r="B164" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C164" s="16" t="e" vm="22">
@@ -15996,7 +16027,7 @@
       <c r="A165" s="5">
         <v>1</v>
       </c>
-      <c r="B165" s="148"/>
+      <c r="B165" s="143"/>
       <c r="C165" s="23" t="s">
         <v>69</v>
       </c>
@@ -16033,7 +16064,7 @@
       <c r="M165" s="11"/>
     </row>
     <row r="166" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B166" s="180" t="s">
+      <c r="B166" s="172" t="s">
         <v>92</v>
       </c>
       <c r="C166" s="63" t="e" vm="22">
@@ -16069,7 +16100,7 @@
       </c>
     </row>
     <row r="167" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B167" s="180"/>
+      <c r="B167" s="172"/>
       <c r="C167" s="63" t="s">
         <v>69</v>
       </c>
@@ -16111,7 +16142,7 @@
       </c>
     </row>
     <row r="168" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B168" s="151" t="s">
+      <c r="B168" s="144" t="s">
         <v>44</v>
       </c>
       <c r="C168" s="63" t="e" vm="22">
@@ -16150,7 +16181,7 @@
       </c>
     </row>
     <row r="169" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B169" s="151"/>
+      <c r="B169" s="144"/>
       <c r="C169" s="63" t="s">
         <v>69</v>
       </c>
@@ -16339,7 +16370,7 @@
       <c r="M173" s="125"/>
     </row>
     <row r="174" spans="1:15" ht="32.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B174" s="153" t="s">
+      <c r="B174" s="184" t="s">
         <v>102</v>
       </c>
       <c r="C174" s="63" t="e" vm="11">
@@ -16374,7 +16405,7 @@
       </c>
     </row>
     <row r="175" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B175" s="154"/>
+      <c r="B175" s="185"/>
       <c r="C175" s="63" t="s">
         <v>37</v>
       </c>
@@ -16411,7 +16442,7 @@
       <c r="M175" s="11"/>
     </row>
     <row r="176" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B176" s="190" t="s">
+      <c r="B176" s="183" t="s">
         <v>104</v>
       </c>
       <c r="C176" s="43" t="e" vm="26">
@@ -16450,7 +16481,7 @@
       </c>
     </row>
     <row r="177" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B177" s="190"/>
+      <c r="B177" s="183"/>
       <c r="C177" s="43" t="s">
         <v>107</v>
       </c>
@@ -16486,7 +16517,7 @@
       <c r="M177" s="123"/>
     </row>
     <row r="178" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B178" s="191" t="s">
+      <c r="B178" s="186" t="s">
         <v>108</v>
       </c>
       <c r="C178" s="39" t="e" vm="26">
@@ -16525,7 +16556,7 @@
       </c>
     </row>
     <row r="179" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B179" s="191"/>
+      <c r="B179" s="186"/>
       <c r="C179" s="39" t="s">
         <v>107</v>
       </c>
@@ -16561,7 +16592,7 @@
       <c r="M179" s="125"/>
     </row>
     <row r="180" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B180" s="187" t="s">
+      <c r="B180" s="180" t="s">
         <v>104</v>
       </c>
       <c r="C180" s="47" t="s">
@@ -16596,7 +16627,7 @@
       </c>
     </row>
     <row r="181" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B181" s="187"/>
+      <c r="B181" s="180"/>
       <c r="C181" s="47" t="s">
         <v>111</v>
       </c>
@@ -16632,7 +16663,7 @@
       <c r="M181" s="123"/>
     </row>
     <row r="182" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B182" s="184" t="s">
+      <c r="B182" s="191" t="s">
         <v>112</v>
       </c>
       <c r="C182" s="49" t="e" vm="27">
@@ -16671,7 +16702,7 @@
       </c>
     </row>
     <row r="183" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B183" s="184"/>
+      <c r="B183" s="191"/>
       <c r="C183" s="49" t="s">
         <v>114</v>
       </c>
@@ -16707,7 +16738,7 @@
       <c r="M183" s="125"/>
     </row>
     <row r="184" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B184" s="185" t="s">
+      <c r="B184" s="139" t="s">
         <v>40</v>
       </c>
       <c r="C184" s="63" t="e" vm="11">
@@ -16742,7 +16773,7 @@
       </c>
     </row>
     <row r="185" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B185" s="186"/>
+      <c r="B185" s="192"/>
       <c r="C185" s="63" t="s">
         <v>37</v>
       </c>
@@ -16781,7 +16812,7 @@
       </c>
     </row>
     <row r="186" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B186" s="185" t="s">
+      <c r="B186" s="139" t="s">
         <v>40</v>
       </c>
       <c r="C186" s="63" t="e" vm="11">
@@ -16816,7 +16847,7 @@
       </c>
     </row>
     <row r="187" spans="1:15" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B187" s="186"/>
+      <c r="B187" s="192"/>
       <c r="C187" s="63" t="s">
         <v>37</v>
       </c>
@@ -16854,7 +16885,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="188" spans="1:15" ht="11.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:15" ht="11.3" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>1</v>
       </c>
@@ -16892,7 +16923,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="40.5" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:15" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>1</v>
       </c>
@@ -16932,11 +16963,11 @@
       <c r="L189" s="83"/>
       <c r="M189" s="11"/>
     </row>
-    <row r="190" spans="1:15" ht="13.55" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:15" ht="13.55" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>1</v>
       </c>
-      <c r="B190" s="147" t="s">
+      <c r="B190" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C190" s="20" t="e" vm="11">
@@ -16970,11 +17001,11 @@
         <v>117</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="36.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:15" ht="36.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>1</v>
       </c>
-      <c r="B191" s="148"/>
+      <c r="B191" s="143"/>
       <c r="C191" s="20" t="s">
         <v>37</v>
       </c>
@@ -17011,7 +17042,7 @@
       <c r="M191" s="11"/>
     </row>
     <row r="192" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B192" s="151" t="s">
+      <c r="B192" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C192" s="63" t="e" vm="11">
@@ -17043,7 +17074,7 @@
       <c r="M192" s="11"/>
     </row>
     <row r="193" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B193" s="151"/>
+      <c r="B193" s="144"/>
       <c r="C193" s="63" t="s">
         <v>37</v>
       </c>
@@ -17082,7 +17113,7 @@
       </c>
     </row>
     <row r="194" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B194" s="160" t="s">
+      <c r="B194" s="155" t="s">
         <v>108</v>
       </c>
       <c r="C194" s="47" t="e" vm="28">
@@ -17114,7 +17145,7 @@
       <c r="M194" s="11"/>
     </row>
     <row r="195" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B195" s="160"/>
+      <c r="B195" s="155"/>
       <c r="C195" s="47" t="s">
         <v>118</v>
       </c>
@@ -17156,7 +17187,7 @@
       </c>
     </row>
     <row r="196" spans="1:15" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B196" s="181" t="s">
+      <c r="B196" s="160" t="s">
         <v>29</v>
       </c>
       <c r="C196" s="63" t="e" vm="11">
@@ -17191,7 +17222,7 @@
       </c>
     </row>
     <row r="197" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B197" s="181"/>
+      <c r="B197" s="160"/>
       <c r="C197" s="63" t="s">
         <v>37</v>
       </c>
@@ -17227,7 +17258,7 @@
       <c r="M197" s="123"/>
     </row>
     <row r="198" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B198" s="181" t="s">
+      <c r="B198" s="160" t="s">
         <v>104</v>
       </c>
       <c r="C198" s="63" t="e" vm="29">
@@ -17263,7 +17294,7 @@
       </c>
     </row>
     <row r="199" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B199" s="181"/>
+      <c r="B199" s="160"/>
       <c r="C199" s="63" t="s">
         <v>121</v>
       </c>
@@ -17300,7 +17331,7 @@
       <c r="N199" s="53"/>
     </row>
     <row r="200" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B200" s="181" t="s">
+      <c r="B200" s="160" t="s">
         <v>108</v>
       </c>
       <c r="C200" s="63" t="e" vm="29">
@@ -17336,7 +17367,7 @@
       </c>
     </row>
     <row r="201" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B201" s="181"/>
+      <c r="B201" s="160"/>
       <c r="C201" s="63" t="s">
         <v>121</v>
       </c>
@@ -17372,7 +17403,7 @@
       <c r="M201" s="123"/>
     </row>
     <row r="202" spans="1:15" ht="11.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B202" s="198" t="s">
+      <c r="B202" s="159" t="s">
         <v>29</v>
       </c>
       <c r="C202" s="47" t="e" vm="30">
@@ -17405,7 +17436,7 @@
       <c r="M202" s="11"/>
     </row>
     <row r="203" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B203" s="198"/>
+      <c r="B203" s="159"/>
       <c r="C203" s="47" t="s">
         <v>123</v>
       </c>
@@ -17448,7 +17479,7 @@
     </row>
     <row r="204" spans="1:15" s="53" customFormat="1" ht="43.2" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="5"/>
-      <c r="B204" s="181" t="s">
+      <c r="B204" s="160" t="s">
         <v>108</v>
       </c>
       <c r="C204" s="63" t="e" vm="22">
@@ -17482,7 +17513,7 @@
     </row>
     <row r="205" spans="1:15" s="53" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5"/>
-      <c r="B205" s="181"/>
+      <c r="B205" s="160"/>
       <c r="C205" s="63" t="s">
         <v>125</v>
       </c>
@@ -17517,11 +17548,11 @@
       <c r="L205" s="83"/>
       <c r="M205" s="123"/>
     </row>
-    <row r="206" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>1</v>
       </c>
-      <c r="B206" s="147" t="s">
+      <c r="B206" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C206" s="16" t="e" vm="11">
@@ -17552,11 +17583,11 @@
       <c r="L206" s="83"/>
       <c r="M206" s="11"/>
     </row>
-    <row r="207" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>1</v>
       </c>
-      <c r="B207" s="148"/>
+      <c r="B207" s="143"/>
       <c r="C207" s="16" t="s">
         <v>37</v>
       </c>
@@ -17592,7 +17623,7 @@
       <c r="L207" s="83"/>
       <c r="M207" s="11"/>
     </row>
-    <row r="208" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:15" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>1</v>
       </c>
@@ -17627,7 +17658,7 @@
       <c r="L208" s="83"/>
       <c r="M208" s="11"/>
     </row>
-    <row r="209" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:15" ht="28.8" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>1</v>
       </c>
@@ -17671,7 +17702,7 @@
       </c>
     </row>
     <row r="210" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B210" s="168" t="s">
+      <c r="B210" s="157" t="s">
         <v>33</v>
       </c>
       <c r="C210" s="52" t="e" vm="11">
@@ -17703,7 +17734,7 @@
       <c r="M210" s="11"/>
     </row>
     <row r="211" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B211" s="169"/>
+      <c r="B211" s="181"/>
       <c r="C211" s="52" t="s">
         <v>37</v>
       </c>
@@ -17745,7 +17776,7 @@
       </c>
     </row>
     <row r="212" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B212" s="161" t="s">
+      <c r="B212" s="182" t="s">
         <v>17</v>
       </c>
       <c r="C212" s="52" t="e" vm="25">
@@ -17781,7 +17812,7 @@
       </c>
     </row>
     <row r="213" spans="1:15" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B213" s="161"/>
+      <c r="B213" s="182"/>
       <c r="C213" s="52" t="s">
         <v>101</v>
       </c>
@@ -17821,7 +17852,7 @@
       </c>
     </row>
     <row r="214" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B214" s="188" t="s">
+      <c r="B214" s="162" t="s">
         <v>32</v>
       </c>
       <c r="C214" s="52" t="e" vm="25">
@@ -17856,7 +17887,7 @@
       <c r="M214" s="11"/>
     </row>
     <row r="215" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B215" s="189"/>
+      <c r="B215" s="163"/>
       <c r="C215" s="52" t="s">
         <v>101</v>
       </c>
@@ -17895,7 +17926,7 @@
       </c>
     </row>
     <row r="216" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B216" s="161" t="s">
+      <c r="B216" s="182" t="s">
         <v>29</v>
       </c>
       <c r="C216" s="52" t="e" vm="25">
@@ -17934,7 +17965,7 @@
       </c>
     </row>
     <row r="217" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B217" s="161"/>
+      <c r="B217" s="182"/>
       <c r="C217" s="52" t="s">
         <v>101</v>
       </c>
@@ -17970,7 +18001,7 @@
       <c r="M217" s="126"/>
     </row>
     <row r="218" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B218" s="161" t="s">
+      <c r="B218" s="182" t="s">
         <v>29</v>
       </c>
       <c r="C218" s="52" t="e" vm="25">
@@ -18009,7 +18040,7 @@
       </c>
     </row>
     <row r="219" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B219" s="161"/>
+      <c r="B219" s="182"/>
       <c r="C219" s="52" t="s">
         <v>101</v>
       </c>
@@ -18045,7 +18076,7 @@
       <c r="M219" s="126"/>
     </row>
     <row r="220" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B220" s="161" t="s">
+      <c r="B220" s="182" t="s">
         <v>29</v>
       </c>
       <c r="C220" s="52" t="e" vm="25">
@@ -18084,7 +18115,7 @@
       </c>
     </row>
     <row r="221" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B221" s="161"/>
+      <c r="B221" s="182"/>
       <c r="C221" s="52" t="s">
         <v>101</v>
       </c>
@@ -18120,7 +18151,7 @@
       <c r="M221" s="126"/>
     </row>
     <row r="222" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B222" s="161" t="s">
+      <c r="B222" s="182" t="s">
         <v>395</v>
       </c>
       <c r="C222" s="52" t="e" vm="25">
@@ -18159,7 +18190,7 @@
       </c>
     </row>
     <row r="223" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B223" s="161"/>
+      <c r="B223" s="182"/>
       <c r="C223" s="52" t="s">
         <v>101</v>
       </c>
@@ -18195,7 +18226,7 @@
       <c r="M223" s="126"/>
     </row>
     <row r="224" spans="1:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B224" s="161" t="s">
+      <c r="B224" s="182" t="s">
         <v>33</v>
       </c>
       <c r="C224" s="52" t="e" vm="25">
@@ -18234,7 +18265,7 @@
       </c>
     </row>
     <row r="225" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B225" s="161"/>
+      <c r="B225" s="182"/>
       <c r="C225" s="52" t="s">
         <v>101</v>
       </c>
@@ -18273,7 +18304,7 @@
       </c>
     </row>
     <row r="226" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B226" s="161" t="s">
+      <c r="B226" s="182" t="s">
         <v>33</v>
       </c>
       <c r="C226" s="52" t="e" vm="25">
@@ -18312,7 +18343,7 @@
       </c>
     </row>
     <row r="227" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B227" s="161"/>
+      <c r="B227" s="182"/>
       <c r="C227" s="52" t="s">
         <v>101</v>
       </c>
@@ -18351,7 +18382,7 @@
       </c>
     </row>
     <row r="228" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B228" s="172" t="s">
+      <c r="B228" s="187" t="s">
         <v>33</v>
       </c>
       <c r="C228" s="52" t="e" vm="25">
@@ -18387,7 +18418,7 @@
       </c>
     </row>
     <row r="229" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B229" s="173"/>
+      <c r="B229" s="188"/>
       <c r="C229" s="52" t="s">
         <v>101</v>
       </c>
@@ -18426,7 +18457,7 @@
       </c>
     </row>
     <row r="230" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B230" s="172" t="s">
+      <c r="B230" s="187" t="s">
         <v>33</v>
       </c>
       <c r="C230" s="52" t="e" vm="25">
@@ -18459,7 +18490,7 @@
       <c r="M230" s="11"/>
     </row>
     <row r="231" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B231" s="173"/>
+      <c r="B231" s="188"/>
       <c r="C231" s="52" t="s">
         <v>101</v>
       </c>
@@ -18501,7 +18532,7 @@
       <c r="A232" s="5">
         <v>1</v>
       </c>
-      <c r="B232" s="147" t="s">
+      <c r="B232" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C232" s="81" t="e" vm="25">
@@ -18537,7 +18568,7 @@
       <c r="A233" s="5">
         <v>1</v>
       </c>
-      <c r="B233" s="148"/>
+      <c r="B233" s="143"/>
       <c r="C233" s="81" t="s">
         <v>101</v>
       </c>
@@ -18580,7 +18611,7 @@
       </c>
     </row>
     <row r="234" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B234" s="164" t="s">
+      <c r="B234" s="165" t="s">
         <v>142</v>
       </c>
       <c r="C234" s="52" t="e" vm="25">
@@ -18613,7 +18644,7 @@
       <c r="M234" s="11"/>
     </row>
     <row r="235" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B235" s="165"/>
+      <c r="B235" s="166"/>
       <c r="C235" s="52" t="s">
         <v>101</v>
       </c>
@@ -18655,7 +18686,7 @@
       </c>
     </row>
     <row r="236" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B236" s="174" t="s">
+      <c r="B236" s="189" t="s">
         <v>395</v>
       </c>
       <c r="C236" s="52" t="e" vm="25">
@@ -18688,7 +18719,7 @@
       <c r="M236" s="11"/>
     </row>
     <row r="237" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B237" s="175"/>
+      <c r="B237" s="190"/>
       <c r="C237" s="52" t="s">
         <v>101</v>
       </c>
@@ -18730,7 +18761,7 @@
       </c>
     </row>
     <row r="238" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B238" s="139" t="s">
+      <c r="B238" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C238" s="63" t="e" vm="25">
@@ -18763,7 +18794,7 @@
       <c r="M238" s="11"/>
     </row>
     <row r="239" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B239" s="140"/>
+      <c r="B239" s="141"/>
       <c r="C239" s="63" t="s">
         <v>101</v>
       </c>
@@ -18804,11 +18835,11 @@
         <v>288</v>
       </c>
     </row>
-    <row r="240" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>1</v>
       </c>
-      <c r="B240" s="151" t="s">
+      <c r="B240" s="144" t="s">
         <v>147</v>
       </c>
       <c r="C240" s="20" t="e" vm="11">
@@ -18839,11 +18870,11 @@
       <c r="L240" s="83"/>
       <c r="M240" s="11"/>
     </row>
-    <row r="241" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>1</v>
       </c>
-      <c r="B241" s="151"/>
+      <c r="B241" s="144"/>
       <c r="C241" s="20" t="s">
         <v>37</v>
       </c>
@@ -18880,7 +18911,7 @@
       <c r="M241" s="11"/>
     </row>
     <row r="242" spans="1:16" ht="29.3" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B242" s="182" t="s">
+      <c r="B242" s="158" t="s">
         <v>33</v>
       </c>
       <c r="C242" s="47" t="e" vm="8">
@@ -18912,7 +18943,7 @@
       <c r="M242" s="11"/>
     </row>
     <row r="243" spans="1:16" ht="51.05" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B243" s="182"/>
+      <c r="B243" s="158"/>
       <c r="C243" s="47" t="s">
         <v>27</v>
       </c>
@@ -18953,7 +18984,7 @@
       <c r="A244" s="5">
         <v>1</v>
       </c>
-      <c r="B244" s="158" t="s">
+      <c r="B244" s="147" t="s">
         <v>380</v>
       </c>
       <c r="C244" s="5" t="e" vm="31">
@@ -18989,7 +19020,7 @@
       <c r="A245" s="5">
         <v>1</v>
       </c>
-      <c r="B245" s="159"/>
+      <c r="B245" s="148"/>
       <c r="C245" s="22" t="s">
         <v>148</v>
       </c>
@@ -19025,11 +19056,11 @@
       <c r="L245" s="83"/>
       <c r="M245" s="11"/>
     </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>1</v>
       </c>
-      <c r="B246" s="183" t="s">
+      <c r="B246" s="193" t="s">
         <v>108</v>
       </c>
       <c r="C246" s="20" t="e" vm="32">
@@ -19061,12 +19092,12 @@
       <c r="L246" s="83"/>
       <c r="M246" s="11"/>
     </row>
-    <row r="247" spans="1:16" ht="15.4" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:16" ht="15.4" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>1</v>
       </c>
-      <c r="B247" s="183"/>
-      <c r="C247" s="207" t="s">
+      <c r="B247" s="193"/>
+      <c r="C247" s="135" t="s">
         <v>407</v>
       </c>
       <c r="D247" s="20" t="str">
@@ -19105,7 +19136,7 @@
       </c>
     </row>
     <row r="248" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B248" s="161" t="s">
+      <c r="B248" s="182" t="s">
         <v>29</v>
       </c>
       <c r="C248" s="52" t="e" vm="22">
@@ -19141,7 +19172,7 @@
       </c>
     </row>
     <row r="249" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B249" s="161"/>
+      <c r="B249" s="182"/>
       <c r="C249" s="52" t="s">
         <v>69</v>
       </c>
@@ -19177,7 +19208,7 @@
       <c r="M249" s="11"/>
     </row>
     <row r="250" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B250" s="180" t="s">
+      <c r="B250" s="172" t="s">
         <v>393</v>
       </c>
       <c r="C250" s="47" t="e" vm="33">
@@ -19219,7 +19250,7 @@
       </c>
     </row>
     <row r="251" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B251" s="180"/>
+      <c r="B251" s="172"/>
       <c r="C251" s="78" t="s">
         <v>152</v>
       </c>
@@ -19256,7 +19287,7 @@
       <c r="M251" s="11"/>
     </row>
     <row r="252" spans="1:16" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B252" s="180" t="s">
+      <c r="B252" s="172" t="s">
         <v>393</v>
       </c>
       <c r="C252" s="47" t="e" vm="33">
@@ -19289,7 +19320,7 @@
       <c r="M252" s="11"/>
     </row>
     <row r="253" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B253" s="180"/>
+      <c r="B253" s="172"/>
       <c r="C253" s="78" t="s">
         <v>152</v>
       </c>
@@ -19332,7 +19363,7 @@
       </c>
     </row>
     <row r="254" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B254" s="168" t="s">
+      <c r="B254" s="157" t="s">
         <v>66</v>
       </c>
       <c r="C254" s="98" t="e" vm="11">
@@ -19364,7 +19395,7 @@
       <c r="M254" s="126"/>
     </row>
     <row r="255" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B255" s="169"/>
+      <c r="B255" s="181"/>
       <c r="C255" s="52" t="s">
         <v>37</v>
       </c>
@@ -19400,7 +19431,7 @@
       <c r="M255" s="11"/>
     </row>
     <row r="256" spans="1:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B256" s="168" t="s">
+      <c r="B256" s="157" t="s">
         <v>154</v>
       </c>
       <c r="C256" s="52" t="e" vm="34">
@@ -19433,7 +19464,7 @@
       <c r="M256" s="126"/>
     </row>
     <row r="257" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B257" s="169"/>
+      <c r="B257" s="181"/>
       <c r="C257" s="52" t="s">
         <v>155</v>
       </c>
@@ -19475,7 +19506,7 @@
       </c>
     </row>
     <row r="258" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B258" s="172" t="s">
+      <c r="B258" s="187" t="s">
         <v>35</v>
       </c>
       <c r="C258" s="52" t="e" vm="30">
@@ -19508,7 +19539,7 @@
       <c r="M258" s="11"/>
     </row>
     <row r="259" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B259" s="173"/>
+      <c r="B259" s="188"/>
       <c r="C259" s="52" t="s">
         <v>123</v>
       </c>
@@ -19553,7 +19584,7 @@
       </c>
     </row>
     <row r="260" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B260" s="174" t="s">
+      <c r="B260" s="189" t="s">
         <v>394</v>
       </c>
       <c r="C260" s="52" t="e" vm="25">
@@ -19586,7 +19617,7 @@
       <c r="M260" s="11"/>
     </row>
     <row r="261" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B261" s="175"/>
+      <c r="B261" s="190"/>
       <c r="C261" s="52" t="s">
         <v>101</v>
       </c>
@@ -19628,7 +19659,7 @@
       </c>
     </row>
     <row r="262" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B262" s="168" t="s">
+      <c r="B262" s="157" t="s">
         <v>161</v>
       </c>
       <c r="C262" s="52" t="e" vm="35">
@@ -19667,7 +19698,7 @@
       </c>
     </row>
     <row r="263" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B263" s="169"/>
+      <c r="B263" s="181"/>
       <c r="C263" s="52" t="s">
         <v>164</v>
       </c>
@@ -19703,7 +19734,7 @@
       <c r="M263" s="11"/>
     </row>
     <row r="264" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B264" s="170" t="s">
+      <c r="B264" s="176" t="s">
         <v>161</v>
       </c>
       <c r="C264" s="52" t="e" vm="25">
@@ -19742,7 +19773,7 @@
       </c>
     </row>
     <row r="265" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B265" s="171"/>
+      <c r="B265" s="177"/>
       <c r="C265" s="52" t="s">
         <v>101</v>
       </c>
@@ -19778,7 +19809,7 @@
       <c r="M265" s="11"/>
     </row>
     <row r="266" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B266" s="176" t="s">
+      <c r="B266" s="194" t="s">
         <v>142</v>
       </c>
       <c r="C266" s="52" t="e" vm="25">
@@ -19811,7 +19842,7 @@
       <c r="M266" s="11"/>
     </row>
     <row r="267" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B267" s="177"/>
+      <c r="B267" s="195"/>
       <c r="C267" s="52" t="s">
         <v>101</v>
       </c>
@@ -19853,7 +19884,7 @@
       </c>
     </row>
     <row r="268" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B268" s="170" t="s">
+      <c r="B268" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C268" s="52" t="e" vm="36">
@@ -19886,7 +19917,7 @@
       <c r="M268" s="126"/>
     </row>
     <row r="269" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B269" s="171"/>
+      <c r="B269" s="177"/>
       <c r="C269" s="52" t="s">
         <v>166</v>
       </c>
@@ -19928,7 +19959,7 @@
       </c>
     </row>
     <row r="270" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B270" s="170" t="s">
+      <c r="B270" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C270" s="52" t="e" vm="36">
@@ -19961,7 +19992,7 @@
       <c r="M270" s="126"/>
     </row>
     <row r="271" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B271" s="171"/>
+      <c r="B271" s="177"/>
       <c r="C271" s="52" t="s">
         <v>166</v>
       </c>
@@ -20003,7 +20034,7 @@
       </c>
     </row>
     <row r="272" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B272" s="170" t="s">
+      <c r="B272" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C272" s="52" t="e" vm="37">
@@ -20036,7 +20067,7 @@
       <c r="M272" s="126"/>
     </row>
     <row r="273" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B273" s="171"/>
+      <c r="B273" s="177"/>
       <c r="C273" s="52" t="s">
         <v>170</v>
       </c>
@@ -20078,7 +20109,7 @@
       </c>
     </row>
     <row r="274" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B274" s="170" t="s">
+      <c r="B274" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C274" s="52" t="e" vm="37">
@@ -20111,7 +20142,7 @@
       <c r="M274" s="126"/>
     </row>
     <row r="275" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B275" s="171"/>
+      <c r="B275" s="177"/>
       <c r="C275" s="52" t="s">
         <v>170</v>
       </c>
@@ -20153,7 +20184,7 @@
       </c>
     </row>
     <row r="276" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B276" s="170" t="s">
+      <c r="B276" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C276" s="52" t="e" vm="25">
@@ -20186,7 +20217,7 @@
       <c r="M276" s="126"/>
     </row>
     <row r="277" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B277" s="171"/>
+      <c r="B277" s="177"/>
       <c r="C277" s="52" t="s">
         <v>101</v>
       </c>
@@ -20228,7 +20259,7 @@
       </c>
     </row>
     <row r="278" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B278" s="170" t="s">
+      <c r="B278" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C278" s="52" t="e" vm="36">
@@ -20261,7 +20292,7 @@
       <c r="M278" s="126"/>
     </row>
     <row r="279" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B279" s="171"/>
+      <c r="B279" s="177"/>
       <c r="C279" s="52" t="s">
         <v>166</v>
       </c>
@@ -20303,7 +20334,7 @@
       </c>
     </row>
     <row r="280" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B280" s="170" t="s">
+      <c r="B280" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C280" s="52" t="e" vm="11">
@@ -20335,7 +20366,7 @@
       <c r="M280" s="11"/>
     </row>
     <row r="281" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B281" s="171"/>
+      <c r="B281" s="177"/>
       <c r="C281" s="52" t="s">
         <v>37</v>
       </c>
@@ -20377,7 +20408,7 @@
       </c>
     </row>
     <row r="282" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B282" s="178" t="s">
+      <c r="B282" s="167" t="s">
         <v>154</v>
       </c>
       <c r="C282" s="52" t="e" vm="37">
@@ -20410,7 +20441,7 @@
       <c r="M282" s="126"/>
     </row>
     <row r="283" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B283" s="171"/>
+      <c r="B283" s="177"/>
       <c r="C283" s="52" t="s">
         <v>170</v>
       </c>
@@ -20452,7 +20483,7 @@
       </c>
     </row>
     <row r="284" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B284" s="178" t="s">
+      <c r="B284" s="167" t="s">
         <v>154</v>
       </c>
       <c r="C284" s="52" t="e" vm="37">
@@ -20485,7 +20516,7 @@
       <c r="M284" s="126"/>
     </row>
     <row r="285" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B285" s="171"/>
+      <c r="B285" s="177"/>
       <c r="C285" s="52" t="s">
         <v>170</v>
       </c>
@@ -20527,7 +20558,7 @@
       </c>
     </row>
     <row r="286" spans="2:15" ht="35.15" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B286" s="178" t="s">
+      <c r="B286" s="167" t="s">
         <v>154</v>
       </c>
       <c r="C286" s="52" t="e" vm="36">
@@ -20560,7 +20591,7 @@
       <c r="M286" s="126"/>
     </row>
     <row r="287" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B287" s="179"/>
+      <c r="B287" s="168"/>
       <c r="C287" s="52" t="s">
         <v>166</v>
       </c>
@@ -20602,7 +20633,7 @@
       </c>
     </row>
     <row r="288" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B288" s="170" t="s">
+      <c r="B288" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C288" s="52" t="e" vm="36">
@@ -20635,7 +20666,7 @@
       <c r="M288" s="126"/>
     </row>
     <row r="289" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B289" s="171"/>
+      <c r="B289" s="177"/>
       <c r="C289" s="52" t="s">
         <v>166</v>
       </c>
@@ -20677,7 +20708,7 @@
       </c>
     </row>
     <row r="290" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B290" s="170" t="s">
+      <c r="B290" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C290" s="52" t="e" vm="36">
@@ -20710,7 +20741,7 @@
       <c r="M290" s="126"/>
     </row>
     <row r="291" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B291" s="171"/>
+      <c r="B291" s="177"/>
       <c r="C291" s="52" t="s">
         <v>166</v>
       </c>
@@ -20752,7 +20783,7 @@
       </c>
     </row>
     <row r="292" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B292" s="170" t="s">
+      <c r="B292" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C292" s="52" t="e" vm="36">
@@ -20785,7 +20816,7 @@
       <c r="M292" s="126"/>
     </row>
     <row r="293" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B293" s="171"/>
+      <c r="B293" s="177"/>
       <c r="C293" s="52" t="s">
         <v>166</v>
       </c>
@@ -20827,7 +20858,7 @@
       </c>
     </row>
     <row r="294" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B294" s="170" t="s">
+      <c r="B294" s="176" t="s">
         <v>44</v>
       </c>
       <c r="C294" s="52" t="e" vm="11">
@@ -20859,7 +20890,7 @@
       <c r="M294" s="11"/>
     </row>
     <row r="295" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B295" s="171"/>
+      <c r="B295" s="177"/>
       <c r="C295" s="52" t="s">
         <v>37</v>
       </c>
@@ -20901,7 +20932,7 @@
       </c>
     </row>
     <row r="296" spans="2:16" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B296" s="174" t="s">
+      <c r="B296" s="189" t="s">
         <v>394</v>
       </c>
       <c r="C296" s="52" t="e" vm="25">
@@ -20934,7 +20965,7 @@
       <c r="M296" s="11"/>
     </row>
     <row r="297" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B297" s="175"/>
+      <c r="B297" s="190"/>
       <c r="C297" s="52" t="s">
         <v>101</v>
       </c>
@@ -20976,7 +21007,7 @@
       </c>
     </row>
     <row r="298" spans="2:16" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B298" s="164" t="s">
+      <c r="B298" s="165" t="s">
         <v>33</v>
       </c>
       <c r="C298" s="52" t="e" vm="25">
@@ -21009,7 +21040,7 @@
       <c r="M298" s="11"/>
     </row>
     <row r="299" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B299" s="165"/>
+      <c r="B299" s="166"/>
       <c r="C299" s="52" t="s">
         <v>101</v>
       </c>
@@ -21051,7 +21082,7 @@
       </c>
     </row>
     <row r="300" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B300" s="139" t="s">
+      <c r="B300" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C300" s="63" t="e" vm="25">
@@ -21084,7 +21115,7 @@
       <c r="M300" s="11"/>
     </row>
     <row r="301" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B301" s="140"/>
+      <c r="B301" s="141"/>
       <c r="C301" s="63" t="s">
         <v>101</v>
       </c>
@@ -21126,7 +21157,7 @@
       </c>
     </row>
     <row r="302" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B302" s="139" t="s">
+      <c r="B302" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C302" s="63" t="e" vm="25">
@@ -21159,7 +21190,7 @@
       <c r="M302" s="11"/>
     </row>
     <row r="303" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B303" s="140"/>
+      <c r="B303" s="141"/>
       <c r="C303" s="63" t="s">
         <v>101</v>
       </c>
@@ -21276,7 +21307,7 @@
       </c>
     </row>
     <row r="306" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B306" s="139" t="s">
+      <c r="B306" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C306" s="63" t="e" vm="25">
@@ -21309,7 +21340,7 @@
       <c r="M306" s="11"/>
     </row>
     <row r="307" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B307" s="140"/>
+      <c r="B307" s="141"/>
       <c r="C307" s="63" t="s">
         <v>101</v>
       </c>
@@ -21351,7 +21382,7 @@
       </c>
     </row>
     <row r="308" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B308" s="178" t="s">
+      <c r="B308" s="167" t="s">
         <v>33</v>
       </c>
       <c r="C308" s="52" t="e" vm="25">
@@ -21384,7 +21415,7 @@
       <c r="M308" s="11"/>
     </row>
     <row r="309" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B309" s="179"/>
+      <c r="B309" s="168"/>
       <c r="C309" s="52" t="s">
         <v>101</v>
       </c>
@@ -21426,7 +21457,7 @@
       </c>
     </row>
     <row r="310" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B310" s="178" t="s">
+      <c r="B310" s="167" t="s">
         <v>154</v>
       </c>
       <c r="C310" s="52" t="e" vm="36">
@@ -21459,7 +21490,7 @@
       <c r="M310" s="126"/>
     </row>
     <row r="311" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B311" s="179"/>
+      <c r="B311" s="168"/>
       <c r="C311" s="52" t="s">
         <v>166</v>
       </c>
@@ -21501,7 +21532,7 @@
       </c>
     </row>
     <row r="312" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B312" s="170" t="s">
+      <c r="B312" s="176" t="s">
         <v>26</v>
       </c>
       <c r="C312" s="52" t="e" vm="25">
@@ -21534,7 +21565,7 @@
       <c r="M312" s="11"/>
     </row>
     <row r="313" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B313" s="171"/>
+      <c r="B313" s="177"/>
       <c r="C313" s="52" t="s">
         <v>101</v>
       </c>
@@ -21576,7 +21607,7 @@
       </c>
     </row>
     <row r="314" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B314" s="178" t="s">
+      <c r="B314" s="167" t="s">
         <v>32</v>
       </c>
       <c r="C314" s="52" t="e" vm="36">
@@ -21609,7 +21640,7 @@
       <c r="M314" s="126"/>
     </row>
     <row r="315" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B315" s="179"/>
+      <c r="B315" s="168"/>
       <c r="C315" s="52" t="s">
         <v>166</v>
       </c>
@@ -21651,7 +21682,7 @@
       </c>
     </row>
     <row r="316" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B316" s="178" t="s">
+      <c r="B316" s="167" t="s">
         <v>32</v>
       </c>
       <c r="C316" s="52" t="e" vm="36">
@@ -21684,7 +21715,7 @@
       <c r="M316" s="126"/>
     </row>
     <row r="317" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B317" s="179"/>
+      <c r="B317" s="168"/>
       <c r="C317" s="52" t="s">
         <v>166</v>
       </c>
@@ -21726,7 +21757,7 @@
       </c>
     </row>
     <row r="318" spans="2:15" ht="14.65" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B318" s="178" t="s">
+      <c r="B318" s="167" t="s">
         <v>32</v>
       </c>
       <c r="C318" s="52" t="e" vm="36">
@@ -21759,7 +21790,7 @@
       <c r="M318" s="126"/>
     </row>
     <row r="319" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B319" s="179"/>
+      <c r="B319" s="168"/>
       <c r="C319" s="52" t="s">
         <v>166</v>
       </c>
@@ -21801,7 +21832,7 @@
       </c>
     </row>
     <row r="320" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B320" s="178" t="s">
+      <c r="B320" s="167" t="s">
         <v>32</v>
       </c>
       <c r="C320" s="52" t="e" vm="36">
@@ -21834,7 +21865,7 @@
       <c r="M320" s="126"/>
     </row>
     <row r="321" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B321" s="179"/>
+      <c r="B321" s="168"/>
       <c r="C321" s="52" t="s">
         <v>166</v>
       </c>
@@ -21876,7 +21907,7 @@
       </c>
     </row>
     <row r="322" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B322" s="139" t="s">
+      <c r="B322" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C322" s="52" t="e" vm="11">
@@ -21908,7 +21939,7 @@
       <c r="M322" s="11"/>
     </row>
     <row r="323" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B323" s="140"/>
+      <c r="B323" s="141"/>
       <c r="C323" s="52" t="s">
         <v>37</v>
       </c>
@@ -21953,7 +21984,7 @@
       <c r="A324" s="5">
         <v>1</v>
       </c>
-      <c r="B324" s="147" t="s">
+      <c r="B324" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C324" s="16" t="e" vm="25">
@@ -21989,7 +22020,7 @@
       <c r="A325" s="5">
         <v>1</v>
       </c>
-      <c r="B325" s="148"/>
+      <c r="B325" s="143"/>
       <c r="C325" s="16" t="s">
         <v>101</v>
       </c>
@@ -22034,7 +22065,7 @@
       </c>
     </row>
     <row r="326" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B326" s="164" t="s">
+      <c r="B326" s="165" t="s">
         <v>33</v>
       </c>
       <c r="C326" s="52" t="e" vm="38">
@@ -22067,7 +22098,7 @@
       <c r="M326" s="11"/>
     </row>
     <row r="327" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B327" s="165"/>
+      <c r="B327" s="166"/>
       <c r="C327" s="52" t="s">
         <v>206</v>
       </c>
@@ -22109,7 +22140,7 @@
       </c>
     </row>
     <row r="328" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B328" s="139" t="s">
+      <c r="B328" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C328" s="52" t="e" vm="11">
@@ -22141,7 +22172,7 @@
       <c r="M328" s="11"/>
     </row>
     <row r="329" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B329" s="140"/>
+      <c r="B329" s="141"/>
       <c r="C329" s="52" t="s">
         <v>37</v>
       </c>
@@ -22183,7 +22214,7 @@
       </c>
     </row>
     <row r="330" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B330" s="164" t="s">
+      <c r="B330" s="165" t="s">
         <v>33</v>
       </c>
       <c r="C330" s="52" t="e" vm="25">
@@ -22216,7 +22247,7 @@
       <c r="M330" s="11"/>
     </row>
     <row r="331" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B331" s="165"/>
+      <c r="B331" s="166"/>
       <c r="C331" s="52" t="s">
         <v>101</v>
       </c>
@@ -22258,7 +22289,7 @@
       </c>
     </row>
     <row r="332" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B332" s="166" t="s">
+      <c r="B332" s="151" t="s">
         <v>209</v>
       </c>
       <c r="C332" s="52" t="e" vm="25">
@@ -22291,7 +22322,7 @@
       <c r="M332" s="11"/>
     </row>
     <row r="333" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B333" s="167"/>
+      <c r="B333" s="196"/>
       <c r="C333" s="52" t="s">
         <v>101</v>
       </c>
@@ -22333,7 +22364,7 @@
       </c>
     </row>
     <row r="334" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B334" s="139" t="s">
+      <c r="B334" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C334" s="52" t="e" vm="11">
@@ -22365,7 +22396,7 @@
       <c r="M334" s="11"/>
     </row>
     <row r="335" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B335" s="140"/>
+      <c r="B335" s="141"/>
       <c r="C335" s="52" t="s">
         <v>37</v>
       </c>
@@ -22410,7 +22441,7 @@
       </c>
     </row>
     <row r="336" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B336" s="139" t="s">
+      <c r="B336" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C336" s="52" t="e" vm="11">
@@ -22442,7 +22473,7 @@
       <c r="M336" s="11"/>
     </row>
     <row r="337" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B337" s="140"/>
+      <c r="B337" s="141"/>
       <c r="C337" s="52" t="s">
         <v>37</v>
       </c>
@@ -22483,7 +22514,7 @@
       </c>
     </row>
     <row r="338" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B338" s="139" t="s">
+      <c r="B338" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C338" s="52" t="e" vm="25">
@@ -22516,7 +22547,7 @@
       <c r="M338" s="11"/>
     </row>
     <row r="339" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B339" s="140"/>
+      <c r="B339" s="141"/>
       <c r="C339" s="52" t="s">
         <v>101</v>
       </c>
@@ -22639,7 +22670,7 @@
       </c>
     </row>
     <row r="342" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B342" s="147" t="s">
+      <c r="B342" s="142" t="s">
         <v>42</v>
       </c>
       <c r="C342" s="52" t="e" vm="11">
@@ -22671,7 +22702,7 @@
       <c r="M342" s="11"/>
     </row>
     <row r="343" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B343" s="148"/>
+      <c r="B343" s="143"/>
       <c r="C343" s="99" t="s">
         <v>37</v>
       </c>
@@ -22716,7 +22747,7 @@
       </c>
     </row>
     <row r="344" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B344" s="147" t="s">
+      <c r="B344" s="142" t="s">
         <v>42</v>
       </c>
       <c r="C344" s="52" t="e" vm="11">
@@ -22751,7 +22782,7 @@
       </c>
     </row>
     <row r="345" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B345" s="148"/>
+      <c r="B345" s="143"/>
       <c r="C345" s="52" t="s">
         <v>37</v>
       </c>
@@ -22793,7 +22824,7 @@
       </c>
     </row>
     <row r="346" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B346" s="156" t="s">
+      <c r="B346" s="197" t="s">
         <v>35</v>
       </c>
       <c r="C346" s="52" t="e" vm="11">
@@ -22825,7 +22856,7 @@
       <c r="M346" s="11"/>
     </row>
     <row r="347" spans="1:17" ht="57.6" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B347" s="157"/>
+      <c r="B347" s="198"/>
       <c r="C347" s="52" t="s">
         <v>37</v>
       </c>
@@ -22873,7 +22904,7 @@
       </c>
     </row>
     <row r="348" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B348" s="138" t="s">
+      <c r="B348" s="199" t="s">
         <v>32</v>
       </c>
       <c r="C348" s="52" t="e" vm="11">
@@ -22905,7 +22936,7 @@
       <c r="M348" s="11"/>
     </row>
     <row r="349" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B349" s="138"/>
+      <c r="B349" s="199"/>
       <c r="C349" s="52" t="s">
         <v>37</v>
       </c>
@@ -23028,7 +23059,7 @@
       <c r="A352" s="5">
         <v>0</v>
       </c>
-      <c r="B352" s="151" t="s">
+      <c r="B352" s="144" t="s">
         <v>223</v>
       </c>
       <c r="C352" s="5" t="e" vm="39">
@@ -23062,7 +23093,7 @@
       <c r="N352" s="13"/>
     </row>
     <row r="353" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B353" s="152"/>
+      <c r="B353" s="204"/>
       <c r="C353" s="52" t="s">
         <v>224</v>
       </c>
@@ -23256,7 +23287,7 @@
       </c>
     </row>
     <row r="358" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B358" s="147" t="s">
+      <c r="B358" s="142" t="s">
         <v>42</v>
       </c>
       <c r="C358" s="52" t="e" vm="11">
@@ -23288,7 +23319,7 @@
       <c r="M358" s="11"/>
     </row>
     <row r="359" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B359" s="148"/>
+      <c r="B359" s="143"/>
       <c r="C359" s="99" t="s">
         <v>37</v>
       </c>
@@ -23331,7 +23362,7 @@
     </row>
     <row r="360" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="13"/>
-      <c r="B360" s="151" t="s">
+      <c r="B360" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C360" s="52" t="e" vm="11">
@@ -23364,7 +23395,7 @@
     </row>
     <row r="361" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="13"/>
-      <c r="B361" s="151"/>
+      <c r="B361" s="144"/>
       <c r="C361" s="52" t="s">
         <v>37</v>
       </c>
@@ -23406,7 +23437,7 @@
       </c>
     </row>
     <row r="362" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B362" s="162" t="s">
+      <c r="B362" s="200" t="s">
         <v>44</v>
       </c>
       <c r="C362" s="52" t="e" vm="11">
@@ -23438,7 +23469,7 @@
       <c r="M362" s="123"/>
     </row>
     <row r="363" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B363" s="163"/>
+      <c r="B363" s="201"/>
       <c r="C363" s="99" t="s">
         <v>37</v>
       </c>
@@ -23480,7 +23511,7 @@
       </c>
     </row>
     <row r="364" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B364" s="147" t="s">
+      <c r="B364" s="142" t="s">
         <v>42</v>
       </c>
       <c r="C364" s="52" t="e" vm="11">
@@ -23512,7 +23543,7 @@
       <c r="M364" s="11"/>
     </row>
     <row r="365" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B365" s="148"/>
+      <c r="B365" s="143"/>
       <c r="C365" s="99" t="s">
         <v>37</v>
       </c>
@@ -23554,7 +23585,7 @@
       </c>
     </row>
     <row r="366" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B366" s="151" t="s">
+      <c r="B366" s="144" t="s">
         <v>233</v>
       </c>
       <c r="C366" s="52" t="e" vm="29">
@@ -23587,7 +23618,7 @@
       <c r="M366" s="123"/>
     </row>
     <row r="367" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B367" s="151"/>
+      <c r="B367" s="144"/>
       <c r="C367" s="52" t="s">
         <v>121</v>
       </c>
@@ -23629,7 +23660,7 @@
       </c>
     </row>
     <row r="368" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B368" s="151" t="s">
+      <c r="B368" s="144" t="s">
         <v>233</v>
       </c>
       <c r="C368" s="52" t="e" vm="40">
@@ -23662,7 +23693,7 @@
       <c r="M368" s="123"/>
     </row>
     <row r="369" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B369" s="151"/>
+      <c r="B369" s="144"/>
       <c r="C369" s="52" t="s">
         <v>236</v>
       </c>
@@ -23704,7 +23735,7 @@
       </c>
     </row>
     <row r="370" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B370" s="149" t="s">
+      <c r="B370" s="202" t="s">
         <v>35</v>
       </c>
       <c r="C370" s="47" t="e" vm="11">
@@ -23736,7 +23767,7 @@
       <c r="M370" s="11"/>
     </row>
     <row r="371" spans="1:16" ht="28.8" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B371" s="150"/>
+      <c r="B371" s="203"/>
       <c r="C371" s="93" t="s">
         <v>37</v>
       </c>
@@ -23860,7 +23891,7 @@
       </c>
     </row>
     <row r="374" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B374" s="147" t="s">
+      <c r="B374" s="142" t="s">
         <v>42</v>
       </c>
       <c r="C374" s="52" t="e" vm="11">
@@ -23892,7 +23923,7 @@
       <c r="M374" s="11"/>
     </row>
     <row r="375" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B375" s="148"/>
+      <c r="B375" s="143"/>
       <c r="C375" s="52" t="s">
         <v>37</v>
       </c>
@@ -23933,11 +23964,11 @@
         <v>283</v>
       </c>
     </row>
-    <row r="376" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A376" s="5">
         <v>1</v>
       </c>
-      <c r="B376" s="147" t="s">
+      <c r="B376" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C376" s="16" t="e" vm="11">
@@ -23968,11 +23999,11 @@
       <c r="L376" s="83"/>
       <c r="M376" s="11"/>
     </row>
-    <row r="377" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A377" s="5">
         <v>1</v>
       </c>
-      <c r="B377" s="148"/>
+      <c r="B377" s="143"/>
       <c r="C377" s="86" t="s">
         <v>37</v>
       </c>
@@ -24088,7 +24119,7 @@
       </c>
     </row>
     <row r="380" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B380" s="153" t="s">
+      <c r="B380" s="184" t="s">
         <v>102</v>
       </c>
       <c r="C380" s="63" t="e" vm="11">
@@ -24120,7 +24151,7 @@
       <c r="M380" s="11"/>
     </row>
     <row r="381" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B381" s="154"/>
+      <c r="B381" s="185"/>
       <c r="C381" s="90" t="s">
         <v>37</v>
       </c>
@@ -24236,7 +24267,7 @@
       </c>
     </row>
     <row r="384" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B384" s="149" t="s">
+      <c r="B384" s="202" t="s">
         <v>35</v>
       </c>
       <c r="C384" s="52" t="e" vm="41">
@@ -24269,7 +24300,7 @@
       <c r="M384" s="11"/>
     </row>
     <row r="385" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B385" s="150"/>
+      <c r="B385" s="203"/>
       <c r="C385" s="52" t="s">
         <v>244</v>
       </c>
@@ -24310,11 +24341,11 @@
         <v>246</v>
       </c>
     </row>
-    <row r="386" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" s="5">
         <v>1</v>
       </c>
-      <c r="B386" s="147" t="s">
+      <c r="B386" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C386" s="13" t="e" vm="11">
@@ -24345,11 +24376,11 @@
       <c r="L386" s="83"/>
       <c r="M386" s="11"/>
     </row>
-    <row r="387" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" s="5">
         <v>1</v>
       </c>
-      <c r="B387" s="148"/>
+      <c r="B387" s="143"/>
       <c r="C387" s="13" t="s">
         <v>37</v>
       </c>
@@ -24466,7 +24497,7 @@
       </c>
     </row>
     <row r="390" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B390" s="151" t="s">
+      <c r="B390" s="144" t="s">
         <v>249</v>
       </c>
       <c r="C390" s="52" t="e" vm="42">
@@ -24499,7 +24530,7 @@
       <c r="M390" s="123"/>
     </row>
     <row r="391" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B391" s="152"/>
+      <c r="B391" s="204"/>
       <c r="C391" s="52" t="s">
         <v>250</v>
       </c>
@@ -24615,7 +24646,7 @@
       </c>
     </row>
     <row r="394" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B394" s="142" t="s">
+      <c r="B394" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C394" s="52" t="e" vm="11">
@@ -24647,7 +24678,7 @@
       <c r="M394" s="11"/>
     </row>
     <row r="395" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B395" s="143"/>
+      <c r="B395" s="150"/>
       <c r="C395" s="52" t="s">
         <v>37</v>
       </c>
@@ -24689,7 +24720,7 @@
       </c>
     </row>
     <row r="396" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B396" s="151" t="s">
+      <c r="B396" s="144" t="s">
         <v>223</v>
       </c>
       <c r="C396" s="52" t="e" vm="42">
@@ -24722,7 +24753,7 @@
       <c r="M396" s="123"/>
     </row>
     <row r="397" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B397" s="152"/>
+      <c r="B397" s="204"/>
       <c r="C397" s="52" t="s">
         <v>250</v>
       </c>
@@ -24764,7 +24795,7 @@
       </c>
     </row>
     <row r="398" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B398" s="151" t="s">
+      <c r="B398" s="144" t="s">
         <v>249</v>
       </c>
       <c r="C398" s="52" t="e" vm="42">
@@ -24797,7 +24828,7 @@
       <c r="M398" s="123"/>
     </row>
     <row r="399" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B399" s="152"/>
+      <c r="B399" s="204"/>
       <c r="C399" s="52" t="s">
         <v>250</v>
       </c>
@@ -24839,7 +24870,7 @@
       </c>
     </row>
     <row r="400" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B400" s="151" t="s">
+      <c r="B400" s="144" t="s">
         <v>255</v>
       </c>
       <c r="C400" s="52" t="e" vm="29">
@@ -24872,7 +24903,7 @@
       <c r="M400" s="123"/>
     </row>
     <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B401" s="151"/>
+      <c r="B401" s="144"/>
       <c r="C401" s="52" t="s">
         <v>121</v>
       </c>
@@ -24914,7 +24945,7 @@
       </c>
     </row>
     <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B402" s="151" t="s">
+      <c r="B402" s="144" t="s">
         <v>258</v>
       </c>
       <c r="C402" s="52" t="e" vm="29">
@@ -24947,7 +24978,7 @@
       <c r="M402" s="123"/>
     </row>
     <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B403" s="151"/>
+      <c r="B403" s="144"/>
       <c r="C403" s="52" t="s">
         <v>121</v>
       </c>
@@ -24989,7 +25020,7 @@
       </c>
     </row>
     <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B404" s="142" t="s">
+      <c r="B404" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C404" s="52" t="e" vm="11">
@@ -25021,7 +25052,7 @@
       <c r="M404" s="11"/>
     </row>
     <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B405" s="143"/>
+      <c r="B405" s="150"/>
       <c r="C405" s="52" t="s">
         <v>37</v>
       </c>
@@ -25063,7 +25094,7 @@
       </c>
     </row>
     <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B406" s="151" t="s">
+      <c r="B406" s="144" t="s">
         <v>255</v>
       </c>
       <c r="C406" s="52" t="e" vm="29">
@@ -25096,7 +25127,7 @@
       <c r="M406" s="123"/>
     </row>
     <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B407" s="151"/>
+      <c r="B407" s="144"/>
       <c r="C407" s="52" t="s">
         <v>121</v>
       </c>
@@ -25138,7 +25169,7 @@
       </c>
     </row>
     <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B408" s="161" t="s">
+      <c r="B408" s="182" t="s">
         <v>89</v>
       </c>
       <c r="C408" s="52" t="e" vm="22">
@@ -25171,7 +25202,7 @@
       <c r="M408" s="11"/>
     </row>
     <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B409" s="161"/>
+      <c r="B409" s="182"/>
       <c r="C409" s="78" t="s">
         <v>69</v>
       </c>
@@ -25219,7 +25250,7 @@
       <c r="A410" s="5">
         <v>1</v>
       </c>
-      <c r="B410" s="155" t="s">
+      <c r="B410" s="175" t="s">
         <v>89</v>
       </c>
       <c r="C410" s="13" t="e" vm="22">
@@ -25256,7 +25287,7 @@
       <c r="A411" s="5">
         <v>1</v>
       </c>
-      <c r="B411" s="155"/>
+      <c r="B411" s="175"/>
       <c r="C411" s="15" t="s">
         <v>69</v>
       </c>
@@ -25307,7 +25338,7 @@
       <c r="A412" s="5">
         <v>1</v>
       </c>
-      <c r="B412" s="142" t="s">
+      <c r="B412" s="149" t="s">
         <v>382</v>
       </c>
       <c r="C412" s="16" t="e" vm="22">
@@ -25343,7 +25374,7 @@
       <c r="A413" s="5">
         <v>1</v>
       </c>
-      <c r="B413" s="143"/>
+      <c r="B413" s="150"/>
       <c r="C413" s="23" t="s">
         <v>69</v>
       </c>
@@ -25388,7 +25419,7 @@
       </c>
     </row>
     <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B414" s="142" t="s">
+      <c r="B414" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C414" s="63" t="e" vm="25">
@@ -25421,7 +25452,7 @@
       <c r="M414" s="11"/>
     </row>
     <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B415" s="143"/>
+      <c r="B415" s="150"/>
       <c r="C415" s="63" t="s">
         <v>101</v>
       </c>
@@ -25466,7 +25497,7 @@
       <c r="A416" s="5">
         <v>1</v>
       </c>
-      <c r="B416" s="158" t="s">
+      <c r="B416" s="147" t="s">
         <v>380</v>
       </c>
       <c r="C416" s="13" t="e" vm="22">
@@ -25502,7 +25533,7 @@
       <c r="A417" s="5">
         <v>1</v>
       </c>
-      <c r="B417" s="159"/>
+      <c r="B417" s="148"/>
       <c r="C417" s="15" t="s">
         <v>69</v>
       </c>
@@ -25544,7 +25575,7 @@
       </c>
     </row>
     <row r="418" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B418" s="160" t="s">
+      <c r="B418" s="155" t="s">
         <v>316</v>
       </c>
       <c r="C418" s="47" t="e" vm="33">
@@ -25577,7 +25608,7 @@
       <c r="M418" s="11"/>
     </row>
     <row r="419" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B419" s="160"/>
+      <c r="B419" s="155"/>
       <c r="C419" s="78" t="s">
         <v>152</v>
       </c>
@@ -25623,7 +25654,7 @@
       <c r="A420" s="5">
         <v>1</v>
       </c>
-      <c r="B420" s="142" t="s">
+      <c r="B420" s="149" t="s">
         <v>383</v>
       </c>
       <c r="C420" s="13" t="e" vm="43">
@@ -25659,7 +25690,7 @@
       <c r="A421" s="5">
         <v>1</v>
       </c>
-      <c r="B421" s="143"/>
+      <c r="B421" s="150"/>
       <c r="C421" s="13" t="s">
         <v>267</v>
       </c>
@@ -25776,7 +25807,7 @@
       </c>
     </row>
     <row r="424" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B424" s="149" t="s">
+      <c r="B424" s="202" t="s">
         <v>35</v>
       </c>
       <c r="C424" s="95" t="e" vm="25">
@@ -25809,7 +25840,7 @@
       <c r="M424" s="123"/>
     </row>
     <row r="425" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B425" s="150"/>
+      <c r="B425" s="203"/>
       <c r="C425" s="95" t="s">
         <v>101</v>
       </c>
@@ -25851,7 +25882,7 @@
       </c>
     </row>
     <row r="426" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B426" s="149" t="s">
+      <c r="B426" s="202" t="s">
         <v>35</v>
       </c>
       <c r="C426" s="95" t="e" vm="25">
@@ -25884,7 +25915,7 @@
       <c r="M426" s="123"/>
     </row>
     <row r="427" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B427" s="150"/>
+      <c r="B427" s="203"/>
       <c r="C427" s="95" t="s">
         <v>101</v>
       </c>
@@ -26082,7 +26113,7 @@
       </c>
     </row>
     <row r="432" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B432" s="149" t="s">
+      <c r="B432" s="202" t="s">
         <v>35</v>
       </c>
       <c r="C432" s="63" t="e" vm="25">
@@ -26115,7 +26146,7 @@
       <c r="M432" s="123"/>
     </row>
     <row r="433" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B433" s="150"/>
+      <c r="B433" s="203"/>
       <c r="C433" s="63" t="s">
         <v>101</v>
       </c>
@@ -26232,7 +26263,7 @@
       </c>
     </row>
     <row r="436" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B436" s="142" t="s">
+      <c r="B436" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C436" s="52" t="e" vm="11">
@@ -26264,7 +26295,7 @@
       <c r="M436" s="11"/>
     </row>
     <row r="437" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B437" s="143"/>
+      <c r="B437" s="150"/>
       <c r="C437" s="52" t="s">
         <v>37</v>
       </c>
@@ -26306,7 +26337,7 @@
       </c>
     </row>
     <row r="438" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B438" s="139" t="s">
+      <c r="B438" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C438" s="63" t="e" vm="25">
@@ -26339,7 +26370,7 @@
       <c r="M438" s="11"/>
     </row>
     <row r="439" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B439" s="140"/>
+      <c r="B439" s="141"/>
       <c r="C439" s="63" t="s">
         <v>101</v>
       </c>
@@ -26384,7 +26415,7 @@
       <c r="A440" s="5">
         <v>1</v>
       </c>
-      <c r="B440" s="145" t="s">
+      <c r="B440" s="206" t="s">
         <v>382</v>
       </c>
       <c r="C440" s="101" t="e" vm="43">
@@ -26420,7 +26451,7 @@
       <c r="A441" s="5">
         <v>1</v>
       </c>
-      <c r="B441" s="146"/>
+      <c r="B441" s="207"/>
       <c r="C441" s="101" t="s">
         <v>267</v>
       </c>
@@ -26465,7 +26496,7 @@
       <c r="A442" s="5">
         <v>1</v>
       </c>
-      <c r="B442" s="139" t="s">
+      <c r="B442" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C442" s="13" t="e" vm="43">
@@ -26501,7 +26532,7 @@
       <c r="A443" s="5">
         <v>1</v>
       </c>
-      <c r="B443" s="140"/>
+      <c r="B443" s="141"/>
       <c r="C443" s="13" t="s">
         <v>267</v>
       </c>
@@ -26617,7 +26648,7 @@
       </c>
     </row>
     <row r="446" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B446" s="142" t="s">
+      <c r="B446" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C446" s="63" t="e" vm="25">
@@ -26650,7 +26681,7 @@
       <c r="M446" s="11"/>
     </row>
     <row r="447" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B447" s="143"/>
+      <c r="B447" s="150"/>
       <c r="C447" s="63" t="s">
         <v>101</v>
       </c>
@@ -26692,7 +26723,7 @@
       </c>
     </row>
     <row r="448" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B448" s="147" t="s">
+      <c r="B448" s="142" t="s">
         <v>33</v>
       </c>
       <c r="C448" s="63" t="e" vm="25">
@@ -26725,7 +26756,7 @@
       <c r="M448" s="11"/>
     </row>
     <row r="449" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B449" s="148"/>
+      <c r="B449" s="143"/>
       <c r="C449" s="63" t="s">
         <v>101</v>
       </c>
@@ -26767,7 +26798,7 @@
       </c>
     </row>
     <row r="450" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B450" s="144" t="s">
+      <c r="B450" s="205" t="s">
         <v>35</v>
       </c>
       <c r="C450" s="95" t="e" vm="25">
@@ -26842,7 +26873,7 @@
       </c>
     </row>
     <row r="452" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B452" s="142" t="s">
+      <c r="B452" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C452" s="13" t="e" vm="11">
@@ -26874,7 +26905,7 @@
       <c r="M452" s="11"/>
     </row>
     <row r="453" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B453" s="143"/>
+      <c r="B453" s="150"/>
       <c r="C453" s="13" t="s">
         <v>37</v>
       </c>
@@ -26916,7 +26947,7 @@
       </c>
     </row>
     <row r="454" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B454" s="144" t="s">
+      <c r="B454" s="205" t="s">
         <v>35</v>
       </c>
       <c r="C454" s="95" t="e" vm="25">
@@ -26991,7 +27022,7 @@
       </c>
     </row>
     <row r="456" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B456" s="142" t="s">
+      <c r="B456" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C456" s="52" t="e" vm="34">
@@ -27024,7 +27055,7 @@
       <c r="M456" s="11"/>
     </row>
     <row r="457" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B457" s="143"/>
+      <c r="B457" s="150"/>
       <c r="C457" s="52" t="s">
         <v>155</v>
       </c>
@@ -27066,7 +27097,7 @@
       </c>
     </row>
     <row r="458" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B458" s="141" t="s">
+      <c r="B458" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C458" s="52" t="e" vm="11">
@@ -27098,7 +27129,7 @@
       <c r="M458" s="11"/>
     </row>
     <row r="459" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B459" s="141"/>
+      <c r="B459" s="154"/>
       <c r="C459" s="52" t="s">
         <v>37</v>
       </c>
@@ -27140,7 +27171,7 @@
       </c>
     </row>
     <row r="460" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B460" s="142" t="s">
+      <c r="B460" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C460" s="52" t="e" vm="11">
@@ -27172,7 +27203,7 @@
       <c r="M460" s="11"/>
     </row>
     <row r="461" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B461" s="143"/>
+      <c r="B461" s="150"/>
       <c r="C461" s="52" t="s">
         <v>37</v>
       </c>
@@ -27214,7 +27245,7 @@
       </c>
     </row>
     <row r="462" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B462" s="142" t="s">
+      <c r="B462" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C462" s="95" t="e" vm="25">
@@ -27247,7 +27278,7 @@
       <c r="M462" s="11"/>
     </row>
     <row r="463" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B463" s="143"/>
+      <c r="B463" s="150"/>
       <c r="C463" s="95" t="s">
         <v>101</v>
       </c>
@@ -27289,7 +27320,7 @@
       </c>
     </row>
     <row r="464" spans="2:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B464" s="142" t="s">
+      <c r="B464" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C464" s="63" t="e" vm="11">
@@ -27321,7 +27352,7 @@
       <c r="M464" s="11"/>
     </row>
     <row r="465" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B465" s="143"/>
+      <c r="B465" s="150"/>
       <c r="C465" s="90" t="s">
         <v>37</v>
       </c>
@@ -27437,7 +27468,7 @@
       </c>
     </row>
     <row r="468" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B468" s="144" t="s">
+      <c r="B468" s="205" t="s">
         <v>35</v>
       </c>
       <c r="C468" s="63" t="e" vm="25">
@@ -27512,7 +27543,7 @@
       </c>
     </row>
     <row r="470" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B470" s="141" t="s">
+      <c r="B470" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C470" s="52" t="e" vm="11">
@@ -27544,7 +27575,7 @@
       <c r="M470" s="11"/>
     </row>
     <row r="471" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B471" s="141"/>
+      <c r="B471" s="154"/>
       <c r="C471" s="52" t="s">
         <v>37</v>
       </c>
@@ -27660,7 +27691,7 @@
       </c>
     </row>
     <row r="474" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B474" s="142" t="s">
+      <c r="B474" s="149" t="s">
         <v>32</v>
       </c>
       <c r="C474" s="52" t="e" vm="34">
@@ -27693,7 +27724,7 @@
       <c r="M474" s="11"/>
     </row>
     <row r="475" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B475" s="143"/>
+      <c r="B475" s="150"/>
       <c r="C475" s="52" t="s">
         <v>155</v>
       </c>
@@ -27734,11 +27765,11 @@
         <v>304</v>
       </c>
     </row>
-    <row r="476" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476" s="5">
         <v>1</v>
       </c>
-      <c r="B476" s="139" t="s">
+      <c r="B476" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C476" s="16" t="e" vm="11">
@@ -27769,11 +27800,11 @@
       <c r="L476" s="83"/>
       <c r="M476" s="11"/>
     </row>
-    <row r="477" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477" s="5">
         <v>1</v>
       </c>
-      <c r="B477" s="140"/>
+      <c r="B477" s="141"/>
       <c r="C477" s="86" t="s">
         <v>37</v>
       </c>
@@ -27815,7 +27846,7 @@
       </c>
     </row>
     <row r="478" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B478" s="139" t="s">
+      <c r="B478" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C478" s="63" t="e" vm="25">
@@ -27848,7 +27879,7 @@
       <c r="M478" s="11"/>
     </row>
     <row r="479" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B479" s="140"/>
+      <c r="B479" s="141"/>
       <c r="C479" s="63" t="s">
         <v>101</v>
       </c>
@@ -27893,7 +27924,7 @@
       <c r="A480" s="5">
         <v>1</v>
       </c>
-      <c r="B480" s="166" t="s">
+      <c r="B480" s="151" t="s">
         <v>307</v>
       </c>
       <c r="C480" s="13" t="e" vm="43">
@@ -27929,7 +27960,7 @@
       <c r="A481" s="5">
         <v>1</v>
       </c>
-      <c r="B481" s="143"/>
+      <c r="B481" s="150"/>
       <c r="C481" s="13" t="s">
         <v>267</v>
       </c>
@@ -27974,7 +28005,7 @@
       <c r="A482" s="5">
         <v>1</v>
       </c>
-      <c r="B482" s="202" t="s">
+      <c r="B482" s="152" t="s">
         <v>381</v>
       </c>
       <c r="C482" s="13" t="e" vm="43">
@@ -28010,7 +28041,7 @@
       <c r="A483" s="5">
         <v>1</v>
       </c>
-      <c r="B483" s="203"/>
+      <c r="B483" s="153"/>
       <c r="C483" s="13" t="s">
         <v>267</v>
       </c>
@@ -28052,7 +28083,7 @@
       </c>
     </row>
     <row r="484" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B484" s="204" t="s">
+      <c r="B484" s="156" t="s">
         <v>90</v>
       </c>
       <c r="C484" s="52" t="e" vm="44">
@@ -28085,7 +28116,7 @@
       <c r="M484" s="11"/>
     </row>
     <row r="485" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B485" s="204"/>
+      <c r="B485" s="156"/>
       <c r="C485" s="52" t="s">
         <v>308</v>
       </c>
@@ -28130,7 +28161,7 @@
       <c r="A486" s="5">
         <v>1</v>
       </c>
-      <c r="B486" s="142" t="s">
+      <c r="B486" s="149" t="s">
         <v>382</v>
       </c>
       <c r="C486" s="16" t="e" vm="25">
@@ -28166,7 +28197,7 @@
       <c r="A487" s="5">
         <v>1</v>
       </c>
-      <c r="B487" s="143"/>
+      <c r="B487" s="150"/>
       <c r="C487" s="16" t="s">
         <v>101</v>
       </c>
@@ -28214,7 +28245,7 @@
       <c r="A488" s="5">
         <v>1</v>
       </c>
-      <c r="B488" s="139" t="s">
+      <c r="B488" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C488" s="81" t="e" vm="25">
@@ -28250,7 +28281,7 @@
       <c r="A489" s="5">
         <v>1</v>
       </c>
-      <c r="B489" s="140"/>
+      <c r="B489" s="141"/>
       <c r="C489" s="81" t="s">
         <v>101</v>
       </c>
@@ -28295,7 +28326,7 @@
       </c>
     </row>
     <row r="490" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B490" s="139" t="s">
+      <c r="B490" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C490" s="95" t="e" vm="45">
@@ -28328,7 +28359,7 @@
       <c r="M490" s="11"/>
     </row>
     <row r="491" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B491" s="140"/>
+      <c r="B491" s="141"/>
       <c r="C491" s="108" t="s">
         <v>310</v>
       </c>
@@ -28373,7 +28404,7 @@
       <c r="A492" s="5">
         <v>1</v>
       </c>
-      <c r="B492" s="166" t="s">
+      <c r="B492" s="151" t="s">
         <v>307</v>
       </c>
       <c r="C492" s="81" t="e" vm="46">
@@ -28409,7 +28440,7 @@
       <c r="A493" s="5">
         <v>1</v>
       </c>
-      <c r="B493" s="143"/>
+      <c r="B493" s="150"/>
       <c r="C493" s="105" t="s">
         <v>311</v>
       </c>
@@ -28452,7 +28483,7 @@
       <c r="A494" s="5">
         <v>1</v>
       </c>
-      <c r="B494" s="166" t="s">
+      <c r="B494" s="151" t="s">
         <v>307</v>
       </c>
       <c r="C494" s="81" t="e" vm="46">
@@ -28488,7 +28519,7 @@
       <c r="A495" s="5">
         <v>1</v>
       </c>
-      <c r="B495" s="143"/>
+      <c r="B495" s="150"/>
       <c r="C495" s="105" t="s">
         <v>311</v>
       </c>
@@ -28528,7 +28559,7 @@
       </c>
     </row>
     <row r="496" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B496" s="151" t="s">
+      <c r="B496" s="144" t="s">
         <v>32</v>
       </c>
       <c r="C496" s="52" t="e" vm="44">
@@ -28561,7 +28592,7 @@
       <c r="M496" s="11"/>
     </row>
     <row r="497" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B497" s="151"/>
+      <c r="B497" s="144"/>
       <c r="C497" s="52" t="s">
         <v>308</v>
       </c>
@@ -28603,7 +28634,7 @@
       </c>
     </row>
     <row r="498" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B498" s="139" t="s">
+      <c r="B498" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C498" s="52" t="e" vm="11">
@@ -28635,7 +28666,7 @@
       <c r="M498" s="11"/>
     </row>
     <row r="499" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B499" s="140"/>
+      <c r="B499" s="141"/>
       <c r="C499" s="52" t="s">
         <v>37</v>
       </c>
@@ -28676,11 +28707,11 @@
         <v>362</v>
       </c>
     </row>
-    <row r="500" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" s="5">
         <v>1</v>
       </c>
-      <c r="B500" s="139" t="s">
+      <c r="B500" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C500" s="13" t="e" vm="11">
@@ -28711,11 +28742,11 @@
       <c r="L500" s="128"/>
       <c r="M500" s="11"/>
     </row>
-    <row r="501" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" s="5">
         <v>1</v>
       </c>
-      <c r="B501" s="140"/>
+      <c r="B501" s="141"/>
       <c r="C501" s="13" t="s">
         <v>37</v>
       </c>
@@ -28757,7 +28788,7 @@
       </c>
     </row>
     <row r="502" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B502" s="139" t="s">
+      <c r="B502" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C502" s="52" t="e" vm="11">
@@ -28789,7 +28820,7 @@
       <c r="M502" s="11"/>
     </row>
     <row r="503" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B503" s="140"/>
+      <c r="B503" s="141"/>
       <c r="C503" s="52" t="s">
         <v>37</v>
       </c>
@@ -28831,7 +28862,7 @@
       </c>
     </row>
     <row r="504" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B504" s="160" t="s">
+      <c r="B504" s="155" t="s">
         <v>316</v>
       </c>
       <c r="C504" s="78" t="e" vm="47">
@@ -28864,7 +28895,7 @@
       <c r="M504" s="11"/>
     </row>
     <row r="505" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B505" s="160"/>
+      <c r="B505" s="155"/>
       <c r="C505" s="78" t="s">
         <v>320</v>
       </c>
@@ -28909,7 +28940,7 @@
       <c r="A506" s="5">
         <v>1</v>
       </c>
-      <c r="B506" s="158" t="s">
+      <c r="B506" s="147" t="s">
         <v>380</v>
       </c>
       <c r="C506" s="101" t="e" vm="43">
@@ -28945,7 +28976,7 @@
       <c r="A507" s="5">
         <v>1</v>
       </c>
-      <c r="B507" s="159"/>
+      <c r="B507" s="148"/>
       <c r="C507" s="101" t="s">
         <v>267</v>
       </c>
@@ -28987,7 +29018,7 @@
       </c>
     </row>
     <row r="508" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B508" s="141" t="s">
+      <c r="B508" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C508" s="52" t="e" vm="11">
@@ -29019,7 +29050,7 @@
       <c r="M508" s="11"/>
     </row>
     <row r="509" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B509" s="141"/>
+      <c r="B509" s="154"/>
       <c r="C509" s="52" t="s">
         <v>37</v>
       </c>
@@ -29060,11 +29091,11 @@
         <v>369</v>
       </c>
     </row>
-    <row r="510" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" s="5">
         <v>1</v>
       </c>
-      <c r="B510" s="147" t="s">
+      <c r="B510" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C510" s="16" t="e" vm="11">
@@ -29095,11 +29126,11 @@
       <c r="L510" s="83"/>
       <c r="M510" s="11"/>
     </row>
-    <row r="511" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" s="5">
         <v>1</v>
       </c>
-      <c r="B511" s="148"/>
+      <c r="B511" s="143"/>
       <c r="C511" s="86" t="s">
         <v>37</v>
       </c>
@@ -29141,7 +29172,7 @@
       </c>
     </row>
     <row r="512" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B512" s="141" t="s">
+      <c r="B512" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C512" s="63" t="e" vm="11">
@@ -29173,7 +29204,7 @@
       <c r="M512" s="11"/>
     </row>
     <row r="513" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B513" s="141"/>
+      <c r="B513" s="154"/>
       <c r="C513" s="90" t="s">
         <v>37</v>
       </c>
@@ -29215,7 +29246,7 @@
       </c>
     </row>
     <row r="514" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B514" s="141" t="s">
+      <c r="B514" s="154" t="s">
         <v>42</v>
       </c>
       <c r="C514" s="63" t="e" vm="11">
@@ -29247,7 +29278,7 @@
       <c r="M514" s="11"/>
     </row>
     <row r="515" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B515" s="141"/>
+      <c r="B515" s="154"/>
       <c r="C515" s="90" t="s">
         <v>37</v>
       </c>
@@ -29362,11 +29393,11 @@
         <v>329</v>
       </c>
     </row>
-    <row r="518" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518" s="5">
         <v>1</v>
       </c>
-      <c r="B518" s="139" t="s">
+      <c r="B518" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C518" s="13" t="e" vm="11">
@@ -29397,11 +29428,11 @@
       <c r="L518" s="83"/>
       <c r="M518" s="11"/>
     </row>
-    <row r="519" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519" s="5">
         <v>1</v>
       </c>
-      <c r="B519" s="140"/>
+      <c r="B519" s="141"/>
       <c r="C519" s="13" t="s">
         <v>37</v>
       </c>
@@ -29446,7 +29477,7 @@
       <c r="A520" s="5">
         <v>1</v>
       </c>
-      <c r="B520" s="142" t="s">
+      <c r="B520" s="149" t="s">
         <v>382</v>
       </c>
       <c r="C520" s="101" t="e" vm="43">
@@ -29482,7 +29513,7 @@
       <c r="A521" s="5">
         <v>1</v>
       </c>
-      <c r="B521" s="143"/>
+      <c r="B521" s="150"/>
       <c r="C521" s="101" t="s">
         <v>267</v>
       </c>
@@ -29601,7 +29632,7 @@
       <c r="A524" s="5">
         <v>1</v>
       </c>
-      <c r="B524" s="139" t="s">
+      <c r="B524" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C524" s="81" t="e" vm="45">
@@ -29639,7 +29670,7 @@
       <c r="A525" s="5">
         <v>1</v>
       </c>
-      <c r="B525" s="140"/>
+      <c r="B525" s="141"/>
       <c r="C525" s="105" t="s">
         <v>310</v>
       </c>
@@ -29687,7 +29718,7 @@
       <c r="A526" s="5">
         <v>1</v>
       </c>
-      <c r="B526" s="142" t="s">
+      <c r="B526" s="149" t="s">
         <v>382</v>
       </c>
       <c r="C526" s="13" t="e" vm="22">
@@ -29723,7 +29754,7 @@
       <c r="A527" s="5">
         <v>1</v>
       </c>
-      <c r="B527" s="143"/>
+      <c r="B527" s="150"/>
       <c r="C527" s="15" t="s">
         <v>69</v>
       </c>
@@ -29764,7 +29795,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="528" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A528" s="5">
         <v>1</v>
       </c>
@@ -29799,7 +29830,7 @@
       <c r="L528" s="83"/>
       <c r="M528" s="11"/>
     </row>
-    <row r="529" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A529" s="5">
         <v>1</v>
       </c>
@@ -29934,7 +29965,7 @@
       <c r="A532" s="13">
         <v>1</v>
       </c>
-      <c r="B532" s="185" t="s">
+      <c r="B532" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C532" s="117" t="e" vm="48">
@@ -29970,7 +30001,7 @@
       <c r="A533" s="13">
         <v>1</v>
       </c>
-      <c r="B533" s="185"/>
+      <c r="B533" s="139"/>
       <c r="C533" s="117" t="s">
         <v>340</v>
       </c>
@@ -30018,7 +30049,7 @@
       <c r="A534" s="5">
         <v>1</v>
       </c>
-      <c r="B534" s="147" t="s">
+      <c r="B534" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C534" s="114" t="e" vm="22">
@@ -30054,7 +30085,7 @@
       <c r="A535" s="5">
         <v>1</v>
       </c>
-      <c r="B535" s="148"/>
+      <c r="B535" s="143"/>
       <c r="C535" s="23" t="s">
         <v>69</v>
       </c>
@@ -30180,7 +30211,7 @@
       <c r="A538" s="5">
         <v>1</v>
       </c>
-      <c r="B538" s="147" t="s">
+      <c r="B538" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C538" s="16" t="e" vm="25">
@@ -30216,7 +30247,7 @@
       <c r="A539" s="5">
         <v>1</v>
       </c>
-      <c r="B539" s="148"/>
+      <c r="B539" s="143"/>
       <c r="C539" s="16" t="s">
         <v>101</v>
       </c>
@@ -30261,7 +30292,7 @@
       <c r="A540" s="5">
         <v>1</v>
       </c>
-      <c r="B540" s="139" t="s">
+      <c r="B540" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C540" s="16" t="e" vm="49">
@@ -30297,7 +30328,7 @@
       <c r="A541" s="5">
         <v>1</v>
       </c>
-      <c r="B541" s="140"/>
+      <c r="B541" s="141"/>
       <c r="C541" s="86" t="s">
         <v>386</v>
       </c>
@@ -30339,7 +30370,7 @@
       </c>
     </row>
     <row r="542" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B542" s="142" t="s">
+      <c r="B542" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C542" s="52" t="e" vm="11">
@@ -30371,7 +30402,7 @@
       <c r="M542" s="11"/>
     </row>
     <row r="543" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B543" s="143"/>
+      <c r="B543" s="150"/>
       <c r="C543" s="52" t="s">
         <v>37</v>
       </c>
@@ -30412,11 +30443,11 @@
         <v>355</v>
       </c>
     </row>
-    <row r="544" spans="1:31" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:31" x14ac:dyDescent="0.35">
       <c r="A544" s="5">
         <v>1</v>
       </c>
-      <c r="B544" s="139" t="s">
+      <c r="B544" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C544" s="13" t="e" vm="11">
@@ -30447,11 +30478,11 @@
       <c r="L544" s="83"/>
       <c r="M544" s="11"/>
     </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A545" s="5">
         <v>1</v>
       </c>
-      <c r="B545" s="140"/>
+      <c r="B545" s="141"/>
       <c r="C545" s="13" t="s">
         <v>37</v>
       </c>
@@ -30493,7 +30524,7 @@
       </c>
     </row>
     <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B546" s="142" t="s">
+      <c r="B546" s="149" t="s">
         <v>44</v>
       </c>
       <c r="C546" s="52" t="e" vm="11">
@@ -30525,7 +30556,7 @@
       <c r="M546" s="11"/>
     </row>
     <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B547" s="143"/>
+      <c r="B547" s="150"/>
       <c r="C547" s="99" t="s">
         <v>37</v>
       </c>
@@ -30570,7 +30601,7 @@
       <c r="A548" s="13">
         <v>1</v>
       </c>
-      <c r="B548" s="185" t="s">
+      <c r="B548" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C548" s="107" t="e" vm="48">
@@ -30606,7 +30637,7 @@
       <c r="A549" s="13">
         <v>1</v>
       </c>
-      <c r="B549" s="185"/>
+      <c r="B549" s="139"/>
       <c r="C549" s="107" t="s">
         <v>340</v>
       </c>
@@ -30650,7 +30681,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A550" s="5">
         <v>1</v>
       </c>
@@ -30685,7 +30716,7 @@
       <c r="L550" s="83"/>
       <c r="M550" s="11"/>
     </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A551" s="5">
         <v>1</v>
       </c>
@@ -30730,7 +30761,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A552" s="5">
         <v>1</v>
       </c>
@@ -30765,7 +30796,7 @@
       <c r="L552" s="83"/>
       <c r="M552" s="11"/>
     </row>
-    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A553" s="5">
         <v>1</v>
       </c>
@@ -30810,11 +30841,11 @@
         <v>353</v>
       </c>
     </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A554" s="5">
         <v>1</v>
       </c>
-      <c r="B554" s="139" t="s">
+      <c r="B554" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C554" s="16" t="e" vm="11">
@@ -30845,11 +30876,11 @@
       <c r="L554" s="83"/>
       <c r="M554" s="11"/>
     </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A555" s="5">
         <v>1</v>
       </c>
-      <c r="B555" s="140"/>
+      <c r="B555" s="141"/>
       <c r="C555" s="86" t="s">
         <v>37</v>
       </c>
@@ -30894,7 +30925,7 @@
       <c r="A556" s="13">
         <v>1</v>
       </c>
-      <c r="B556" s="151" t="s">
+      <c r="B556" s="144" t="s">
         <v>359</v>
       </c>
       <c r="C556" s="117" t="e" vm="48">
@@ -30930,7 +30961,7 @@
       <c r="A557" s="13">
         <v>1</v>
       </c>
-      <c r="B557" s="151"/>
+      <c r="B557" s="144"/>
       <c r="C557" s="117" t="s">
         <v>340</v>
       </c>
@@ -30975,7 +31006,7 @@
       </c>
     </row>
     <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B558" s="139" t="s">
+      <c r="B558" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C558" s="133" t="e" vm="25">
@@ -31008,7 +31039,7 @@
       <c r="M558" s="11"/>
     </row>
     <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B559" s="140"/>
+      <c r="B559" s="141"/>
       <c r="C559" s="63" t="s">
         <v>101</v>
       </c>
@@ -31050,11 +31081,11 @@
         <v>356</v>
       </c>
     </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A560" s="5">
         <v>1</v>
       </c>
-      <c r="B560" s="139" t="s">
+      <c r="B560" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C560" s="13" t="e" vm="11">
@@ -31085,11 +31116,11 @@
       <c r="L560" s="83"/>
       <c r="M560" s="11"/>
     </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A561" s="5">
         <v>1</v>
       </c>
-      <c r="B561" s="140"/>
+      <c r="B561" s="141"/>
       <c r="C561" s="13" t="s">
         <v>37</v>
       </c>
@@ -31137,7 +31168,7 @@
       <c r="A562" s="13">
         <v>1</v>
       </c>
-      <c r="B562" s="185" t="s">
+      <c r="B562" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C562" s="107" t="e" vm="48">
@@ -31173,7 +31204,7 @@
       <c r="A563" s="13">
         <v>1</v>
       </c>
-      <c r="B563" s="185"/>
+      <c r="B563" s="139"/>
       <c r="C563" s="107" t="s">
         <v>340</v>
       </c>
@@ -31221,7 +31252,7 @@
       <c r="A564" s="13">
         <v>1</v>
       </c>
-      <c r="B564" s="135" t="s">
+      <c r="B564" s="138" t="s">
         <v>361</v>
       </c>
       <c r="C564" s="117" t="e" vm="48">
@@ -31257,7 +31288,7 @@
       <c r="A565" s="13">
         <v>1</v>
       </c>
-      <c r="B565" s="135"/>
+      <c r="B565" s="138"/>
       <c r="C565" s="117" t="s">
         <v>340</v>
       </c>
@@ -31299,7 +31330,7 @@
       </c>
     </row>
     <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B566" s="139" t="s">
+      <c r="B566" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C566" s="63" t="e" vm="36">
@@ -31332,7 +31363,7 @@
       <c r="M566" s="11"/>
     </row>
     <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B567" s="140"/>
+      <c r="B567" s="141"/>
       <c r="C567" s="90" t="s">
         <v>363</v>
       </c>
@@ -31377,7 +31408,7 @@
       <c r="A568" s="13">
         <v>1</v>
       </c>
-      <c r="B568" s="185" t="s">
+      <c r="B568" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C568" s="107" t="e" vm="48">
@@ -31413,7 +31444,7 @@
       <c r="A569" s="13">
         <v>1</v>
       </c>
-      <c r="B569" s="185"/>
+      <c r="B569" s="139"/>
       <c r="C569" s="107" t="s">
         <v>340</v>
       </c>
@@ -31459,7 +31490,7 @@
       <c r="A570" s="5">
         <v>1</v>
       </c>
-      <c r="B570" s="147" t="s">
+      <c r="B570" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C570" s="13" t="e" vm="44">
@@ -31495,7 +31526,7 @@
       <c r="A571" s="5">
         <v>1</v>
       </c>
-      <c r="B571" s="148"/>
+      <c r="B571" s="143"/>
       <c r="C571" s="13" t="s">
         <v>308</v>
       </c>
@@ -31537,7 +31568,7 @@
       </c>
     </row>
     <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B572" s="139" t="s">
+      <c r="B572" s="140" t="s">
         <v>32</v>
       </c>
       <c r="C572" s="52" t="e" vm="36">
@@ -31570,7 +31601,7 @@
       <c r="M572" s="11"/>
     </row>
     <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B573" s="140"/>
+      <c r="B573" s="141"/>
       <c r="C573" s="52" t="s">
         <v>363</v>
       </c>
@@ -31611,11 +31642,11 @@
         <v>373</v>
       </c>
     </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A574" s="5">
         <v>1</v>
       </c>
-      <c r="B574" s="147" t="s">
+      <c r="B574" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C574" s="16" t="e" vm="11">
@@ -31646,11 +31677,11 @@
       <c r="L574" s="83"/>
       <c r="M574" s="11"/>
     </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A575" s="5">
         <v>1</v>
       </c>
-      <c r="B575" s="148"/>
+      <c r="B575" s="143"/>
       <c r="C575" s="86" t="s">
         <v>37</v>
       </c>
@@ -31691,11 +31722,11 @@
         <v>374</v>
       </c>
     </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A576" s="5">
         <v>1</v>
       </c>
-      <c r="B576" s="147" t="s">
+      <c r="B576" s="142" t="s">
         <v>381</v>
       </c>
       <c r="C576" s="13" t="e" vm="11">
@@ -31726,11 +31757,11 @@
       <c r="L576" s="11"/>
       <c r="M576" s="11"/>
     </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A577" s="5">
         <v>1</v>
       </c>
-      <c r="B577" s="148"/>
+      <c r="B577" s="143"/>
       <c r="C577" s="13" t="s">
         <v>37</v>
       </c>
@@ -31775,7 +31806,7 @@
       <c r="A578" s="13">
         <v>1</v>
       </c>
-      <c r="B578" s="185" t="s">
+      <c r="B578" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C578" s="107" t="e" vm="50">
@@ -31811,7 +31842,7 @@
       <c r="A579" s="13">
         <v>1</v>
       </c>
-      <c r="B579" s="185"/>
+      <c r="B579" s="139"/>
       <c r="C579" s="107" t="s">
         <v>406</v>
       </c>
@@ -31860,7 +31891,7 @@
       <c r="A580" s="13">
         <v>1</v>
       </c>
-      <c r="B580" s="185" t="s">
+      <c r="B580" s="139" t="s">
         <v>376</v>
       </c>
       <c r="C580" s="107" t="e" vm="51">
@@ -31896,7 +31927,7 @@
       <c r="A581" s="13">
         <v>1</v>
       </c>
-      <c r="B581" s="185"/>
+      <c r="B581" s="139"/>
       <c r="C581" s="107" t="s">
         <v>375</v>
       </c>
@@ -31938,7 +31969,7 @@
       </c>
     </row>
     <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B582" s="139" t="s">
+      <c r="B582" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C582" s="63" t="e" vm="36">
@@ -31971,7 +32002,7 @@
       <c r="M582" s="11"/>
     </row>
     <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B583" s="140"/>
+      <c r="B583" s="141"/>
       <c r="C583" s="90" t="s">
         <v>363</v>
       </c>
@@ -32016,7 +32047,7 @@
       <c r="A584" s="5">
         <v>1</v>
       </c>
-      <c r="B584" s="158" t="s">
+      <c r="B584" s="147" t="s">
         <v>380</v>
       </c>
       <c r="C584" s="101" t="e" vm="43">
@@ -32052,7 +32083,7 @@
       <c r="A585" s="5">
         <v>1</v>
       </c>
-      <c r="B585" s="159"/>
+      <c r="B585" s="148"/>
       <c r="C585" s="101" t="s">
         <v>267</v>
       </c>
@@ -32097,7 +32128,7 @@
       <c r="A586" s="5">
         <v>1</v>
       </c>
-      <c r="B586" s="205" t="s">
+      <c r="B586" s="145" t="s">
         <v>29</v>
       </c>
       <c r="C586" s="16" t="e" vm="49">
@@ -32133,7 +32164,7 @@
       <c r="A587" s="5">
         <v>1</v>
       </c>
-      <c r="B587" s="206"/>
+      <c r="B587" s="146"/>
       <c r="C587" s="86" t="s">
         <v>386</v>
       </c>
@@ -32174,11 +32205,11 @@
         <v>390</v>
       </c>
     </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A588" s="5">
         <v>1</v>
       </c>
-      <c r="B588" s="135" t="s">
+      <c r="B588" s="138" t="s">
         <v>102</v>
       </c>
       <c r="C588" s="16" t="e" vm="11">
@@ -32207,11 +32238,11 @@
       <c r="J588" s="10"/>
       <c r="K588" s="7"/>
     </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A589" s="5">
         <v>1</v>
       </c>
-      <c r="B589" s="135"/>
+      <c r="B589" s="138"/>
       <c r="C589" s="86" t="s">
         <v>37</v>
       </c>
@@ -32248,11 +32279,11 @@
         <v>46055</v>
       </c>
     </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A590" s="5">
         <v>1</v>
       </c>
-      <c r="B590" s="139" t="s">
+      <c r="B590" s="140" t="s">
         <v>384</v>
       </c>
       <c r="C590" s="13" t="e" vm="11">
@@ -32281,11 +32312,11 @@
       <c r="J590" s="10"/>
       <c r="K590" s="7"/>
     </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A591" s="5">
         <v>1</v>
       </c>
-      <c r="B591" s="140"/>
+      <c r="B591" s="141"/>
       <c r="C591" s="13" t="s">
         <v>37</v>
       </c>
@@ -32322,7 +32353,7 @@
         <v>46056</v>
       </c>
     </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A592" s="5">
         <v>1</v>
       </c>
@@ -32357,7 +32388,7 @@
       <c r="L592" s="83"/>
       <c r="M592" s="11"/>
     </row>
-    <row r="593" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A593" s="5">
         <v>1</v>
       </c>
@@ -32402,7 +32433,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="594" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A594" s="5">
         <v>1</v>
       </c>
@@ -32436,7 +32467,7 @@
       <c r="K594" s="7"/>
       <c r="L594" s="83"/>
     </row>
-    <row r="595" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A595" s="5">
         <v>1</v>
       </c>
@@ -32477,7 +32508,7 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="596" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A596" s="5">
         <v>1</v>
       </c>
@@ -32511,7 +32542,7 @@
       <c r="K596" s="7"/>
       <c r="L596" s="83"/>
     </row>
-    <row r="597" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A597" s="5">
         <v>1</v>
       </c>
@@ -32630,7 +32661,7 @@
       </c>
       <c r="M599" s="11"/>
     </row>
-    <row r="600" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A600" s="5">
         <v>1</v>
       </c>
@@ -32654,7 +32685,7 @@
         <v>2</v>
       </c>
       <c r="H600" s="13">
-        <f t="shared" ref="H600:H603" si="336">F600*G600</f>
+        <f t="shared" ref="H600:H605" si="336">F600*G600</f>
         <v>774.66</v>
       </c>
       <c r="I600" s="13" t="s">
@@ -32664,7 +32695,7 @@
       <c r="K600" s="7"/>
       <c r="L600" s="83"/>
     </row>
-    <row r="601" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A601" s="5">
         <v>1</v>
       </c>
@@ -32705,11 +32736,11 @@
         <v>46084</v>
       </c>
     </row>
-    <row r="602" spans="1:14" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:14" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A602" s="5">
         <v>1</v>
       </c>
-      <c r="B602" s="135" t="s">
+      <c r="B602" s="138" t="s">
         <v>102</v>
       </c>
       <c r="C602" s="16" t="e" vm="11">
@@ -32738,11 +32769,11 @@
       <c r="J602" s="10"/>
       <c r="K602" s="7"/>
     </row>
-    <row r="603" spans="1:14" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A603" s="5">
         <v>1</v>
       </c>
-      <c r="B603" s="135"/>
+      <c r="B603" s="138"/>
       <c r="C603" s="86" t="s">
         <v>37</v>
       </c>
@@ -32779,79 +32810,278 @@
         <v>46087</v>
       </c>
     </row>
+    <row r="604" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A604" s="5">
+        <v>1</v>
+      </c>
+      <c r="B604" s="136" t="s">
+        <v>385</v>
+      </c>
+      <c r="C604" s="13" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D604" s="13" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E604" s="13" cm="1">
+        <f t="array" aca="1" ref="E604" ca="1">_FV(D604,"Price")</f>
+        <v>396.80220000000003</v>
+      </c>
+      <c r="F604" s="13">
+        <v>388.14</v>
+      </c>
+      <c r="G604" s="14">
+        <v>1</v>
+      </c>
+      <c r="H604" s="13">
+        <f t="shared" si="336"/>
+        <v>388.14</v>
+      </c>
+      <c r="I604" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J604" s="10"/>
+      <c r="K604" s="7"/>
+      <c r="L604" s="83"/>
+    </row>
+    <row r="605" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A605" s="5">
+        <v>1</v>
+      </c>
+      <c r="B605" s="137"/>
+      <c r="C605" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D605" s="13" t="str">
+        <f t="shared" ref="D605" si="339">C605</f>
+        <v>TSLA</v>
+      </c>
+      <c r="E605" s="13">
+        <f ca="1">E604</f>
+        <v>396.80220000000003</v>
+      </c>
+      <c r="F605" s="13">
+        <f ca="1">E605</f>
+        <v>396.80220000000003</v>
+      </c>
+      <c r="G605" s="14">
+        <f>G604</f>
+        <v>1</v>
+      </c>
+      <c r="H605" s="13">
+        <f t="shared" ca="1" si="336"/>
+        <v>396.80220000000003</v>
+      </c>
+      <c r="I605" s="13"/>
+      <c r="J605" s="10">
+        <f ca="1">H605-H604</f>
+        <v>8.6622000000000412</v>
+      </c>
+      <c r="K605" s="7">
+        <f ca="1">(H605/H604)-100%</f>
+        <v>2.2317205132168949E-2</v>
+      </c>
+      <c r="L605" s="83">
+        <v>46090</v>
+      </c>
+    </row>
     <row r="611" spans="3:3" x14ac:dyDescent="0.35">
       <c r="C611" s="83"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q603" xr:uid="{7ECB3444-92D9-4200-8B78-7CB7FAE28719}">
+    <filterColumn colId="0">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
     <filterColumn colId="2">
       <filters>
-        <filter val="Manulife"/>
-        <filter val="MANULIFE FINANCIAL CORPORATION (XTSE:MFC)"/>
+        <filter val="TESLA, INC. (XNAS:TSLA)"/>
+        <filter val="Tradr 2X Short TSLA Dl (XNAS:TSLQ)"/>
+        <filter val="TSLA"/>
+        <filter val="TSLA INVERSE ETF"/>
+        <filter val="TSLA Q -2x SHORT"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <mergeCells count="259">
-    <mergeCell ref="B596:B597"/>
-    <mergeCell ref="B592:B593"/>
-    <mergeCell ref="B588:B589"/>
-    <mergeCell ref="B578:B579"/>
-    <mergeCell ref="B580:B581"/>
-    <mergeCell ref="B572:B573"/>
-    <mergeCell ref="B570:B571"/>
-    <mergeCell ref="B566:B567"/>
-    <mergeCell ref="B554:B555"/>
-    <mergeCell ref="B556:B557"/>
-    <mergeCell ref="B590:B591"/>
-    <mergeCell ref="B594:B595"/>
-    <mergeCell ref="B550:B551"/>
-    <mergeCell ref="B552:B553"/>
-    <mergeCell ref="B574:B575"/>
-    <mergeCell ref="B576:B577"/>
-    <mergeCell ref="B586:B587"/>
-    <mergeCell ref="B582:B583"/>
-    <mergeCell ref="B584:B585"/>
-    <mergeCell ref="B548:B549"/>
-    <mergeCell ref="B542:B543"/>
-    <mergeCell ref="B544:B545"/>
-    <mergeCell ref="B546:B547"/>
-    <mergeCell ref="B560:B561"/>
-    <mergeCell ref="B562:B563"/>
-    <mergeCell ref="B564:B565"/>
-    <mergeCell ref="B558:B559"/>
-    <mergeCell ref="B568:B569"/>
-    <mergeCell ref="B538:B539"/>
-    <mergeCell ref="B530:B531"/>
-    <mergeCell ref="B528:B529"/>
-    <mergeCell ref="B520:B521"/>
-    <mergeCell ref="B516:B517"/>
-    <mergeCell ref="B518:B519"/>
-    <mergeCell ref="B540:B541"/>
-    <mergeCell ref="B536:B537"/>
-    <mergeCell ref="B534:B535"/>
-    <mergeCell ref="B532:B533"/>
-    <mergeCell ref="B522:B523"/>
-    <mergeCell ref="B524:B525"/>
-    <mergeCell ref="B526:B527"/>
-    <mergeCell ref="B480:B481"/>
-    <mergeCell ref="B482:B483"/>
-    <mergeCell ref="B514:B515"/>
-    <mergeCell ref="B512:B513"/>
-    <mergeCell ref="B510:B511"/>
-    <mergeCell ref="B508:B509"/>
-    <mergeCell ref="B478:B479"/>
-    <mergeCell ref="B502:B503"/>
-    <mergeCell ref="B504:B505"/>
-    <mergeCell ref="B492:B493"/>
-    <mergeCell ref="B494:B495"/>
-    <mergeCell ref="B496:B497"/>
-    <mergeCell ref="B506:B507"/>
-    <mergeCell ref="B498:B499"/>
-    <mergeCell ref="B500:B501"/>
-    <mergeCell ref="B484:B485"/>
-    <mergeCell ref="B486:B487"/>
-    <mergeCell ref="B490:B491"/>
-    <mergeCell ref="B488:B489"/>
+  <mergeCells count="260">
+    <mergeCell ref="B604:B605"/>
+    <mergeCell ref="B602:B603"/>
+    <mergeCell ref="B600:B601"/>
+    <mergeCell ref="B598:B599"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B476:B477"/>
+    <mergeCell ref="B458:B459"/>
+    <mergeCell ref="B460:B461"/>
+    <mergeCell ref="B462:B463"/>
+    <mergeCell ref="B454:B455"/>
+    <mergeCell ref="B456:B457"/>
+    <mergeCell ref="B422:B423"/>
+    <mergeCell ref="B472:B473"/>
+    <mergeCell ref="B474:B475"/>
+    <mergeCell ref="B464:B465"/>
+    <mergeCell ref="B466:B467"/>
+    <mergeCell ref="B450:B451"/>
+    <mergeCell ref="B452:B453"/>
+    <mergeCell ref="B444:B445"/>
+    <mergeCell ref="B438:B439"/>
+    <mergeCell ref="B440:B441"/>
+    <mergeCell ref="B468:B469"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="B442:B443"/>
+    <mergeCell ref="B434:B435"/>
+    <mergeCell ref="B432:B433"/>
+    <mergeCell ref="B426:B427"/>
+    <mergeCell ref="B428:B429"/>
+    <mergeCell ref="B430:B431"/>
+    <mergeCell ref="B436:B437"/>
+    <mergeCell ref="B424:B425"/>
+    <mergeCell ref="B352:B353"/>
+    <mergeCell ref="B354:B355"/>
+    <mergeCell ref="B394:B395"/>
+    <mergeCell ref="B396:B397"/>
+    <mergeCell ref="B384:B385"/>
+    <mergeCell ref="B382:B383"/>
+    <mergeCell ref="B374:B375"/>
+    <mergeCell ref="B404:B405"/>
+    <mergeCell ref="B376:B377"/>
+    <mergeCell ref="B380:B381"/>
+    <mergeCell ref="B378:B379"/>
+    <mergeCell ref="B388:B389"/>
+    <mergeCell ref="B390:B391"/>
+    <mergeCell ref="B386:B387"/>
+    <mergeCell ref="B402:B403"/>
+    <mergeCell ref="B392:B393"/>
+    <mergeCell ref="B410:B411"/>
+    <mergeCell ref="B420:B421"/>
+    <mergeCell ref="B350:B351"/>
+    <mergeCell ref="B346:B347"/>
+    <mergeCell ref="B348:B349"/>
+    <mergeCell ref="B344:B345"/>
+    <mergeCell ref="B340:B341"/>
+    <mergeCell ref="B356:B357"/>
+    <mergeCell ref="B358:B359"/>
+    <mergeCell ref="B416:B417"/>
+    <mergeCell ref="B418:B419"/>
+    <mergeCell ref="B414:B415"/>
+    <mergeCell ref="B412:B413"/>
+    <mergeCell ref="B408:B409"/>
+    <mergeCell ref="B372:B373"/>
+    <mergeCell ref="B364:B365"/>
+    <mergeCell ref="B362:B363"/>
+    <mergeCell ref="B360:B361"/>
+    <mergeCell ref="B366:B367"/>
+    <mergeCell ref="B368:B369"/>
+    <mergeCell ref="B370:B371"/>
+    <mergeCell ref="B398:B399"/>
+    <mergeCell ref="B406:B407"/>
+    <mergeCell ref="B400:B401"/>
+    <mergeCell ref="B334:B335"/>
+    <mergeCell ref="B336:B337"/>
+    <mergeCell ref="B324:B325"/>
+    <mergeCell ref="B326:B327"/>
+    <mergeCell ref="B322:B323"/>
+    <mergeCell ref="B342:B343"/>
+    <mergeCell ref="B338:B339"/>
+    <mergeCell ref="B330:B331"/>
+    <mergeCell ref="B332:B333"/>
+    <mergeCell ref="B328:B329"/>
+    <mergeCell ref="B254:B255"/>
+    <mergeCell ref="B278:B279"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="B272:B273"/>
+    <mergeCell ref="B256:B257"/>
+    <mergeCell ref="B258:B259"/>
+    <mergeCell ref="B262:B263"/>
+    <mergeCell ref="B260:B261"/>
+    <mergeCell ref="B268:B269"/>
+    <mergeCell ref="B264:B265"/>
+    <mergeCell ref="B266:B267"/>
+    <mergeCell ref="B298:B299"/>
+    <mergeCell ref="B294:B295"/>
+    <mergeCell ref="B296:B297"/>
+    <mergeCell ref="B306:B307"/>
+    <mergeCell ref="B310:B311"/>
+    <mergeCell ref="B308:B309"/>
+    <mergeCell ref="B320:B321"/>
+    <mergeCell ref="B318:B319"/>
+    <mergeCell ref="B316:B317"/>
+    <mergeCell ref="B302:B303"/>
+    <mergeCell ref="B314:B315"/>
+    <mergeCell ref="B312:B313"/>
+    <mergeCell ref="B304:B305"/>
+    <mergeCell ref="B250:B251"/>
+    <mergeCell ref="B252:B253"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="B248:B249"/>
+    <mergeCell ref="B206:B207"/>
+    <mergeCell ref="B204:B205"/>
+    <mergeCell ref="B190:B191"/>
+    <mergeCell ref="B198:B199"/>
+    <mergeCell ref="B300:B301"/>
+    <mergeCell ref="B292:B293"/>
+    <mergeCell ref="B280:B281"/>
+    <mergeCell ref="B282:B283"/>
+    <mergeCell ref="B284:B285"/>
+    <mergeCell ref="B276:B277"/>
+    <mergeCell ref="B290:B291"/>
+    <mergeCell ref="B286:B287"/>
+    <mergeCell ref="B288:B289"/>
+    <mergeCell ref="B220:B221"/>
+    <mergeCell ref="B222:B223"/>
+    <mergeCell ref="B242:B243"/>
+    <mergeCell ref="B240:B241"/>
+    <mergeCell ref="B270:B271"/>
+    <mergeCell ref="B246:B247"/>
+    <mergeCell ref="B244:B245"/>
+    <mergeCell ref="B238:B239"/>
+    <mergeCell ref="B228:B229"/>
+    <mergeCell ref="B236:B237"/>
+    <mergeCell ref="B200:B201"/>
+    <mergeCell ref="B216:B217"/>
+    <mergeCell ref="B218:B219"/>
+    <mergeCell ref="B182:B183"/>
+    <mergeCell ref="B192:B193"/>
+    <mergeCell ref="B186:B187"/>
+    <mergeCell ref="B230:B231"/>
+    <mergeCell ref="B232:B233"/>
+    <mergeCell ref="B184:B185"/>
+    <mergeCell ref="B234:B235"/>
+    <mergeCell ref="B180:B181"/>
+    <mergeCell ref="B214:B215"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B208:B209"/>
+    <mergeCell ref="B212:B213"/>
+    <mergeCell ref="B226:B227"/>
+    <mergeCell ref="B224:B225"/>
+    <mergeCell ref="B146:B147"/>
+    <mergeCell ref="B176:B177"/>
+    <mergeCell ref="B174:B175"/>
+    <mergeCell ref="B178:B179"/>
+    <mergeCell ref="B166:B167"/>
+    <mergeCell ref="B164:B165"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="B144:B145"/>
+    <mergeCell ref="B162:B163"/>
+    <mergeCell ref="B158:B159"/>
+    <mergeCell ref="B102:B103"/>
+    <mergeCell ref="B104:B105"/>
+    <mergeCell ref="B136:B137"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="B116:B117"/>
+    <mergeCell ref="B160:B161"/>
+    <mergeCell ref="B130:B131"/>
+    <mergeCell ref="B138:B139"/>
+    <mergeCell ref="B140:B141"/>
+    <mergeCell ref="B120:B121"/>
+    <mergeCell ref="B118:B119"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="B44:B45"/>
@@ -32876,830 +33106,730 @@
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="B168:B169"/>
     <mergeCell ref="B54:B55"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="B144:B145"/>
-    <mergeCell ref="B162:B163"/>
-    <mergeCell ref="B158:B159"/>
-    <mergeCell ref="B102:B103"/>
-    <mergeCell ref="B104:B105"/>
-    <mergeCell ref="B136:B137"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="B116:B117"/>
-    <mergeCell ref="B160:B161"/>
-    <mergeCell ref="B130:B131"/>
-    <mergeCell ref="B138:B139"/>
-    <mergeCell ref="B140:B141"/>
-    <mergeCell ref="B120:B121"/>
-    <mergeCell ref="B118:B119"/>
-    <mergeCell ref="B180:B181"/>
-    <mergeCell ref="B214:B215"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B208:B209"/>
-    <mergeCell ref="B212:B213"/>
-    <mergeCell ref="B226:B227"/>
-    <mergeCell ref="B224:B225"/>
-    <mergeCell ref="B146:B147"/>
-    <mergeCell ref="B176:B177"/>
-    <mergeCell ref="B174:B175"/>
-    <mergeCell ref="B178:B179"/>
-    <mergeCell ref="B166:B167"/>
-    <mergeCell ref="B164:B165"/>
-    <mergeCell ref="B238:B239"/>
-    <mergeCell ref="B228:B229"/>
-    <mergeCell ref="B236:B237"/>
-    <mergeCell ref="B200:B201"/>
-    <mergeCell ref="B216:B217"/>
-    <mergeCell ref="B218:B219"/>
-    <mergeCell ref="B182:B183"/>
-    <mergeCell ref="B192:B193"/>
-    <mergeCell ref="B186:B187"/>
-    <mergeCell ref="B230:B231"/>
-    <mergeCell ref="B232:B233"/>
-    <mergeCell ref="B184:B185"/>
-    <mergeCell ref="B234:B235"/>
-    <mergeCell ref="B250:B251"/>
-    <mergeCell ref="B252:B253"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="B248:B249"/>
-    <mergeCell ref="B206:B207"/>
-    <mergeCell ref="B204:B205"/>
-    <mergeCell ref="B190:B191"/>
-    <mergeCell ref="B198:B199"/>
-    <mergeCell ref="B300:B301"/>
-    <mergeCell ref="B292:B293"/>
-    <mergeCell ref="B280:B281"/>
-    <mergeCell ref="B282:B283"/>
-    <mergeCell ref="B284:B285"/>
-    <mergeCell ref="B276:B277"/>
-    <mergeCell ref="B290:B291"/>
-    <mergeCell ref="B286:B287"/>
-    <mergeCell ref="B288:B289"/>
-    <mergeCell ref="B220:B221"/>
-    <mergeCell ref="B222:B223"/>
-    <mergeCell ref="B242:B243"/>
-    <mergeCell ref="B240:B241"/>
-    <mergeCell ref="B270:B271"/>
-    <mergeCell ref="B246:B247"/>
-    <mergeCell ref="B244:B245"/>
-    <mergeCell ref="B298:B299"/>
-    <mergeCell ref="B294:B295"/>
-    <mergeCell ref="B296:B297"/>
-    <mergeCell ref="B306:B307"/>
-    <mergeCell ref="B310:B311"/>
-    <mergeCell ref="B308:B309"/>
-    <mergeCell ref="B320:B321"/>
-    <mergeCell ref="B318:B319"/>
-    <mergeCell ref="B316:B317"/>
-    <mergeCell ref="B302:B303"/>
-    <mergeCell ref="B314:B315"/>
-    <mergeCell ref="B312:B313"/>
-    <mergeCell ref="B304:B305"/>
-    <mergeCell ref="B254:B255"/>
-    <mergeCell ref="B278:B279"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="B272:B273"/>
-    <mergeCell ref="B256:B257"/>
-    <mergeCell ref="B258:B259"/>
-    <mergeCell ref="B262:B263"/>
-    <mergeCell ref="B260:B261"/>
-    <mergeCell ref="B268:B269"/>
-    <mergeCell ref="B264:B265"/>
-    <mergeCell ref="B266:B267"/>
-    <mergeCell ref="B334:B335"/>
-    <mergeCell ref="B336:B337"/>
-    <mergeCell ref="B324:B325"/>
-    <mergeCell ref="B326:B327"/>
-    <mergeCell ref="B322:B323"/>
-    <mergeCell ref="B342:B343"/>
-    <mergeCell ref="B338:B339"/>
-    <mergeCell ref="B330:B331"/>
-    <mergeCell ref="B332:B333"/>
-    <mergeCell ref="B328:B329"/>
-    <mergeCell ref="B410:B411"/>
-    <mergeCell ref="B420:B421"/>
-    <mergeCell ref="B350:B351"/>
-    <mergeCell ref="B346:B347"/>
-    <mergeCell ref="B348:B349"/>
-    <mergeCell ref="B344:B345"/>
-    <mergeCell ref="B340:B341"/>
-    <mergeCell ref="B356:B357"/>
-    <mergeCell ref="B358:B359"/>
-    <mergeCell ref="B416:B417"/>
-    <mergeCell ref="B418:B419"/>
-    <mergeCell ref="B414:B415"/>
-    <mergeCell ref="B412:B413"/>
-    <mergeCell ref="B408:B409"/>
-    <mergeCell ref="B372:B373"/>
-    <mergeCell ref="B364:B365"/>
-    <mergeCell ref="B362:B363"/>
-    <mergeCell ref="B360:B361"/>
-    <mergeCell ref="B366:B367"/>
-    <mergeCell ref="B368:B369"/>
-    <mergeCell ref="B370:B371"/>
-    <mergeCell ref="B398:B399"/>
-    <mergeCell ref="B406:B407"/>
-    <mergeCell ref="B400:B401"/>
-    <mergeCell ref="B442:B443"/>
-    <mergeCell ref="B434:B435"/>
-    <mergeCell ref="B432:B433"/>
-    <mergeCell ref="B426:B427"/>
-    <mergeCell ref="B428:B429"/>
-    <mergeCell ref="B430:B431"/>
-    <mergeCell ref="B436:B437"/>
-    <mergeCell ref="B424:B425"/>
-    <mergeCell ref="B352:B353"/>
-    <mergeCell ref="B354:B355"/>
-    <mergeCell ref="B394:B395"/>
-    <mergeCell ref="B396:B397"/>
-    <mergeCell ref="B384:B385"/>
-    <mergeCell ref="B382:B383"/>
-    <mergeCell ref="B374:B375"/>
-    <mergeCell ref="B404:B405"/>
-    <mergeCell ref="B376:B377"/>
-    <mergeCell ref="B380:B381"/>
-    <mergeCell ref="B378:B379"/>
-    <mergeCell ref="B388:B389"/>
-    <mergeCell ref="B390:B391"/>
-    <mergeCell ref="B386:B387"/>
-    <mergeCell ref="B402:B403"/>
-    <mergeCell ref="B392:B393"/>
-    <mergeCell ref="B602:B603"/>
-    <mergeCell ref="B600:B601"/>
-    <mergeCell ref="B598:B599"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B476:B477"/>
-    <mergeCell ref="B458:B459"/>
-    <mergeCell ref="B460:B461"/>
-    <mergeCell ref="B462:B463"/>
-    <mergeCell ref="B454:B455"/>
-    <mergeCell ref="B456:B457"/>
-    <mergeCell ref="B422:B423"/>
-    <mergeCell ref="B472:B473"/>
-    <mergeCell ref="B474:B475"/>
-    <mergeCell ref="B464:B465"/>
-    <mergeCell ref="B466:B467"/>
-    <mergeCell ref="B450:B451"/>
-    <mergeCell ref="B452:B453"/>
-    <mergeCell ref="B444:B445"/>
-    <mergeCell ref="B438:B439"/>
-    <mergeCell ref="B440:B441"/>
-    <mergeCell ref="B468:B469"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="B446:B447"/>
+    <mergeCell ref="B480:B481"/>
+    <mergeCell ref="B482:B483"/>
+    <mergeCell ref="B514:B515"/>
+    <mergeCell ref="B512:B513"/>
+    <mergeCell ref="B510:B511"/>
+    <mergeCell ref="B508:B509"/>
+    <mergeCell ref="B478:B479"/>
+    <mergeCell ref="B502:B503"/>
+    <mergeCell ref="B504:B505"/>
+    <mergeCell ref="B492:B493"/>
+    <mergeCell ref="B494:B495"/>
+    <mergeCell ref="B496:B497"/>
+    <mergeCell ref="B506:B507"/>
+    <mergeCell ref="B498:B499"/>
+    <mergeCell ref="B500:B501"/>
+    <mergeCell ref="B484:B485"/>
+    <mergeCell ref="B486:B487"/>
+    <mergeCell ref="B490:B491"/>
+    <mergeCell ref="B488:B489"/>
+    <mergeCell ref="B538:B539"/>
+    <mergeCell ref="B530:B531"/>
+    <mergeCell ref="B528:B529"/>
+    <mergeCell ref="B520:B521"/>
+    <mergeCell ref="B516:B517"/>
+    <mergeCell ref="B518:B519"/>
+    <mergeCell ref="B540:B541"/>
+    <mergeCell ref="B536:B537"/>
+    <mergeCell ref="B534:B535"/>
+    <mergeCell ref="B532:B533"/>
+    <mergeCell ref="B522:B523"/>
+    <mergeCell ref="B524:B525"/>
+    <mergeCell ref="B526:B527"/>
+    <mergeCell ref="B550:B551"/>
+    <mergeCell ref="B552:B553"/>
+    <mergeCell ref="B574:B575"/>
+    <mergeCell ref="B576:B577"/>
+    <mergeCell ref="B586:B587"/>
+    <mergeCell ref="B582:B583"/>
+    <mergeCell ref="B584:B585"/>
+    <mergeCell ref="B548:B549"/>
+    <mergeCell ref="B542:B543"/>
+    <mergeCell ref="B544:B545"/>
+    <mergeCell ref="B546:B547"/>
+    <mergeCell ref="B560:B561"/>
+    <mergeCell ref="B562:B563"/>
+    <mergeCell ref="B564:B565"/>
+    <mergeCell ref="B558:B559"/>
+    <mergeCell ref="B568:B569"/>
+    <mergeCell ref="B596:B597"/>
+    <mergeCell ref="B592:B593"/>
+    <mergeCell ref="B588:B589"/>
+    <mergeCell ref="B578:B579"/>
+    <mergeCell ref="B580:B581"/>
+    <mergeCell ref="B572:B573"/>
+    <mergeCell ref="B570:B571"/>
+    <mergeCell ref="B566:B567"/>
+    <mergeCell ref="B554:B555"/>
+    <mergeCell ref="B556:B557"/>
+    <mergeCell ref="B590:B591"/>
+    <mergeCell ref="B594:B595"/>
   </mergeCells>
   <conditionalFormatting sqref="J2:J5 J174:J243">
-    <cfRule type="cellIs" dxfId="132" priority="584" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="135" priority="587" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J8:J13">
-    <cfRule type="cellIs" dxfId="131" priority="764" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="134" priority="767" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J14:J51">
-    <cfRule type="cellIs" dxfId="130" priority="659" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="133" priority="662" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J52:J57">
-    <cfRule type="cellIs" dxfId="129" priority="574" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="132" priority="577" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J60:J61">
-    <cfRule type="cellIs" dxfId="128" priority="686" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="131" priority="689" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J168:J169">
-    <cfRule type="cellIs" dxfId="127" priority="548" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="130" priority="551" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J246:J247">
-    <cfRule type="cellIs" dxfId="126" priority="587" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="129" priority="590" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J254:J255">
-    <cfRule type="cellIs" dxfId="125" priority="571" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="128" priority="574" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J255">
-    <cfRule type="cellIs" dxfId="124" priority="502" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="127" priority="505" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="123" priority="504" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="126" priority="507" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J255:J257">
-    <cfRule type="cellIs" dxfId="122" priority="525" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="125" priority="528" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J257">
-    <cfRule type="cellIs" dxfId="121" priority="506" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="124" priority="509" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="120" priority="508" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="123" priority="511" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J258:J259">
-    <cfRule type="cellIs" dxfId="119" priority="567" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="122" priority="570" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J260:J263">
-    <cfRule type="cellIs" dxfId="118" priority="557" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="121" priority="560" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J263:J265">
-    <cfRule type="cellIs" dxfId="117" priority="500" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="120" priority="503" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J266:J279">
-    <cfRule type="cellIs" dxfId="116" priority="537" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="119" priority="540" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J269">
-    <cfRule type="cellIs" dxfId="115" priority="523" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="118" priority="526" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J271">
-    <cfRule type="cellIs" dxfId="114" priority="521" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="117" priority="524" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J273">
-    <cfRule type="cellIs" dxfId="113" priority="519" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="116" priority="522" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J275">
-    <cfRule type="cellIs" dxfId="112" priority="517" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="115" priority="520" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J277">
-    <cfRule type="cellIs" dxfId="111" priority="515" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="114" priority="518" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J279">
-    <cfRule type="cellIs" dxfId="110" priority="511" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="113" priority="514" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J280:J285">
-    <cfRule type="cellIs" dxfId="109" priority="496" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="112" priority="499" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J283">
-    <cfRule type="cellIs" dxfId="108" priority="494" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="111" priority="497" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J285:J333">
-    <cfRule type="cellIs" dxfId="107" priority="487" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="110" priority="490" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J287">
-    <cfRule type="cellIs" dxfId="106" priority="484" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="109" priority="487" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J289">
-    <cfRule type="cellIs" dxfId="105" priority="479" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="108" priority="482" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J291">
-    <cfRule type="cellIs" dxfId="104" priority="475" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="107" priority="478" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J293">
-    <cfRule type="cellIs" dxfId="103" priority="471" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="106" priority="474" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J311">
-    <cfRule type="cellIs" dxfId="102" priority="452" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="105" priority="455" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J315">
-    <cfRule type="cellIs" dxfId="101" priority="446" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="104" priority="449" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J317">
-    <cfRule type="cellIs" dxfId="100" priority="442" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="103" priority="445" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J319">
-    <cfRule type="cellIs" dxfId="99" priority="438" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="102" priority="441" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J321">
-    <cfRule type="cellIs" dxfId="98" priority="434" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="101" priority="437" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J330:J331">
-    <cfRule type="cellIs" dxfId="97" priority="409" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="100" priority="412" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J334:J341">
-    <cfRule type="cellIs" dxfId="96" priority="414" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="99" priority="417" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J342:J365">
-    <cfRule type="cellIs" dxfId="95" priority="406" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="98" priority="409" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J366:J367">
-    <cfRule type="cellIs" dxfId="94" priority="379" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="97" priority="382" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J368:J369">
-    <cfRule type="cellIs" dxfId="93" priority="373" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="96" priority="376" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J370:J387">
-    <cfRule type="cellIs" dxfId="92" priority="364" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="95" priority="367" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J388:J391">
-    <cfRule type="cellIs" dxfId="91" priority="347" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="94" priority="350" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J392:J395">
-    <cfRule type="cellIs" dxfId="90" priority="341" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="93" priority="344" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J396:J397">
-    <cfRule type="cellIs" dxfId="89" priority="337" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="92" priority="340" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J398:J399">
-    <cfRule type="cellIs" dxfId="88" priority="333" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="91" priority="336" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J400:J407">
-    <cfRule type="cellIs" dxfId="87" priority="323" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="90" priority="326" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J414:J415">
-    <cfRule type="cellIs" dxfId="86" priority="313" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="89" priority="316" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J420:J421">
-    <cfRule type="cellIs" dxfId="85" priority="307" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="88" priority="310" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J422:J427">
-    <cfRule type="cellIs" dxfId="84" priority="303" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="87" priority="306" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J430:J437">
-    <cfRule type="cellIs" dxfId="83" priority="288" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="86" priority="291" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J438:J465">
-    <cfRule type="cellIs" dxfId="82" priority="276" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="85" priority="279" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J466:J503">
-    <cfRule type="cellIs" dxfId="81" priority="214" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="84" priority="217" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J506:J511">
-    <cfRule type="cellIs" dxfId="80" priority="139" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="83" priority="142" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J512:J515">
-    <cfRule type="cellIs" dxfId="79" priority="194" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="82" priority="197" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J516:J525">
-    <cfRule type="cellIs" dxfId="78" priority="174" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="81" priority="177" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J528:J529">
-    <cfRule type="cellIs" dxfId="77" priority="141" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="80" priority="144" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J530:J531">
-    <cfRule type="cellIs" dxfId="76" priority="166" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="79" priority="169" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J536:J537">
-    <cfRule type="cellIs" dxfId="75" priority="159" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="78" priority="162" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J538:J541">
-    <cfRule type="cellIs" dxfId="74" priority="153" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="77" priority="156" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J542:J545">
-    <cfRule type="cellIs" dxfId="73" priority="147" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="76" priority="150" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J546:J547">
-    <cfRule type="cellIs" dxfId="72" priority="143" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="75" priority="146" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J550:J555">
-    <cfRule type="cellIs" dxfId="71" priority="130" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="74" priority="133" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J558:J559">
-    <cfRule type="cellIs" dxfId="70" priority="125" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="73" priority="128" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J560:J561">
-    <cfRule type="cellIs" dxfId="69" priority="121" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="72" priority="124" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J566:J567">
-    <cfRule type="cellIs" dxfId="68" priority="115" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="71" priority="118" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J570:J577">
-    <cfRule type="cellIs" dxfId="67" priority="104" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="70" priority="107" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J582:J587">
-    <cfRule type="cellIs" dxfId="66" priority="89" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="69" priority="92" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J588:J589">
-    <cfRule type="cellIs" dxfId="65" priority="24" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="68" priority="27" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J590:J597">
-    <cfRule type="cellIs" dxfId="64" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="67" priority="21" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J598:J603">
-    <cfRule type="cellIs" dxfId="63" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="66" priority="6" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J46:K163 J296:K311 J321:K335 J450:K467">
-    <cfRule type="cellIs" dxfId="62" priority="790" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="65" priority="793" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J164:K165">
-    <cfRule type="cellIs" dxfId="61" priority="573" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="64" priority="576" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J166:K253 J12:M45">
-    <cfRule type="cellIs" dxfId="60" priority="657" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="63" priority="660" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J254:K255">
-    <cfRule type="cellIs" dxfId="59" priority="568" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="62" priority="571" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J255:K255">
-    <cfRule type="cellIs" dxfId="58" priority="505" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="61" priority="508" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="57" priority="503" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="60" priority="506" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J256:K257">
-    <cfRule type="cellIs" dxfId="56" priority="524" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="59" priority="527" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J257:K257">
-    <cfRule type="cellIs" dxfId="55" priority="507" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="58" priority="510" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J258:K261">
-    <cfRule type="cellIs" dxfId="54" priority="560" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="57" priority="563" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J262:K278">
-    <cfRule type="cellIs" dxfId="53" priority="527" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="56" priority="530" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J269:K269">
-    <cfRule type="cellIs" dxfId="52" priority="522" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="55" priority="525" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J271:K271">
-    <cfRule type="cellIs" dxfId="51" priority="520" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="54" priority="523" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J273:K273">
-    <cfRule type="cellIs" dxfId="50" priority="518" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="53" priority="521" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J275:K275">
-    <cfRule type="cellIs" dxfId="49" priority="516" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="52" priority="519" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J277:K277">
-    <cfRule type="cellIs" dxfId="48" priority="514" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="51" priority="517" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J279:K279">
-    <cfRule type="cellIs" dxfId="47" priority="513" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="50" priority="516" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J279:K281">
-    <cfRule type="cellIs" dxfId="46" priority="499" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="49" priority="502" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J282:K283">
-    <cfRule type="cellIs" dxfId="45" priority="495" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="48" priority="498" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J283:K285">
-    <cfRule type="cellIs" dxfId="44" priority="491" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="47" priority="494" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J285:K287">
-    <cfRule type="cellIs" dxfId="43" priority="485" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="46" priority="488" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J287:K289">
-    <cfRule type="cellIs" dxfId="42" priority="480" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="45" priority="483" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J289:K291">
-    <cfRule type="cellIs" dxfId="41" priority="476" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="44" priority="479" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J291:K293">
-    <cfRule type="cellIs" dxfId="40" priority="472" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="43" priority="475" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J293:K295">
-    <cfRule type="cellIs" dxfId="39" priority="468" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="42" priority="471" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J311:K315">
-    <cfRule type="cellIs" dxfId="38" priority="447" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="41" priority="450" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J315:K317">
-    <cfRule type="cellIs" dxfId="37" priority="443" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="40" priority="446" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J317:K319">
-    <cfRule type="cellIs" dxfId="36" priority="439" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="39" priority="442" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J319:K321">
-    <cfRule type="cellIs" dxfId="35" priority="435" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="38" priority="438" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J330:K331">
-    <cfRule type="cellIs" dxfId="34" priority="408" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="37" priority="411" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J336:K343">
-    <cfRule type="cellIs" dxfId="33" priority="407" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="36" priority="410" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J344:K366">
-    <cfRule type="cellIs" dxfId="32" priority="382" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="35" priority="385" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J367:K368">
-    <cfRule type="cellIs" dxfId="31" priority="376" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="34" priority="379" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J369:K371">
-    <cfRule type="cellIs" dxfId="30" priority="370" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="33" priority="373" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J372:K390">
-    <cfRule type="cellIs" dxfId="29" priority="348" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="32" priority="351" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J391:K393">
-    <cfRule type="cellIs" dxfId="28" priority="344" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="31" priority="347" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J394:K396">
-    <cfRule type="cellIs" dxfId="27" priority="338" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="341" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J397:K398">
-    <cfRule type="cellIs" dxfId="26" priority="334" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="29" priority="337" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J399:K400">
-    <cfRule type="cellIs" dxfId="25" priority="330" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="28" priority="333" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J401:K415">
-    <cfRule type="cellIs" dxfId="24" priority="314" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="317" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J416:K423">
-    <cfRule type="cellIs" dxfId="23" priority="304" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="26" priority="307" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J424:K439">
-    <cfRule type="cellIs" dxfId="22" priority="285" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="25" priority="288" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J440:K449">
-    <cfRule type="cellIs" dxfId="21" priority="271" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="274" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J468:K511">
-    <cfRule type="cellIs" dxfId="20" priority="138" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="23" priority="141" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J512:K517">
-    <cfRule type="cellIs" dxfId="19" priority="185" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="22" priority="188" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J518:K529">
-    <cfRule type="cellIs" dxfId="18" priority="140" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="143" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J530:K539">
-    <cfRule type="cellIs" dxfId="17" priority="156" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="20" priority="159" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J540:K543">
-    <cfRule type="cellIs" dxfId="16" priority="150" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="19" priority="153" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J544:K547">
-    <cfRule type="cellIs" dxfId="15" priority="144" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="147" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J548:K561">
-    <cfRule type="cellIs" dxfId="14" priority="122" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="17" priority="125" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J587:K591">
-    <cfRule type="cellIs" dxfId="13" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="16" priority="24" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J587:K603">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J592:K599">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="14" priority="13" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J600:K603">
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:M5">
-    <cfRule type="cellIs" dxfId="9" priority="582" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="585" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="583" operator="lessThan">
+    <cfRule type="cellIs" dxfId="11" priority="586" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12:M45 M46:M530 J46:K575 M532:M558 M560:M575 J576:M576 J577:K577 M577 J578:M580 J581:K581 M581 J582:M584 M584:M585 J585:K585 J586:M586 M587">
-    <cfRule type="cellIs" dxfId="7" priority="87" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="90" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J6:N11">
-    <cfRule type="cellIs" dxfId="6" priority="762" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="765" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="763" operator="lessThan">
+    <cfRule type="cellIs" dxfId="8" priority="766" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M46:M530 M532:M558 M560:M575 J562:K575 J576:M576 J577:K577 M577 J578:M580 J581:K581 M581 J582:M584 M584:M585 J585:K585 J586:M586 M587">
-    <cfRule type="cellIs" dxfId="4" priority="88" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="7" priority="91" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M592:M593">
-    <cfRule type="cellIs" dxfId="3" priority="16" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="19" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="15" operator="lessThan">
+    <cfRule type="cellIs" dxfId="5" priority="18" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M598:M599">
-    <cfRule type="cellIs" dxfId="1" priority="7" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="10" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="8" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="11" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J604:J605">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J604:K605">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J604:K605">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
